--- a/public/data/1_elizabeth_plaza.xlsx
+++ b/public/data/1_elizabeth_plaza.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dakotacorp-my.sharepoint.com/personal/jake_dakotacorp_com_au/Documents/Desktop/Commercial Automation/Main file/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jgoldberg\Downloads\portfolio-dashboard\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF8BB5CD-EB0A-471D-B099-EB47D4B7F037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDDD644-350D-4453-9187-D9B29B066A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-12150" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="663" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-4690" windowWidth="38620" windowHeight="21100" tabRatio="663" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="Leasing Fees" sheetId="12" r:id="rId12"/>
     <sheet name="Rental Analysis" sheetId="13" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -42,6 +42,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2942,118 +2964,155 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="173" fontId="20" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3061,116 +3120,79 @@
     <xf numFmtId="167" fontId="11" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="20" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="183" fontId="20" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="20" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="20" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3186,83 +3208,83 @@
     <xf numFmtId="0" fontId="28" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4528,14 +4550,14 @@
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="224" t="s">
+      <c r="A17" s="204" t="s">
         <v>467</v>
       </c>
-      <c r="B17" s="190"/>
-      <c r="C17" s="190"/>
+      <c r="B17" s="191"/>
+      <c r="C17" s="191"/>
       <c r="D17" s="157" t="str">
         <f ca="1">TEXT(Dashboard!E14,"0.0")&amp;" years"</f>
-        <v>4.2 years</v>
+        <v>4.1 years</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
@@ -4553,11 +4575,11 @@
       <c r="A18" s="302" t="s">
         <v>468</v>
       </c>
-      <c r="B18" s="190"/>
-      <c r="C18" s="190"/>
+      <c r="B18" s="191"/>
+      <c r="C18" s="191"/>
       <c r="D18" s="16" t="str">
         <f>TEXT('Input Data'!K26,"0.00%")</f>
-        <v>88.53%</v>
+        <v>88.49%</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
@@ -4572,11 +4594,11 @@
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="224" t="s">
+      <c r="A19" s="204" t="s">
         <v>469</v>
       </c>
-      <c r="B19" s="190"/>
-      <c r="C19" s="190"/>
+      <c r="B19" s="191"/>
+      <c r="C19" s="191"/>
       <c r="D19" s="157" t="s">
         <v>470</v>
       </c>
@@ -4596,8 +4618,8 @@
       <c r="A20" s="302" t="s">
         <v>471</v>
       </c>
-      <c r="B20" s="190"/>
-      <c r="C20" s="190"/>
+      <c r="B20" s="191"/>
+      <c r="C20" s="191"/>
       <c r="D20" s="16" t="s">
         <v>472</v>
       </c>
@@ -4616,11 +4638,11 @@
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="224" t="s">
+      <c r="A21" s="204" t="s">
         <v>474</v>
       </c>
-      <c r="B21" s="190"/>
-      <c r="C21" s="190"/>
+      <c r="B21" s="191"/>
+      <c r="C21" s="191"/>
       <c r="D21" s="157" t="s">
         <v>475</v>
       </c>
@@ -4640,8 +4662,8 @@
       <c r="A22" s="302" t="s">
         <v>476</v>
       </c>
-      <c r="B22" s="190"/>
-      <c r="C22" s="190"/>
+      <c r="B22" s="191"/>
+      <c r="C22" s="191"/>
       <c r="D22" s="16" t="s">
         <v>477</v>
       </c>
@@ -4658,11 +4680,11 @@
       <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="224" t="s">
+      <c r="A23" s="204" t="s">
         <v>478</v>
       </c>
-      <c r="B23" s="190"/>
-      <c r="C23" s="190"/>
+      <c r="B23" s="191"/>
+      <c r="C23" s="191"/>
       <c r="D23" s="157" t="str">
         <f>TEXT(SUM(E3:E12),"#,##0")&amp;" sqm leased/renewed"</f>
         <v>3,333 sqm leased/renewed</v>
@@ -4808,15 +4830,15 @@
       <c r="A2" s="197" t="s">
         <v>480</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="190"/>
-      <c r="D2" s="190"/>
-      <c r="E2" s="190"/>
-      <c r="F2" s="190"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="190"/>
-      <c r="I2" s="190"/>
-      <c r="J2" s="190"/>
+      <c r="B2" s="191"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="191"/>
+      <c r="J2" s="191"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
@@ -4838,7 +4860,7 @@
     </row>
     <row r="4" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
-      <c r="B4" s="199" t="s">
+      <c r="B4" s="189" t="s">
         <v>481</v>
       </c>
       <c r="C4" s="183"/>
@@ -4855,22 +4877,22 @@
     </row>
     <row r="5" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
-      <c r="B5" s="224" t="s">
+      <c r="B5" s="204" t="s">
         <v>482</v>
       </c>
-      <c r="C5" s="190"/>
-      <c r="D5" s="224" t="s">
+      <c r="C5" s="191"/>
+      <c r="D5" s="204" t="s">
         <v>483</v>
       </c>
-      <c r="E5" s="190"/>
-      <c r="F5" s="224" t="s">
+      <c r="E5" s="191"/>
+      <c r="F5" s="204" t="s">
         <v>484</v>
       </c>
-      <c r="G5" s="190"/>
-      <c r="H5" s="224" t="s">
+      <c r="G5" s="191"/>
+      <c r="H5" s="204" t="s">
         <v>485</v>
       </c>
-      <c r="I5" s="190"/>
+      <c r="I5" s="191"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
@@ -4881,19 +4903,19 @@
       <c r="B6" s="303" t="s">
         <v>178</v>
       </c>
-      <c r="C6" s="190"/>
+      <c r="C6" s="191"/>
       <c r="D6" s="303" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="190"/>
+      <c r="E6" s="191"/>
       <c r="F6" s="303" t="s">
         <v>178</v>
       </c>
-      <c r="G6" s="190"/>
+      <c r="G6" s="191"/>
       <c r="H6" s="303" t="s">
         <v>178</v>
       </c>
-      <c r="I6" s="190"/>
+      <c r="I6" s="191"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
@@ -4916,7 +4938,7 @@
     </row>
     <row r="8" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6"/>
-      <c r="B8" s="199" t="s">
+      <c r="B8" s="189" t="s">
         <v>486</v>
       </c>
       <c r="C8" s="183"/>
@@ -5425,7 +5447,7 @@
     </row>
     <row r="27" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6"/>
-      <c r="B27" s="199" t="s">
+      <c r="B27" s="189" t="s">
         <v>521</v>
       </c>
       <c r="C27" s="183"/>
@@ -5642,12 +5664,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="B5:C5"/>
@@ -5655,6 +5671,12 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5705,23 +5727,23 @@
       <c r="A2" s="197" t="s">
         <v>561</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="190"/>
-      <c r="D2" s="190"/>
-      <c r="E2" s="190"/>
-      <c r="F2" s="190"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="190"/>
-      <c r="I2" s="190"/>
-      <c r="J2" s="190"/>
-      <c r="K2" s="190"/>
-      <c r="L2" s="190"/>
-      <c r="M2" s="190"/>
-      <c r="N2" s="190"/>
+      <c r="B2" s="191"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="191"/>
+      <c r="J2" s="191"/>
+      <c r="K2" s="191"/>
+      <c r="L2" s="191"/>
+      <c r="M2" s="191"/>
+      <c r="N2" s="191"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="189" t="s">
         <v>562</v>
       </c>
       <c r="C3" s="183"/>
@@ -5739,31 +5761,31 @@
     </row>
     <row r="4" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
-      <c r="B4" s="224" t="s">
+      <c r="B4" s="204" t="s">
         <v>563</v>
       </c>
-      <c r="C4" s="190"/>
+      <c r="C4" s="191"/>
       <c r="D4" s="164" t="s">
         <v>564</v>
       </c>
-      <c r="E4" s="224" t="s">
+      <c r="E4" s="204" t="s">
         <v>565</v>
       </c>
-      <c r="F4" s="190"/>
+      <c r="F4" s="191"/>
       <c r="G4" s="164" t="s">
         <v>566</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="204" t="s">
         <v>567</v>
       </c>
-      <c r="I4" s="190"/>
+      <c r="I4" s="191"/>
       <c r="J4" s="164" t="s">
         <v>187</v>
       </c>
-      <c r="K4" s="224" t="s">
+      <c r="K4" s="204" t="s">
         <v>568</v>
       </c>
-      <c r="L4" s="190"/>
+      <c r="L4" s="191"/>
       <c r="M4" s="164" t="s">
         <v>569</v>
       </c>
@@ -5787,7 +5809,7 @@
     </row>
     <row r="6" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6"/>
-      <c r="B6" s="199" t="s">
+      <c r="B6" s="189" t="s">
         <v>570</v>
       </c>
       <c r="C6" s="183"/>
@@ -6039,7 +6061,7 @@
     </row>
     <row r="14" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
-      <c r="B14" s="199" t="s">
+      <c r="B14" s="189" t="s">
         <v>585</v>
       </c>
       <c r="C14" s="183"/>
@@ -6060,17 +6082,17 @@
       <c r="B15" s="210" t="s">
         <v>586</v>
       </c>
-      <c r="C15" s="190"/>
-      <c r="D15" s="190"/>
-      <c r="E15" s="190"/>
-      <c r="F15" s="190"/>
-      <c r="G15" s="190"/>
-      <c r="H15" s="190"/>
-      <c r="I15" s="190"/>
-      <c r="J15" s="190"/>
-      <c r="K15" s="190"/>
-      <c r="L15" s="190"/>
-      <c r="M15" s="190"/>
+      <c r="C15" s="191"/>
+      <c r="D15" s="191"/>
+      <c r="E15" s="191"/>
+      <c r="F15" s="191"/>
+      <c r="G15" s="191"/>
+      <c r="H15" s="191"/>
+      <c r="I15" s="191"/>
+      <c r="J15" s="191"/>
+      <c r="K15" s="191"/>
+      <c r="L15" s="191"/>
+      <c r="M15" s="191"/>
       <c r="N15" s="6"/>
     </row>
   </sheetData>
@@ -6125,13 +6147,13 @@
       <c r="A2" s="197" t="s">
         <v>588</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="190"/>
-      <c r="D2" s="190"/>
-      <c r="E2" s="190"/>
-      <c r="F2" s="190"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="190"/>
+      <c r="B2" s="191"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
     </row>
     <row r="3" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
@@ -6145,7 +6167,7 @@
     </row>
     <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
-      <c r="B4" s="199" t="s">
+      <c r="B4" s="189" t="s">
         <v>589</v>
       </c>
       <c r="C4" s="183"/>
@@ -6200,7 +6222,7 @@
     </row>
     <row r="8" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6"/>
-      <c r="B8" s="199" t="s">
+      <c r="B8" s="189" t="s">
         <v>594</v>
       </c>
       <c r="C8" s="183"/>
@@ -6304,7 +6326,7 @@
     </row>
     <row r="15" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6"/>
-      <c r="B15" s="199" t="s">
+      <c r="B15" s="189" t="s">
         <v>604</v>
       </c>
       <c r="C15" s="183"/>
@@ -6442,7 +6464,7 @@
     </row>
     <row r="24" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6"/>
-      <c r="B24" s="199" t="s">
+      <c r="B24" s="189" t="s">
         <v>612</v>
       </c>
       <c r="C24" s="183"/>
@@ -6562,7 +6584,7 @@
     </row>
     <row r="32" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6"/>
-      <c r="B32" s="199" t="s">
+      <c r="B32" s="189" t="s">
         <v>620</v>
       </c>
       <c r="C32" s="183"/>
@@ -6574,7 +6596,7 @@
     </row>
     <row r="33" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6"/>
-      <c r="B33" s="213" t="s">
+      <c r="B33" s="218" t="s">
         <v>621</v>
       </c>
       <c r="C33" s="183"/>
@@ -6594,11 +6616,11 @@
     </row>
     <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6"/>
-      <c r="B34" s="192" t="s">
+      <c r="B34" s="194" t="s">
         <v>626</v>
       </c>
-      <c r="C34" s="190"/>
-      <c r="D34" s="190"/>
+      <c r="C34" s="191"/>
+      <c r="D34" s="191"/>
       <c r="E34" s="172">
         <f>D11</f>
         <v>985</v>
@@ -6621,8 +6643,8 @@
       <c r="B35" s="304" t="s">
         <v>627</v>
       </c>
-      <c r="C35" s="190"/>
-      <c r="D35" s="190"/>
+      <c r="C35" s="191"/>
+      <c r="D35" s="191"/>
       <c r="E35" s="175">
         <f>D27</f>
         <v>78.849999999999994</v>
@@ -6642,11 +6664,11 @@
     </row>
     <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6"/>
-      <c r="B36" s="192" t="s">
+      <c r="B36" s="194" t="s">
         <v>628</v>
       </c>
-      <c r="C36" s="190"/>
-      <c r="D36" s="190"/>
+      <c r="C36" s="191"/>
+      <c r="D36" s="191"/>
       <c r="E36" s="172">
         <f>D30</f>
         <v>0</v>
@@ -6669,8 +6691,8 @@
       <c r="B37" s="304" t="s">
         <v>629</v>
       </c>
-      <c r="C37" s="190"/>
-      <c r="D37" s="190"/>
+      <c r="C37" s="191"/>
+      <c r="D37" s="191"/>
       <c r="E37" s="175">
         <f>IF(D20&gt;0,-D11/D9/12*MIN(D20,12),IF(D16&gt;0,-D18,0))</f>
         <v>-1.1772908366533865</v>
@@ -6690,7 +6712,7 @@
     </row>
     <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6"/>
-      <c r="B38" s="199" t="s">
+      <c r="B38" s="189" t="s">
         <v>630</v>
       </c>
       <c r="C38" s="183"/>
@@ -6724,7 +6746,7 @@
     </row>
     <row r="40" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="6"/>
-      <c r="B40" s="199" t="s">
+      <c r="B40" s="189" t="s">
         <v>631</v>
       </c>
       <c r="C40" s="183"/>
@@ -6864,7 +6886,7 @@
     </row>
     <row r="49" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="6"/>
-      <c r="B49" s="199" t="s">
+      <c r="B49" s="189" t="s">
         <v>638</v>
       </c>
       <c r="C49" s="183"/>
@@ -7005,7 +7027,7 @@
     </row>
     <row r="58" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="6"/>
-      <c r="B58" s="199" t="s">
+      <c r="B58" s="189" t="s">
         <v>646</v>
       </c>
       <c r="C58" s="183"/>
@@ -7129,18 +7151,24 @@
     </row>
     <row r="66" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="6"/>
-      <c r="B66" s="267" t="s">
+      <c r="B66" s="259" t="s">
         <v>652</v>
       </c>
-      <c r="C66" s="190"/>
-      <c r="D66" s="190"/>
-      <c r="E66" s="190"/>
-      <c r="F66" s="190"/>
-      <c r="G66" s="190"/>
-      <c r="H66" s="190"/>
+      <c r="C66" s="191"/>
+      <c r="D66" s="191"/>
+      <c r="E66" s="191"/>
+      <c r="F66" s="191"/>
+      <c r="G66" s="191"/>
+      <c r="H66" s="191"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B66:H66"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B58:G58"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
@@ -7152,12 +7180,6 @@
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B66:H66"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B49:G49"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B58:G58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -7197,13 +7219,13 @@
       <c r="A2" s="197" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="190"/>
-      <c r="D2" s="190"/>
-      <c r="E2" s="190"/>
-      <c r="F2" s="190"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="190"/>
+      <c r="B2" s="191"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
     </row>
     <row r="3" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
@@ -7217,7 +7239,7 @@
     </row>
     <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
-      <c r="B4" s="199" t="s">
+      <c r="B4" s="189" t="s">
         <v>182</v>
       </c>
       <c r="C4" s="183"/>
@@ -7229,141 +7251,141 @@
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
-      <c r="B5" s="193" t="s">
+      <c r="B5" s="192" t="s">
         <v>183</v>
       </c>
-      <c r="C5" s="190"/>
-      <c r="D5" s="192" t="s">
+      <c r="C5" s="191"/>
+      <c r="D5" s="194" t="s">
         <v>184</v>
       </c>
-      <c r="E5" s="190"/>
-      <c r="F5" s="190"/>
-      <c r="G5" s="190"/>
+      <c r="E5" s="191"/>
+      <c r="F5" s="191"/>
+      <c r="G5" s="191"/>
       <c r="H5" s="6"/>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6"/>
-      <c r="B6" s="191" t="s">
+      <c r="B6" s="190" t="s">
         <v>185</v>
       </c>
-      <c r="C6" s="190"/>
+      <c r="C6" s="191"/>
       <c r="D6" s="198">
         <v>46142</v>
       </c>
-      <c r="E6" s="190"/>
-      <c r="F6" s="190"/>
-      <c r="G6" s="190"/>
+      <c r="E6" s="191"/>
+      <c r="F6" s="191"/>
+      <c r="G6" s="191"/>
       <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
-      <c r="B7" s="193" t="s">
+      <c r="B7" s="192" t="s">
         <v>186</v>
       </c>
-      <c r="C7" s="190"/>
-      <c r="D7" s="192" t="s">
+      <c r="C7" s="191"/>
+      <c r="D7" s="194" t="s">
         <v>187</v>
       </c>
-      <c r="E7" s="190"/>
-      <c r="F7" s="190"/>
-      <c r="G7" s="190"/>
+      <c r="E7" s="191"/>
+      <c r="F7" s="191"/>
+      <c r="G7" s="191"/>
       <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6"/>
-      <c r="B8" s="191" t="s">
+      <c r="B8" s="190" t="s">
         <v>188</v>
       </c>
-      <c r="C8" s="190"/>
-      <c r="D8" s="194">
+      <c r="C8" s="191"/>
+      <c r="D8" s="196">
         <f>'Input Data'!B53</f>
         <v>0</v>
       </c>
-      <c r="E8" s="190"/>
-      <c r="F8" s="190"/>
-      <c r="G8" s="190"/>
+      <c r="E8" s="191"/>
+      <c r="F8" s="191"/>
+      <c r="G8" s="191"/>
       <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
-      <c r="B9" s="193" t="s">
+      <c r="B9" s="192" t="s">
         <v>189</v>
       </c>
-      <c r="C9" s="190"/>
-      <c r="D9" s="192">
+      <c r="C9" s="191"/>
+      <c r="D9" s="194">
         <f>'Input Data'!B54</f>
         <v>0</v>
       </c>
-      <c r="E9" s="190"/>
-      <c r="F9" s="190"/>
-      <c r="G9" s="190"/>
+      <c r="E9" s="191"/>
+      <c r="F9" s="191"/>
+      <c r="G9" s="191"/>
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6"/>
-      <c r="B10" s="191" t="s">
+      <c r="B10" s="190" t="s">
         <v>190</v>
       </c>
-      <c r="C10" s="190"/>
-      <c r="D10" s="194">
+      <c r="C10" s="191"/>
+      <c r="D10" s="196">
         <f>'Input Data'!V53</f>
         <v>0</v>
       </c>
-      <c r="E10" s="190"/>
-      <c r="F10" s="190"/>
-      <c r="G10" s="190"/>
+      <c r="E10" s="191"/>
+      <c r="F10" s="191"/>
+      <c r="G10" s="191"/>
       <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
-      <c r="B11" s="193" t="s">
+      <c r="B11" s="192" t="s">
         <v>191</v>
       </c>
-      <c r="C11" s="190"/>
-      <c r="D11" s="192">
+      <c r="C11" s="191"/>
+      <c r="D11" s="194">
         <f>'Input Data'!K53</f>
         <v>0</v>
       </c>
-      <c r="E11" s="190"/>
-      <c r="F11" s="190"/>
-      <c r="G11" s="190"/>
+      <c r="E11" s="191"/>
+      <c r="F11" s="191"/>
+      <c r="G11" s="191"/>
       <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6"/>
-      <c r="B12" s="191" t="s">
+      <c r="B12" s="190" t="s">
         <v>192</v>
       </c>
-      <c r="C12" s="190"/>
-      <c r="D12" s="194" t="s">
+      <c r="C12" s="191"/>
+      <c r="D12" s="196" t="s">
         <v>193</v>
       </c>
-      <c r="E12" s="190"/>
-      <c r="F12" s="190"/>
-      <c r="G12" s="190"/>
+      <c r="E12" s="191"/>
+      <c r="F12" s="191"/>
+      <c r="G12" s="191"/>
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6"/>
-      <c r="B13" s="193" t="s">
+      <c r="B13" s="192" t="s">
         <v>194</v>
       </c>
-      <c r="C13" s="190"/>
-      <c r="D13" s="192" t="s">
+      <c r="C13" s="191"/>
+      <c r="D13" s="194" t="s">
         <v>195</v>
       </c>
-      <c r="E13" s="190"/>
-      <c r="F13" s="190"/>
-      <c r="G13" s="190"/>
+      <c r="E13" s="191"/>
+      <c r="F13" s="191"/>
+      <c r="G13" s="191"/>
       <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
-      <c r="B14" s="191" t="s">
+      <c r="B14" s="190" t="s">
         <v>196</v>
       </c>
-      <c r="C14" s="190"/>
-      <c r="D14" s="196"/>
+      <c r="C14" s="191"/>
+      <c r="D14" s="195"/>
       <c r="E14" s="186"/>
       <c r="F14" s="186"/>
       <c r="G14" s="186"/>
@@ -7371,11 +7393,11 @@
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6"/>
-      <c r="B15" s="193" t="s">
+      <c r="B15" s="192" t="s">
         <v>197</v>
       </c>
-      <c r="C15" s="190"/>
-      <c r="D15" s="196"/>
+      <c r="C15" s="191"/>
+      <c r="D15" s="195"/>
       <c r="E15" s="186"/>
       <c r="F15" s="186"/>
       <c r="G15" s="186"/>
@@ -7383,11 +7405,11 @@
     </row>
     <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6"/>
-      <c r="B16" s="191" t="s">
+      <c r="B16" s="190" t="s">
         <v>198</v>
       </c>
-      <c r="C16" s="190"/>
-      <c r="D16" s="200"/>
+      <c r="C16" s="191"/>
+      <c r="D16" s="193"/>
       <c r="E16" s="186"/>
       <c r="F16" s="186"/>
       <c r="G16" s="186"/>
@@ -7405,7 +7427,7 @@
     </row>
     <row r="18" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6"/>
-      <c r="B18" s="199" t="s">
+      <c r="B18" s="189" t="s">
         <v>199</v>
       </c>
       <c r="C18" s="183"/>
@@ -7639,7 +7661,7 @@
     </row>
     <row r="39" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="6"/>
-      <c r="B39" s="199" t="s">
+      <c r="B39" s="189" t="s">
         <v>210</v>
       </c>
       <c r="C39" s="183"/>
@@ -7654,13 +7676,13 @@
       <c r="B40" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="C40" s="195" t="s">
+      <c r="C40" s="200" t="s">
         <v>212</v>
       </c>
-      <c r="D40" s="190"/>
-      <c r="E40" s="190"/>
-      <c r="F40" s="190"/>
-      <c r="G40" s="190"/>
+      <c r="D40" s="191"/>
+      <c r="E40" s="191"/>
+      <c r="F40" s="191"/>
+      <c r="G40" s="191"/>
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -7668,13 +7690,13 @@
       <c r="B41" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="C41" s="189" t="s">
+      <c r="C41" s="199" t="s">
         <v>214</v>
       </c>
-      <c r="D41" s="190"/>
-      <c r="E41" s="190"/>
-      <c r="F41" s="190"/>
-      <c r="G41" s="190"/>
+      <c r="D41" s="191"/>
+      <c r="E41" s="191"/>
+      <c r="F41" s="191"/>
+      <c r="G41" s="191"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -7682,13 +7704,13 @@
       <c r="B42" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="C42" s="195" t="s">
+      <c r="C42" s="200" t="s">
         <v>216</v>
       </c>
-      <c r="D42" s="190"/>
-      <c r="E42" s="190"/>
-      <c r="F42" s="190"/>
-      <c r="G42" s="190"/>
+      <c r="D42" s="191"/>
+      <c r="E42" s="191"/>
+      <c r="F42" s="191"/>
+      <c r="G42" s="191"/>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -7696,13 +7718,13 @@
       <c r="B43" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="C43" s="189" t="s">
+      <c r="C43" s="199" t="s">
         <v>218</v>
       </c>
-      <c r="D43" s="190"/>
-      <c r="E43" s="190"/>
-      <c r="F43" s="190"/>
-      <c r="G43" s="190"/>
+      <c r="D43" s="191"/>
+      <c r="E43" s="191"/>
+      <c r="F43" s="191"/>
+      <c r="G43" s="191"/>
       <c r="H43" s="6"/>
     </row>
     <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -7710,13 +7732,13 @@
       <c r="B44" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="C44" s="195" t="s">
+      <c r="C44" s="200" t="s">
         <v>220</v>
       </c>
-      <c r="D44" s="190"/>
-      <c r="E44" s="190"/>
-      <c r="F44" s="190"/>
-      <c r="G44" s="190"/>
+      <c r="D44" s="191"/>
+      <c r="E44" s="191"/>
+      <c r="F44" s="191"/>
+      <c r="G44" s="191"/>
       <c r="H44" s="6"/>
     </row>
     <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -7724,13 +7746,13 @@
       <c r="B45" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="C45" s="189" t="s">
+      <c r="C45" s="199" t="s">
         <v>222</v>
       </c>
-      <c r="D45" s="190"/>
-      <c r="E45" s="190"/>
-      <c r="F45" s="190"/>
-      <c r="G45" s="190"/>
+      <c r="D45" s="191"/>
+      <c r="E45" s="191"/>
+      <c r="F45" s="191"/>
+      <c r="G45" s="191"/>
       <c r="H45" s="6"/>
     </row>
     <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -7738,13 +7760,13 @@
       <c r="B46" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="C46" s="195" t="s">
+      <c r="C46" s="200" t="s">
         <v>224</v>
       </c>
-      <c r="D46" s="190"/>
-      <c r="E46" s="190"/>
-      <c r="F46" s="190"/>
-      <c r="G46" s="190"/>
+      <c r="D46" s="191"/>
+      <c r="E46" s="191"/>
+      <c r="F46" s="191"/>
+      <c r="G46" s="191"/>
       <c r="H46" s="6"/>
     </row>
     <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -7752,13 +7774,13 @@
       <c r="B47" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="C47" s="189" t="s">
+      <c r="C47" s="199" t="s">
         <v>226</v>
       </c>
-      <c r="D47" s="190"/>
-      <c r="E47" s="190"/>
-      <c r="F47" s="190"/>
-      <c r="G47" s="190"/>
+      <c r="D47" s="191"/>
+      <c r="E47" s="191"/>
+      <c r="F47" s="191"/>
+      <c r="G47" s="191"/>
       <c r="H47" s="6"/>
     </row>
     <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -7766,13 +7788,13 @@
       <c r="B48" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="C48" s="195" t="s">
+      <c r="C48" s="200" t="s">
         <v>228</v>
       </c>
-      <c r="D48" s="190"/>
-      <c r="E48" s="190"/>
-      <c r="F48" s="190"/>
-      <c r="G48" s="190"/>
+      <c r="D48" s="191"/>
+      <c r="E48" s="191"/>
+      <c r="F48" s="191"/>
+      <c r="G48" s="191"/>
       <c r="H48" s="6"/>
     </row>
     <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -7780,24 +7802,33 @@
       <c r="B49" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="C49" s="189" t="s">
+      <c r="C49" s="199" t="s">
         <v>230</v>
       </c>
-      <c r="D49" s="190"/>
-      <c r="E49" s="190"/>
-      <c r="F49" s="190"/>
-      <c r="G49" s="190"/>
+      <c r="D49" s="191"/>
+      <c r="E49" s="191"/>
+      <c r="F49" s="191"/>
+      <c r="G49" s="191"/>
       <c r="H49" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C48:G48"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="D14:G14"/>
@@ -7814,22 +7845,13 @@
     <mergeCell ref="D11:G11"/>
     <mergeCell ref="D13:G13"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D7:G7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8076,11 +8098,11 @@
       </c>
       <c r="V3" s="26">
         <f t="shared" ref="V3:V24" ca="1" si="2">IFERROR(MAX((H3-TODAY())/365.25,0),0)</f>
-        <v>2.5051334702258727</v>
+        <v>2.4120465434633811</v>
       </c>
       <c r="W3" s="22">
         <f t="shared" ref="W3:W24" ca="1" si="3">F3*V3</f>
-        <v>269.80287474332653</v>
+        <v>259.77741273100617</v>
       </c>
       <c r="X3" s="25">
         <v>950</v>
@@ -8181,11 +8203,11 @@
       </c>
       <c r="V4" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>4.9993155373032172</v>
+        <v>4.9062286105407251</v>
       </c>
       <c r="W4" s="34">
         <f t="shared" ca="1" si="3"/>
-        <v>3976.9555099247091</v>
+        <v>3902.9048596851467</v>
       </c>
       <c r="X4" s="37">
         <v>870</v>
@@ -8286,11 +8308,11 @@
       </c>
       <c r="V5" s="26">
         <f t="shared" ca="1" si="2"/>
-        <v>4.9993155373032172</v>
+        <v>4.9062286105407251</v>
       </c>
       <c r="W5" s="22">
         <f t="shared" ca="1" si="3"/>
-        <v>5234.283367556468</v>
+        <v>5136.8213552361394</v>
       </c>
       <c r="X5" s="25">
         <v>870</v>
@@ -8391,11 +8413,11 @@
       </c>
       <c r="V6" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>4.9993155373032172</v>
+        <v>4.9062286105407251</v>
       </c>
       <c r="W6" s="34">
         <f t="shared" ca="1" si="3"/>
-        <v>2185.2008213552363</v>
+        <v>2144.5125256673509</v>
       </c>
       <c r="X6" s="37">
         <v>870</v>
@@ -8496,11 +8518,11 @@
       </c>
       <c r="V7" s="26">
         <f t="shared" ca="1" si="2"/>
-        <v>2.9185489390828199</v>
+        <v>2.8254620123203287</v>
       </c>
       <c r="W7" s="22">
         <f t="shared" ca="1" si="3"/>
-        <v>670.68254620123207</v>
+        <v>649.29117043121153</v>
       </c>
       <c r="X7" s="25">
         <v>950</v>
@@ -8601,11 +8623,11 @@
       </c>
       <c r="V8" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>2.6666666666666665</v>
+        <v>2.5735797399041753</v>
       </c>
       <c r="W8" s="34">
         <f t="shared" ca="1" si="3"/>
-        <v>1102.6666666666665</v>
+        <v>1064.1752224503764</v>
       </c>
       <c r="X8" s="37">
         <v>990</v>
@@ -8706,11 +8728,11 @@
       </c>
       <c r="V9" s="26">
         <f t="shared" ca="1" si="2"/>
-        <v>3.2087611225188226</v>
+        <v>3.1156741957563314</v>
       </c>
       <c r="W9" s="22">
         <f t="shared" ca="1" si="3"/>
-        <v>1449.3973990417521</v>
+        <v>1407.3500342231348</v>
       </c>
       <c r="X9" s="25">
         <v>955</v>
@@ -8811,11 +8833,11 @@
       </c>
       <c r="V10" s="47">
         <f t="shared" ca="1" si="2"/>
-        <v>0.91718001368925395</v>
+        <v>0.82409308692676253</v>
       </c>
       <c r="W10" s="43">
         <f t="shared" ca="1" si="3"/>
-        <v>173.71389459274471</v>
+        <v>156.08323066392882</v>
       </c>
       <c r="X10" s="45">
         <v>990</v>
@@ -8916,11 +8938,11 @@
       </c>
       <c r="V11" s="26">
         <f t="shared" ca="1" si="2"/>
-        <v>6.0862422997946615</v>
+        <v>5.9931553730321694</v>
       </c>
       <c r="W11" s="22">
         <f t="shared" ca="1" si="3"/>
-        <v>1630.5043121149897</v>
+        <v>1605.5663244353179</v>
       </c>
       <c r="X11" s="25">
         <v>955</v>
@@ -9021,11 +9043,11 @@
       </c>
       <c r="V12" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>3.2087611225188226</v>
+        <v>3.1156741957563314</v>
       </c>
       <c r="W12" s="34">
         <f t="shared" ca="1" si="3"/>
-        <v>1553.3612594113622</v>
+        <v>1508.2978781656402</v>
       </c>
       <c r="X12" s="37">
         <v>1020</v>
@@ -9126,11 +9148,11 @@
       </c>
       <c r="V13" s="26">
         <f t="shared" ca="1" si="2"/>
-        <v>3.2087611225188226</v>
+        <v>3.1156741957563314</v>
       </c>
       <c r="W13" s="22">
         <f t="shared" ca="1" si="3"/>
-        <v>1172.8021902806297</v>
+        <v>1138.7789185489391</v>
       </c>
       <c r="X13" s="25">
         <v>1020</v>
@@ -9231,11 +9253,11 @@
       </c>
       <c r="V14" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>2.001368925393566</v>
+        <v>1.9082819986310746</v>
       </c>
       <c r="W14" s="34">
         <f t="shared" ca="1" si="3"/>
-        <v>1374.3400410677618</v>
+        <v>1310.417248459959</v>
       </c>
       <c r="X14" s="37">
         <v>990</v>
@@ -9336,11 +9358,11 @@
       </c>
       <c r="V15" s="26">
         <f t="shared" ca="1" si="2"/>
-        <v>4.3367556468172488</v>
+        <v>4.2436687200547567</v>
       </c>
       <c r="W15" s="22">
         <f t="shared" ca="1" si="3"/>
-        <v>504.36468172484604</v>
+        <v>493.53867214236817</v>
       </c>
       <c r="X15" s="25">
         <v>990</v>
@@ -9441,11 +9463,11 @@
       </c>
       <c r="V16" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>1.0075290896646132</v>
+        <v>0.91444216290212188</v>
       </c>
       <c r="W16" s="34">
         <f t="shared" ca="1" si="3"/>
-        <v>456.71293634496919</v>
+        <v>414.51663244353188</v>
       </c>
       <c r="X16" s="37">
         <v>1040</v>
@@ -9546,11 +9568,11 @@
       </c>
       <c r="V17" s="26">
         <f t="shared" ca="1" si="2"/>
-        <v>3.5044490075290895</v>
+        <v>3.4113620807665983</v>
       </c>
       <c r="W17" s="22">
         <f t="shared" ca="1" si="3"/>
-        <v>1207.2826830937713</v>
+        <v>1175.2142368240932</v>
       </c>
       <c r="X17" s="25">
         <v>1040</v>
@@ -9651,11 +9673,11 @@
       </c>
       <c r="V18" s="38">
         <f t="shared" ca="1" si="2"/>
-        <v>4.3367556468172488</v>
+        <v>4.2436687200547567</v>
       </c>
       <c r="W18" s="34">
         <f t="shared" ca="1" si="3"/>
-        <v>1088.5256673511294</v>
+        <v>1065.1608487337439</v>
       </c>
       <c r="X18" s="37">
         <v>990</v>
@@ -9756,11 +9778,11 @@
       </c>
       <c r="V19" s="26">
         <f t="shared" ca="1" si="2"/>
-        <v>4.4599589322381927</v>
+        <v>4.3668720054757015</v>
       </c>
       <c r="W19" s="22">
         <f t="shared" ca="1" si="3"/>
-        <v>2390.5379876796715</v>
+        <v>2340.6433949349762</v>
       </c>
       <c r="X19" s="25">
         <v>1010</v>
@@ -9845,11 +9867,11 @@
       <c r="U20" s="53"/>
       <c r="V20" s="54">
         <f t="shared" ca="1" si="2"/>
-        <v>6.0013689253935665</v>
+        <v>5.9082819986310744</v>
       </c>
       <c r="W20" s="51">
         <f t="shared" ca="1" si="3"/>
-        <v>1118.6551676933609</v>
+        <v>1101.3037645448323</v>
       </c>
       <c r="X20" s="53"/>
       <c r="Y20" s="52">
@@ -10031,7 +10053,7 @@
       </c>
       <c r="E23" s="56"/>
       <c r="F23" s="51">
-        <v>236</v>
+        <v>242.5</v>
       </c>
       <c r="G23" s="53"/>
       <c r="H23" s="53"/>
@@ -10104,10 +10126,10 @@
         <v>164</v>
       </c>
       <c r="F24" s="22">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="G24" s="23">
-        <v>46203</v>
+        <v>46296</v>
       </c>
       <c r="H24" s="23">
         <v>49582</v>
@@ -10120,7 +10142,7 @@
       </c>
       <c r="K24" s="25">
         <f t="shared" si="0"/>
-        <v>557440</v>
+        <v>569920</v>
       </c>
       <c r="L24" s="25">
         <v>-671072</v>
@@ -10131,7 +10153,7 @@
       <c r="P24" s="25"/>
       <c r="Q24" s="25">
         <f t="shared" si="1"/>
-        <v>-113632</v>
+        <v>-101152</v>
       </c>
       <c r="R24" s="13"/>
       <c r="S24" s="14" t="s">
@@ -10143,11 +10165,11 @@
       <c r="U24" s="14"/>
       <c r="V24" s="26">
         <f t="shared" ca="1" si="2"/>
-        <v>9.2511978097193701</v>
+        <v>9.158110882956878</v>
       </c>
       <c r="W24" s="22">
         <f t="shared" ca="1" si="3"/>
-        <v>4958.642026009582</v>
+        <v>5018.6447638603695</v>
       </c>
       <c r="X24" s="25">
         <v>1040</v>
@@ -10188,7 +10210,7 @@
       <c r="E25" s="183"/>
       <c r="F25" s="62">
         <f>SUM(F3:F24)</f>
-        <v>8922.4000000000015</v>
+        <v>8940.9000000000015</v>
       </c>
       <c r="G25" s="61"/>
       <c r="H25" s="61"/>
@@ -10196,7 +10218,7 @@
       <c r="J25" s="61"/>
       <c r="K25" s="63">
         <f>SUM(K3:K24)</f>
-        <v>7199043.9990000008</v>
+        <v>7211523.9990000008</v>
       </c>
       <c r="L25" s="63">
         <f>SUM(L3:L24)</f>
@@ -10208,7 +10230,7 @@
       <c r="P25" s="61"/>
       <c r="Q25" s="63">
         <f>SUM(Q3:Q24)</f>
-        <v>5377867.9789999994</v>
+        <v>5390347.9789999994</v>
       </c>
       <c r="R25" s="61"/>
       <c r="S25" s="61"/>
@@ -10216,11 +10238,11 @@
       <c r="U25" s="61"/>
       <c r="V25" s="64">
         <f ca="1">IFERROR(SUMPRODUCT((H3:H24&lt;&gt;"")*F3:F24*MAX((H3:H24-TODAY())/365.25,0))/SUMPRODUCT((H3:H24&lt;&gt;"")*F3:F24),0)</f>
-        <v>9.2511978097193683</v>
+        <v>9.1581108829568798</v>
       </c>
       <c r="W25" s="62">
         <f ca="1">SUM(W3:W24)</f>
-        <v>32518.432032854202</v>
+        <v>31892.998494182066</v>
       </c>
       <c r="X25" s="61"/>
       <c r="Y25" s="61"/>
@@ -10243,35 +10265,35 @@
       </c>
       <c r="E26" s="66">
         <f>SUMPRODUCT((H3:H24&lt;&gt;"")*F3:F24)</f>
-        <v>7899.4000000000005</v>
+        <v>7911.4000000000005</v>
       </c>
       <c r="F26" s="65" t="s">
         <v>170</v>
       </c>
       <c r="G26" s="66">
         <f>SUMPRODUCT((H3:H24="")*F3:F24)</f>
-        <v>1023</v>
+        <v>1029.5</v>
       </c>
       <c r="H26" s="65" t="s">
         <v>171</v>
       </c>
       <c r="I26" s="66">
         <f>SUM(F3:F24)</f>
-        <v>8922.4000000000015</v>
+        <v>8940.9000000000015</v>
       </c>
       <c r="J26" s="65" t="s">
         <v>172</v>
       </c>
       <c r="K26" s="67">
         <f>IFERROR(E26/I26,0)</f>
-        <v>0.88534475029140136</v>
+        <v>0.88485499222673325</v>
       </c>
       <c r="L26" s="65" t="s">
         <v>173</v>
       </c>
       <c r="M26" s="67">
         <f>IFERROR(G26/I26,0)</f>
-        <v>0.11465524970859857</v>
+        <v>0.11514500777326665</v>
       </c>
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
@@ -10318,7 +10340,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="233" t="s">
+      <c r="A1" s="239" t="s">
         <v>231</v>
       </c>
       <c r="B1" s="183"/>
@@ -10336,7 +10358,7 @@
       <c r="N1" s="183"/>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="246" t="s">
+      <c r="A2" s="221" t="s">
         <v>232</v>
       </c>
       <c r="B2" s="183"/>
@@ -10371,27 +10393,27 @@
     </row>
     <row r="4" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="225" t="s">
         <v>233</v>
       </c>
       <c r="C4" s="183"/>
-      <c r="D4" s="227" t="s">
+      <c r="D4" s="226" t="s">
         <v>234</v>
       </c>
       <c r="E4" s="183"/>
-      <c r="F4" s="242" t="s">
+      <c r="F4" s="236" t="s">
         <v>235</v>
       </c>
       <c r="G4" s="183"/>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="226" t="s">
         <v>236</v>
       </c>
       <c r="I4" s="183"/>
-      <c r="J4" s="223" t="s">
+      <c r="J4" s="250" t="s">
         <v>237</v>
       </c>
       <c r="K4" s="183"/>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="237" t="s">
         <v>238</v>
       </c>
       <c r="M4" s="183"/>
@@ -10399,32 +10421,32 @@
     </row>
     <row r="5" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
-      <c r="B5" s="250">
+      <c r="B5" s="213">
         <f>SUM('Input Data'!F3:F24)</f>
-        <v>8922.4000000000015</v>
+        <v>8940.9000000000015</v>
       </c>
       <c r="C5" s="183"/>
-      <c r="D5" s="251">
+      <c r="D5" s="215">
         <f>SUMPRODUCT(('Input Data'!H3:H24&lt;&gt;"")*'Input Data'!F3:F24)</f>
-        <v>7899.4000000000005</v>
+        <v>7911.4000000000005</v>
       </c>
       <c r="E5" s="183"/>
-      <c r="F5" s="235">
+      <c r="F5" s="241">
         <f>SUMPRODUCT(('Input Data'!H3:H24="")*'Input Data'!F3:F24)</f>
-        <v>1023</v>
+        <v>1029.5</v>
       </c>
       <c r="G5" s="183"/>
-      <c r="H5" s="241">
-        <f>IFERROR(SUMPRODUCT(('Input Data'!H3:H24&lt;&gt;"")*'Input Data'!F3:F24)/SUM('Input Data'!F3:F24),0)</f>
-        <v>0.88534475029140136</v>
+      <c r="H5" s="235" cm="1">
+        <f t="array" ref="H5">IFERROR(SUMPRODUCT(('Input Data'!H3:H24&lt;&gt;"")*'Input Data'!F3:F24)/SUM('Input Data'!F3:F24),0)</f>
+        <v>0.88485499222673325</v>
       </c>
       <c r="I5" s="183"/>
-      <c r="J5" s="254">
-        <f>IFERROR(SUMPRODUCT(('Input Data'!H3:H24="")*'Input Data'!F3:F24)/SUM('Input Data'!F3:F24),0)</f>
-        <v>0.11465524970859857</v>
+      <c r="J5" s="219" cm="1">
+        <f t="array" ref="J5">IFERROR(SUMPRODUCT(('Input Data'!H3:H24="")*'Input Data'!F3:F24)/SUM('Input Data'!F3:F24),0)</f>
+        <v>0.11514500777326665</v>
       </c>
       <c r="K5" s="183"/>
-      <c r="L5" s="218" t="s">
+      <c r="L5" s="252" t="s">
         <v>239</v>
       </c>
       <c r="M5" s="183"/>
@@ -10432,17 +10454,17 @@
     </row>
     <row r="6" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6"/>
-      <c r="B6" s="229"/>
+      <c r="B6" s="242"/>
       <c r="C6" s="183"/>
-      <c r="D6" s="214"/>
+      <c r="D6" s="228"/>
       <c r="E6" s="186"/>
-      <c r="F6" s="230"/>
+      <c r="F6" s="243"/>
       <c r="G6" s="186"/>
-      <c r="H6" s="214"/>
+      <c r="H6" s="228"/>
       <c r="I6" s="186"/>
-      <c r="J6" s="256"/>
+      <c r="J6" s="229"/>
       <c r="K6" s="186"/>
-      <c r="L6" s="206"/>
+      <c r="L6" s="203"/>
       <c r="M6" s="186"/>
       <c r="N6" s="6"/>
     </row>
@@ -10464,27 +10486,27 @@
     </row>
     <row r="8" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6"/>
-      <c r="B8" s="225" t="s">
+      <c r="B8" s="237" t="s">
         <v>240</v>
       </c>
       <c r="C8" s="183"/>
-      <c r="D8" s="252" t="s">
+      <c r="D8" s="225" t="s">
         <v>241</v>
       </c>
       <c r="E8" s="183"/>
-      <c r="F8" s="242" t="s">
+      <c r="F8" s="236" t="s">
         <v>242</v>
       </c>
       <c r="G8" s="183"/>
-      <c r="H8" s="225" t="s">
+      <c r="H8" s="237" t="s">
         <v>243</v>
       </c>
       <c r="I8" s="183"/>
-      <c r="J8" s="225" t="s">
+      <c r="J8" s="237" t="s">
         <v>244</v>
       </c>
       <c r="K8" s="183"/>
-      <c r="L8" s="225" t="s">
+      <c r="L8" s="237" t="s">
         <v>245</v>
       </c>
       <c r="M8" s="183"/>
@@ -10492,32 +10514,32 @@
     </row>
     <row r="9" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
-      <c r="B9" s="247">
+      <c r="B9" s="222">
         <f>SUM('Input Data'!K3:K24)</f>
-        <v>7199043.9990000008</v>
+        <v>7211523.9990000008</v>
       </c>
       <c r="C9" s="183"/>
-      <c r="D9" s="236">
+      <c r="D9" s="253">
         <f>SUM('Input Data'!Q3:Q24)</f>
-        <v>5377867.9789999994</v>
+        <v>5390347.9789999994</v>
       </c>
       <c r="E9" s="183"/>
-      <c r="F9" s="238">
+      <c r="F9" s="254">
         <f>SUM('Input Data'!L3:L24)</f>
         <v>-2473509.17</v>
       </c>
       <c r="G9" s="183"/>
-      <c r="H9" s="211">
+      <c r="H9" s="255">
         <f ca="1">E14</f>
-        <v>4.1606113490454577</v>
+        <v>4.0756198168055668</v>
       </c>
       <c r="I9" s="183"/>
-      <c r="J9" s="211">
+      <c r="J9" s="255">
         <f ca="1">E15</f>
-        <v>4.118221979567946</v>
+        <v>4.0340179932725686</v>
       </c>
       <c r="K9" s="183"/>
-      <c r="L9" s="248" t="s">
+      <c r="L9" s="223" t="s">
         <v>246</v>
       </c>
       <c r="M9" s="183"/>
@@ -10525,17 +10547,17 @@
     </row>
     <row r="10" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6"/>
-      <c r="B10" s="206"/>
+      <c r="B10" s="203"/>
       <c r="C10" s="186"/>
-      <c r="D10" s="229"/>
+      <c r="D10" s="242"/>
       <c r="E10" s="183"/>
-      <c r="F10" s="230"/>
+      <c r="F10" s="243"/>
       <c r="G10" s="186"/>
-      <c r="H10" s="206"/>
+      <c r="H10" s="203"/>
       <c r="I10" s="186"/>
-      <c r="J10" s="206"/>
+      <c r="J10" s="203"/>
       <c r="K10" s="186"/>
-      <c r="L10" s="206"/>
+      <c r="L10" s="203"/>
       <c r="M10" s="186"/>
       <c r="N10" s="6"/>
     </row>
@@ -10557,7 +10579,7 @@
     </row>
     <row r="12" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6"/>
-      <c r="B12" s="199" t="s">
+      <c r="B12" s="189" t="s">
         <v>247</v>
       </c>
       <c r="C12" s="183"/>
@@ -10575,7 +10597,7 @@
     </row>
     <row r="13" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6"/>
-      <c r="B13" s="213" t="s">
+      <c r="B13" s="218" t="s">
         <v>248</v>
       </c>
       <c r="C13" s="183"/>
@@ -10583,7 +10605,7 @@
       <c r="E13" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="F13" s="213" t="s">
+      <c r="F13" s="218" t="s">
         <v>250</v>
       </c>
       <c r="G13" s="183"/>
@@ -10597,48 +10619,48 @@
     </row>
     <row r="14" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
-      <c r="B14" s="193" t="s">
+      <c r="B14" s="192" t="s">
         <v>243</v>
       </c>
-      <c r="C14" s="190"/>
-      <c r="D14" s="190"/>
+      <c r="C14" s="191"/>
+      <c r="D14" s="191"/>
       <c r="E14" s="71">
         <f ca="1">IFERROR(SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!F3:F24*('Input Data'!AD3:AD24-TODAY())/365.25)/SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!F3:F24),0)</f>
-        <v>4.1606113490454577</v>
-      </c>
-      <c r="F14" s="208" t="s">
+        <v>4.0756198168055668</v>
+      </c>
+      <c r="F14" s="202" t="s">
         <v>251</v>
       </c>
-      <c r="G14" s="190"/>
-      <c r="H14" s="190"/>
-      <c r="I14" s="190"/>
-      <c r="J14" s="190"/>
-      <c r="K14" s="190"/>
-      <c r="L14" s="190"/>
-      <c r="M14" s="190"/>
+      <c r="G14" s="191"/>
+      <c r="H14" s="191"/>
+      <c r="I14" s="191"/>
+      <c r="J14" s="191"/>
+      <c r="K14" s="191"/>
+      <c r="L14" s="191"/>
+      <c r="M14" s="191"/>
       <c r="N14" s="6"/>
     </row>
     <row r="15" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6"/>
-      <c r="B15" s="258" t="s">
+      <c r="B15" s="231" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="190"/>
-      <c r="D15" s="190"/>
+      <c r="C15" s="191"/>
+      <c r="D15" s="191"/>
       <c r="E15" s="73">
         <f ca="1">IFERROR(SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!AE3:AE24*'Input Data'!F3:F24*('Input Data'!AD3:AD24-TODAY())/365.25)/SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!AE3:AE24*'Input Data'!F3:F24),0)</f>
-        <v>4.118221979567946</v>
-      </c>
-      <c r="F15" s="234" t="s">
+        <v>4.0340179932725686</v>
+      </c>
+      <c r="F15" s="240" t="s">
         <v>252</v>
       </c>
-      <c r="G15" s="190"/>
-      <c r="H15" s="190"/>
-      <c r="I15" s="190"/>
-      <c r="J15" s="190"/>
-      <c r="K15" s="190"/>
-      <c r="L15" s="190"/>
-      <c r="M15" s="190"/>
+      <c r="G15" s="191"/>
+      <c r="H15" s="191"/>
+      <c r="I15" s="191"/>
+      <c r="J15" s="191"/>
+      <c r="K15" s="191"/>
+      <c r="L15" s="191"/>
+      <c r="M15" s="191"/>
       <c r="N15" s="6"/>
     </row>
     <row r="16" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10659,7 +10681,7 @@
     </row>
     <row r="17" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6"/>
-      <c r="B17" s="199" t="s">
+      <c r="B17" s="189" t="s">
         <v>253</v>
       </c>
       <c r="C17" s="183"/>
@@ -10677,11 +10699,11 @@
     </row>
     <row r="18" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6"/>
-      <c r="B18" s="213" t="s">
+      <c r="B18" s="218" t="s">
         <v>254</v>
       </c>
       <c r="C18" s="183"/>
-      <c r="D18" s="213" t="s">
+      <c r="D18" s="218" t="s">
         <v>255</v>
       </c>
       <c r="E18" s="183"/>
@@ -10697,7 +10719,7 @@
       <c r="I18" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="J18" s="213" t="s">
+      <c r="J18" s="218" t="s">
         <v>259</v>
       </c>
       <c r="K18" s="183"/>
@@ -10707,15 +10729,15 @@
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6"/>
-      <c r="B19" s="245" t="s">
+      <c r="B19" s="238" t="s">
         <v>260</v>
       </c>
       <c r="C19" s="183"/>
-      <c r="D19" s="231">
+      <c r="D19" s="244">
         <f>SUMPRODUCT(('Input Data'!AD3:AD24&lt;&gt;"")*('Input Data'!AD3:AD24&lt;=DATE(2026,12,31))*'Input Data'!AE3:AE24*'Input Data'!F3:F24)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="190"/>
+      <c r="E19" s="191"/>
       <c r="F19" s="74">
         <f ca="1">IFERROR(D19/(SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!AE3:AE24*'Input Data'!F3:F24)),0)</f>
         <v>0</v>
@@ -10732,29 +10754,29 @@
         <f>SUMPRODUCT(('Input Data'!AD3:AD24&lt;&gt;"")*('Input Data'!AD3:AD24&lt;=DATE(2026,12,31))*1)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="222" t="str">
+      <c r="J19" s="249" t="str">
         <f>IFERROR(MID(IF(('Input Data'!AD3&lt;&gt;"")*('Input Data'!AD3&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF3&amp;" ("&amp;'Input Data'!C3&amp;")","")&amp;IF(('Input Data'!AD4&lt;&gt;"")*('Input Data'!AD4&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF4&amp;" ("&amp;'Input Data'!C4&amp;")","")&amp;IF(('Input Data'!AD5&lt;&gt;"")*('Input Data'!AD5&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF5&amp;" ("&amp;'Input Data'!C5&amp;")","")&amp;IF(('Input Data'!AD6&lt;&gt;"")*('Input Data'!AD6&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF6&amp;" ("&amp;'Input Data'!C6&amp;")","")&amp;IF(('Input Data'!AD7&lt;&gt;"")*('Input Data'!AD7&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF7&amp;" ("&amp;'Input Data'!C7&amp;")","")&amp;IF(('Input Data'!AD8&lt;&gt;"")*('Input Data'!AD8&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF8&amp;" ("&amp;'Input Data'!C8&amp;")","")&amp;IF(('Input Data'!AD9&lt;&gt;"")*('Input Data'!AD9&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF9&amp;" ("&amp;'Input Data'!C9&amp;")","")&amp;IF(('Input Data'!AD10&lt;&gt;"")*('Input Data'!AD10&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF10&amp;" ("&amp;'Input Data'!C10&amp;")","")&amp;IF(('Input Data'!AD11&lt;&gt;"")*('Input Data'!AD11&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF11&amp;" ("&amp;'Input Data'!C11&amp;")","")&amp;IF(('Input Data'!AD12&lt;&gt;"")*('Input Data'!AD12&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF12&amp;" ("&amp;'Input Data'!C12&amp;")","")&amp;IF(('Input Data'!AD13&lt;&gt;"")*('Input Data'!AD13&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF13&amp;" ("&amp;'Input Data'!C13&amp;")","")&amp;IF(('Input Data'!AD14&lt;&gt;"")*('Input Data'!AD14&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF14&amp;" ("&amp;'Input Data'!C14&amp;")","")&amp;IF(('Input Data'!AD15&lt;&gt;"")*('Input Data'!AD15&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF15&amp;" ("&amp;'Input Data'!C15&amp;")","")&amp;IF(('Input Data'!AD16&lt;&gt;"")*('Input Data'!AD16&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF16&amp;" ("&amp;'Input Data'!C16&amp;")","")&amp;IF(('Input Data'!AD17&lt;&gt;"")*('Input Data'!AD17&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF17&amp;" ("&amp;'Input Data'!C17&amp;")","")&amp;IF(('Input Data'!AD18&lt;&gt;"")*('Input Data'!AD18&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF18&amp;" ("&amp;'Input Data'!C18&amp;")","")&amp;IF(('Input Data'!AD19&lt;&gt;"")*('Input Data'!AD19&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF19&amp;" ("&amp;'Input Data'!C19&amp;")","")&amp;IF(('Input Data'!AD20&lt;&gt;"")*('Input Data'!AD20&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF20&amp;" ("&amp;'Input Data'!C20&amp;")","")&amp;IF(('Input Data'!AD21&lt;&gt;"")*('Input Data'!AD21&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF21&amp;" ("&amp;'Input Data'!C21&amp;")","")&amp;IF(('Input Data'!AD22&lt;&gt;"")*('Input Data'!AD22&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF22&amp;" ("&amp;'Input Data'!C22&amp;")","")&amp;IF(('Input Data'!AD23&lt;&gt;"")*('Input Data'!AD23&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF23&amp;" ("&amp;'Input Data'!C23&amp;")","")&amp;IF(('Input Data'!AD24&lt;&gt;"")*('Input Data'!AD24&lt;=DATE(2026,12,31)),", "&amp;'Input Data'!AF24&amp;" ("&amp;'Input Data'!C24&amp;")",""),3,999),"—")</f>
         <v/>
       </c>
-      <c r="K19" s="190"/>
-      <c r="L19" s="190"/>
-      <c r="M19" s="190"/>
+      <c r="K19" s="191"/>
+      <c r="L19" s="191"/>
+      <c r="M19" s="191"/>
       <c r="N19" s="6"/>
     </row>
     <row r="20" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6"/>
-      <c r="B20" s="209" t="s">
+      <c r="B20" s="214" t="s">
         <v>261</v>
       </c>
       <c r="C20" s="183"/>
-      <c r="D20" s="202">
+      <c r="D20" s="257">
         <f t="array" aca="1" ref="D20" ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*(YEAR('Input Data'!AD3:AD24)=2027)*('Input Data'!AE3:AE24&gt;0)*'Input Data'!AE3:AE24*'Input Data'!F3:F24)</f>
         <v>658925.80700000003</v>
       </c>
-      <c r="E20" s="190"/>
+      <c r="E20" s="191"/>
       <c r="F20" s="77">
         <f ca="1">IFERROR(D20/(SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!AE3:AE24*'Input Data'!F3:F24)),0)</f>
-        <v>9.1529626307538831E-2</v>
+        <v>9.137122847977365E-2</v>
       </c>
       <c r="G20" s="78">
         <f ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*(YEAR('Input Data'!AD3:AD24)=2027)*('Input Data'!AE3:AE24&gt;0)*'Input Data'!F3:F24)</f>
@@ -10762,19 +10784,19 @@
       </c>
       <c r="H20" s="77">
         <f ca="1">IFERROR(G20/(SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!F3:F24)),0)</f>
-        <v>8.5307742337965731E-2</v>
+        <v>8.5172080202494074E-2</v>
       </c>
       <c r="I20" s="79">
         <f ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*(YEAR('Input Data'!AD3:AD24)=2027)*('Input Data'!AE3:AE24&gt;0)*1)</f>
         <v>2</v>
       </c>
-      <c r="J20" s="240" t="str">
+      <c r="J20" s="247" t="str">
         <f ca="1">IFERROR(MID(IF(('Input Data'!AD3&gt;TODAY())*(YEAR('Input Data'!AD3)=2027)*('Input Data'!AE3&gt;0),", "&amp;'Input Data'!AF3&amp;" ("&amp;'Input Data'!C3&amp;")","")&amp;IF(('Input Data'!AD4&gt;TODAY())*(YEAR('Input Data'!AD4)=2027)*('Input Data'!AE4&gt;0),", "&amp;'Input Data'!AF4&amp;" ("&amp;'Input Data'!C4&amp;")","")&amp;IF(('Input Data'!AD5&gt;TODAY())*(YEAR('Input Data'!AD5)=2027)*('Input Data'!AE5&gt;0),", "&amp;'Input Data'!AF5&amp;" ("&amp;'Input Data'!C5&amp;")","")&amp;IF(('Input Data'!AD6&gt;TODAY())*(YEAR('Input Data'!AD6)=2027)*('Input Data'!AE6&gt;0),", "&amp;'Input Data'!AF6&amp;" ("&amp;'Input Data'!C6&amp;")","")&amp;IF(('Input Data'!AD7&gt;TODAY())*(YEAR('Input Data'!AD7)=2027)*('Input Data'!AE7&gt;0),", "&amp;'Input Data'!AF7&amp;" ("&amp;'Input Data'!C7&amp;")","")&amp;IF(('Input Data'!AD8&gt;TODAY())*(YEAR('Input Data'!AD8)=2027)*('Input Data'!AE8&gt;0),", "&amp;'Input Data'!AF8&amp;" ("&amp;'Input Data'!C8&amp;")","")&amp;IF(('Input Data'!AD9&gt;TODAY())*(YEAR('Input Data'!AD9)=2027)*('Input Data'!AE9&gt;0),", "&amp;'Input Data'!AF9&amp;" ("&amp;'Input Data'!C9&amp;")","")&amp;IF(('Input Data'!AD10&gt;TODAY())*(YEAR('Input Data'!AD10)=2027)*('Input Data'!AE10&gt;0),", "&amp;'Input Data'!AF10&amp;" ("&amp;'Input Data'!C10&amp;")","")&amp;IF(('Input Data'!AD11&gt;TODAY())*(YEAR('Input Data'!AD11)=2027)*('Input Data'!AE11&gt;0),", "&amp;'Input Data'!AF11&amp;" ("&amp;'Input Data'!C11&amp;")","")&amp;IF(('Input Data'!AD12&gt;TODAY())*(YEAR('Input Data'!AD12)=2027)*('Input Data'!AE12&gt;0),", "&amp;'Input Data'!AF12&amp;" ("&amp;'Input Data'!C12&amp;")","")&amp;IF(('Input Data'!AD13&gt;TODAY())*(YEAR('Input Data'!AD13)=2027)*('Input Data'!AE13&gt;0),", "&amp;'Input Data'!AF13&amp;" ("&amp;'Input Data'!C13&amp;")","")&amp;IF(('Input Data'!AD14&gt;TODAY())*(YEAR('Input Data'!AD14)=2027)*('Input Data'!AE14&gt;0),", "&amp;'Input Data'!AF14&amp;" ("&amp;'Input Data'!C14&amp;")","")&amp;IF(('Input Data'!AD15&gt;TODAY())*(YEAR('Input Data'!AD15)=2027)*('Input Data'!AE15&gt;0),", "&amp;'Input Data'!AF15&amp;" ("&amp;'Input Data'!C15&amp;")","")&amp;IF(('Input Data'!AD16&gt;TODAY())*(YEAR('Input Data'!AD16)=2027)*('Input Data'!AE16&gt;0),", "&amp;'Input Data'!AF16&amp;" ("&amp;'Input Data'!C16&amp;")","")&amp;IF(('Input Data'!AD17&gt;TODAY())*(YEAR('Input Data'!AD17)=2027)*('Input Data'!AE17&gt;0),", "&amp;'Input Data'!AF17&amp;" ("&amp;'Input Data'!C17&amp;")","")&amp;IF(('Input Data'!AD18&gt;TODAY())*(YEAR('Input Data'!AD18)=2027)*('Input Data'!AE18&gt;0),", "&amp;'Input Data'!AF18&amp;" ("&amp;'Input Data'!C18&amp;")","")&amp;IF(('Input Data'!AD19&gt;TODAY())*(YEAR('Input Data'!AD19)=2027)*('Input Data'!AE19&gt;0),", "&amp;'Input Data'!AF19&amp;" ("&amp;'Input Data'!C19&amp;")","")&amp;IF(('Input Data'!AD20&gt;TODAY())*(YEAR('Input Data'!AD20)=2027)*('Input Data'!AE20&gt;0),", "&amp;'Input Data'!AF20&amp;" ("&amp;'Input Data'!C20&amp;")","")&amp;IF(('Input Data'!AD21&gt;TODAY())*(YEAR('Input Data'!AD21)=2027)*('Input Data'!AE21&gt;0),", "&amp;'Input Data'!AF21&amp;" ("&amp;'Input Data'!C21&amp;")","")&amp;IF(('Input Data'!AD22&gt;TODAY())*(YEAR('Input Data'!AD22)=2027)*('Input Data'!AE22&gt;0),", "&amp;'Input Data'!AF22&amp;" ("&amp;'Input Data'!C22&amp;")","")&amp;IF(('Input Data'!AD23&gt;TODAY())*(YEAR('Input Data'!AD23)=2027)*('Input Data'!AE23&gt;0),", "&amp;'Input Data'!AF23&amp;" ("&amp;'Input Data'!C23&amp;")","")&amp;IF(('Input Data'!AD24&gt;TODAY())*(YEAR('Input Data'!AD24)=2027)*('Input Data'!AE24&gt;0),", "&amp;'Input Data'!AF24&amp;" ("&amp;'Input Data'!C24&amp;")",""),3,999),"—")</f>
         <v>Keeping Company (6.03), Pitt &amp; Sherry (9.01)</v>
       </c>
-      <c r="K20" s="190"/>
-      <c r="L20" s="190"/>
-      <c r="M20" s="190"/>
+      <c r="K20" s="191"/>
+      <c r="L20" s="191"/>
+      <c r="M20" s="191"/>
       <c r="N20" s="6"/>
     </row>
     <row r="21" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -10783,14 +10805,14 @@
         <v>262</v>
       </c>
       <c r="C21" s="183"/>
-      <c r="D21" s="255">
+      <c r="D21" s="227">
         <f ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*(YEAR('Input Data'!AD3:AD24)=2028)*('Input Data'!AE3:AE24&gt;0)*'Input Data'!AE3:AE24*'Input Data'!F3:F24)</f>
         <v>824159.84700000007</v>
       </c>
-      <c r="E21" s="190"/>
+      <c r="E21" s="191"/>
       <c r="F21" s="81">
         <f ca="1">IFERROR(D21/(SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!AE3:AE24*'Input Data'!F3:F24)),0)</f>
-        <v>0.11448184607768501</v>
+        <v>0.1142837279768165</v>
       </c>
       <c r="G21" s="82">
         <f ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*(YEAR('Input Data'!AD3:AD24)=2028)*('Input Data'!AE3:AE24&gt;0)*'Input Data'!F3:F24)</f>
@@ -10798,24 +10820,24 @@
       </c>
       <c r="H21" s="81">
         <f ca="1">IFERROR(G21/(SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!F3:F24)),0)</f>
-        <v>0.10544339585075459</v>
+        <v>0.10527571263865146</v>
       </c>
       <c r="I21" s="83">
         <f ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*(YEAR('Input Data'!AD3:AD24)=2028)*('Input Data'!AE3:AE24&gt;0)*1)</f>
         <v>2</v>
       </c>
-      <c r="J21" s="244" t="str">
+      <c r="J21" s="233" t="str">
         <f ca="1">IFERROR(MID(IF(('Input Data'!AD3&gt;TODAY())*(YEAR('Input Data'!AD3)=2028)*('Input Data'!AE3&gt;0),", "&amp;'Input Data'!AF3&amp;" ("&amp;'Input Data'!C3&amp;")","")&amp;IF(('Input Data'!AD4&gt;TODAY())*(YEAR('Input Data'!AD4)=2028)*('Input Data'!AE4&gt;0),", "&amp;'Input Data'!AF4&amp;" ("&amp;'Input Data'!C4&amp;")","")&amp;IF(('Input Data'!AD5&gt;TODAY())*(YEAR('Input Data'!AD5)=2028)*('Input Data'!AE5&gt;0),", "&amp;'Input Data'!AF5&amp;" ("&amp;'Input Data'!C5&amp;")","")&amp;IF(('Input Data'!AD6&gt;TODAY())*(YEAR('Input Data'!AD6)=2028)*('Input Data'!AE6&gt;0),", "&amp;'Input Data'!AF6&amp;" ("&amp;'Input Data'!C6&amp;")","")&amp;IF(('Input Data'!AD7&gt;TODAY())*(YEAR('Input Data'!AD7)=2028)*('Input Data'!AE7&gt;0),", "&amp;'Input Data'!AF7&amp;" ("&amp;'Input Data'!C7&amp;")","")&amp;IF(('Input Data'!AD8&gt;TODAY())*(YEAR('Input Data'!AD8)=2028)*('Input Data'!AE8&gt;0),", "&amp;'Input Data'!AF8&amp;" ("&amp;'Input Data'!C8&amp;")","")&amp;IF(('Input Data'!AD9&gt;TODAY())*(YEAR('Input Data'!AD9)=2028)*('Input Data'!AE9&gt;0),", "&amp;'Input Data'!AF9&amp;" ("&amp;'Input Data'!C9&amp;")","")&amp;IF(('Input Data'!AD10&gt;TODAY())*(YEAR('Input Data'!AD10)=2028)*('Input Data'!AE10&gt;0),", "&amp;'Input Data'!AF10&amp;" ("&amp;'Input Data'!C10&amp;")","")&amp;IF(('Input Data'!AD11&gt;TODAY())*(YEAR('Input Data'!AD11)=2028)*('Input Data'!AE11&gt;0),", "&amp;'Input Data'!AF11&amp;" ("&amp;'Input Data'!C11&amp;")","")&amp;IF(('Input Data'!AD12&gt;TODAY())*(YEAR('Input Data'!AD12)=2028)*('Input Data'!AE12&gt;0),", "&amp;'Input Data'!AF12&amp;" ("&amp;'Input Data'!C12&amp;")","")&amp;IF(('Input Data'!AD13&gt;TODAY())*(YEAR('Input Data'!AD13)=2028)*('Input Data'!AE13&gt;0),", "&amp;'Input Data'!AF13&amp;" ("&amp;'Input Data'!C13&amp;")","")&amp;IF(('Input Data'!AD14&gt;TODAY())*(YEAR('Input Data'!AD14)=2028)*('Input Data'!AE14&gt;0),", "&amp;'Input Data'!AF14&amp;" ("&amp;'Input Data'!C14&amp;")","")&amp;IF(('Input Data'!AD15&gt;TODAY())*(YEAR('Input Data'!AD15)=2028)*('Input Data'!AE15&gt;0),", "&amp;'Input Data'!AF15&amp;" ("&amp;'Input Data'!C15&amp;")","")&amp;IF(('Input Data'!AD16&gt;TODAY())*(YEAR('Input Data'!AD16)=2028)*('Input Data'!AE16&gt;0),", "&amp;'Input Data'!AF16&amp;" ("&amp;'Input Data'!C16&amp;")","")&amp;IF(('Input Data'!AD17&gt;TODAY())*(YEAR('Input Data'!AD17)=2028)*('Input Data'!AE17&gt;0),", "&amp;'Input Data'!AF17&amp;" ("&amp;'Input Data'!C17&amp;")","")&amp;IF(('Input Data'!AD18&gt;TODAY())*(YEAR('Input Data'!AD18)=2028)*('Input Data'!AE18&gt;0),", "&amp;'Input Data'!AF18&amp;" ("&amp;'Input Data'!C18&amp;")","")&amp;IF(('Input Data'!AD19&gt;TODAY())*(YEAR('Input Data'!AD19)=2028)*('Input Data'!AE19&gt;0),", "&amp;'Input Data'!AF19&amp;" ("&amp;'Input Data'!C19&amp;")","")&amp;IF(('Input Data'!AD20&gt;TODAY())*(YEAR('Input Data'!AD20)=2028)*('Input Data'!AE20&gt;0),", "&amp;'Input Data'!AF20&amp;" ("&amp;'Input Data'!C20&amp;")","")&amp;IF(('Input Data'!AD21&gt;TODAY())*(YEAR('Input Data'!AD21)=2028)*('Input Data'!AE21&gt;0),", "&amp;'Input Data'!AF21&amp;" ("&amp;'Input Data'!C21&amp;")","")&amp;IF(('Input Data'!AD22&gt;TODAY())*(YEAR('Input Data'!AD22)=2028)*('Input Data'!AE22&gt;0),", "&amp;'Input Data'!AF22&amp;" ("&amp;'Input Data'!C22&amp;")","")&amp;IF(('Input Data'!AD23&gt;TODAY())*(YEAR('Input Data'!AD23)=2028)*('Input Data'!AE23&gt;0),", "&amp;'Input Data'!AF23&amp;" ("&amp;'Input Data'!C23&amp;")","")&amp;IF(('Input Data'!AD24&gt;TODAY())*(YEAR('Input Data'!AD24)=2028)*('Input Data'!AE24&gt;0),", "&amp;'Input Data'!AF24&amp;" ("&amp;'Input Data'!C24&amp;")",""),3,999),"—")</f>
         <v>Sydney Smiletree (3.01), Vanderlande Industries (8.01)</v>
       </c>
-      <c r="K21" s="190"/>
-      <c r="L21" s="190"/>
-      <c r="M21" s="190"/>
+      <c r="K21" s="191"/>
+      <c r="L21" s="191"/>
+      <c r="M21" s="191"/>
       <c r="N21" s="6"/>
     </row>
     <row r="22" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6"/>
-      <c r="B22" s="209" t="s">
+      <c r="B22" s="214" t="s">
         <v>263</v>
       </c>
       <c r="C22" s="183"/>
@@ -10823,10 +10845,10 @@
         <f ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*(YEAR('Input Data'!AD3:AD24)=2029)*('Input Data'!AE3:AE24&gt;0)*'Input Data'!AE3:AE24*'Input Data'!F3:F24)</f>
         <v>1897968.6250000002</v>
       </c>
-      <c r="E22" s="190"/>
+      <c r="E22" s="191"/>
       <c r="F22" s="84">
         <f ca="1">IFERROR(D22/(SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!AE3:AE24*'Input Data'!F3:F24)),0)</f>
-        <v>0.26364175927576522</v>
+        <v>0.26318551047783872</v>
       </c>
       <c r="G22" s="85">
         <f ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*(YEAR('Input Data'!AD3:AD24)=2029)*('Input Data'!AE3:AE24&gt;0)*'Input Data'!F3:F24)</f>
@@ -10834,7 +10856,7 @@
       </c>
       <c r="H22" s="84">
         <f ca="1">IFERROR(G22/(SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!F3:F24)),0)</f>
-        <v>0.25532592681081506</v>
+        <v>0.25491989027153816</v>
       </c>
       <c r="I22" s="86">
         <f ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*(YEAR('Input Data'!AD3:AD24)=2029)*('Input Data'!AE3:AE24&gt;0)*1)</f>
@@ -10844,14 +10866,14 @@
         <f ca="1">IFERROR(MID(IF(('Input Data'!AD3&gt;TODAY())*(YEAR('Input Data'!AD3)=2029)*('Input Data'!AE3&gt;0),", "&amp;'Input Data'!AF3&amp;" ("&amp;'Input Data'!C3&amp;")","")&amp;IF(('Input Data'!AD4&gt;TODAY())*(YEAR('Input Data'!AD4)=2029)*('Input Data'!AE4&gt;0),", "&amp;'Input Data'!AF4&amp;" ("&amp;'Input Data'!C4&amp;")","")&amp;IF(('Input Data'!AD5&gt;TODAY())*(YEAR('Input Data'!AD5)=2029)*('Input Data'!AE5&gt;0),", "&amp;'Input Data'!AF5&amp;" ("&amp;'Input Data'!C5&amp;")","")&amp;IF(('Input Data'!AD6&gt;TODAY())*(YEAR('Input Data'!AD6)=2029)*('Input Data'!AE6&gt;0),", "&amp;'Input Data'!AF6&amp;" ("&amp;'Input Data'!C6&amp;")","")&amp;IF(('Input Data'!AD7&gt;TODAY())*(YEAR('Input Data'!AD7)=2029)*('Input Data'!AE7&gt;0),", "&amp;'Input Data'!AF7&amp;" ("&amp;'Input Data'!C7&amp;")","")&amp;IF(('Input Data'!AD8&gt;TODAY())*(YEAR('Input Data'!AD8)=2029)*('Input Data'!AE8&gt;0),", "&amp;'Input Data'!AF8&amp;" ("&amp;'Input Data'!C8&amp;")","")&amp;IF(('Input Data'!AD9&gt;TODAY())*(YEAR('Input Data'!AD9)=2029)*('Input Data'!AE9&gt;0),", "&amp;'Input Data'!AF9&amp;" ("&amp;'Input Data'!C9&amp;")","")&amp;IF(('Input Data'!AD10&gt;TODAY())*(YEAR('Input Data'!AD10)=2029)*('Input Data'!AE10&gt;0),", "&amp;'Input Data'!AF10&amp;" ("&amp;'Input Data'!C10&amp;")","")&amp;IF(('Input Data'!AD11&gt;TODAY())*(YEAR('Input Data'!AD11)=2029)*('Input Data'!AE11&gt;0),", "&amp;'Input Data'!AF11&amp;" ("&amp;'Input Data'!C11&amp;")","")&amp;IF(('Input Data'!AD12&gt;TODAY())*(YEAR('Input Data'!AD12)=2029)*('Input Data'!AE12&gt;0),", "&amp;'Input Data'!AF12&amp;" ("&amp;'Input Data'!C12&amp;")","")&amp;IF(('Input Data'!AD13&gt;TODAY())*(YEAR('Input Data'!AD13)=2029)*('Input Data'!AE13&gt;0),", "&amp;'Input Data'!AF13&amp;" ("&amp;'Input Data'!C13&amp;")","")&amp;IF(('Input Data'!AD14&gt;TODAY())*(YEAR('Input Data'!AD14)=2029)*('Input Data'!AE14&gt;0),", "&amp;'Input Data'!AF14&amp;" ("&amp;'Input Data'!C14&amp;")","")&amp;IF(('Input Data'!AD15&gt;TODAY())*(YEAR('Input Data'!AD15)=2029)*('Input Data'!AE15&gt;0),", "&amp;'Input Data'!AF15&amp;" ("&amp;'Input Data'!C15&amp;")","")&amp;IF(('Input Data'!AD16&gt;TODAY())*(YEAR('Input Data'!AD16)=2029)*('Input Data'!AE16&gt;0),", "&amp;'Input Data'!AF16&amp;" ("&amp;'Input Data'!C16&amp;")","")&amp;IF(('Input Data'!AD17&gt;TODAY())*(YEAR('Input Data'!AD17)=2029)*('Input Data'!AE17&gt;0),", "&amp;'Input Data'!AF17&amp;" ("&amp;'Input Data'!C17&amp;")","")&amp;IF(('Input Data'!AD18&gt;TODAY())*(YEAR('Input Data'!AD18)=2029)*('Input Data'!AE18&gt;0),", "&amp;'Input Data'!AF18&amp;" ("&amp;'Input Data'!C18&amp;")","")&amp;IF(('Input Data'!AD19&gt;TODAY())*(YEAR('Input Data'!AD19)=2029)*('Input Data'!AE19&gt;0),", "&amp;'Input Data'!AF19&amp;" ("&amp;'Input Data'!C19&amp;")","")&amp;IF(('Input Data'!AD20&gt;TODAY())*(YEAR('Input Data'!AD20)=2029)*('Input Data'!AE20&gt;0),", "&amp;'Input Data'!AF20&amp;" ("&amp;'Input Data'!C20&amp;")","")&amp;IF(('Input Data'!AD21&gt;TODAY())*(YEAR('Input Data'!AD21)=2029)*('Input Data'!AE21&gt;0),", "&amp;'Input Data'!AF21&amp;" ("&amp;'Input Data'!C21&amp;")","")&amp;IF(('Input Data'!AD22&gt;TODAY())*(YEAR('Input Data'!AD22)=2029)*('Input Data'!AE22&gt;0),", "&amp;'Input Data'!AF22&amp;" ("&amp;'Input Data'!C22&amp;")","")&amp;IF(('Input Data'!AD23&gt;TODAY())*(YEAR('Input Data'!AD23)=2029)*('Input Data'!AE23&gt;0),", "&amp;'Input Data'!AF23&amp;" ("&amp;'Input Data'!C23&amp;")","")&amp;IF(('Input Data'!AD24&gt;TODAY())*(YEAR('Input Data'!AD24)=2029)*('Input Data'!AE24&gt;0),", "&amp;'Input Data'!AF24&amp;" ("&amp;'Input Data'!C24&amp;")",""),3,999),"—")</f>
         <v>Asterx (MediRecords) (5.03), Auctionsplus (5.04), Sungrow (L6) (6.02), Sungrow (L7 Main) (7.01), Hulsbosch Design (12.01)</v>
       </c>
-      <c r="K22" s="190"/>
-      <c r="L22" s="190"/>
-      <c r="M22" s="190"/>
+      <c r="K22" s="191"/>
+      <c r="L22" s="191"/>
+      <c r="M22" s="191"/>
       <c r="N22" s="6"/>
     </row>
     <row r="23" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
-      <c r="B23" s="257" t="s">
+      <c r="B23" s="230" t="s">
         <v>264</v>
       </c>
       <c r="C23" s="183"/>
@@ -10859,10 +10881,10 @@
         <f ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*(YEAR('Input Data'!AD3:AD24)=2030)*('Input Data'!AE3:AE24&gt;0)*'Input Data'!AE3:AE24*'Input Data'!F3:F24)</f>
         <v>891940</v>
       </c>
-      <c r="E23" s="190"/>
+      <c r="E23" s="191"/>
       <c r="F23" s="84">
         <f ca="1">IFERROR(D23/(SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!AE3:AE24*'Input Data'!F3:F24)),0)</f>
-        <v>0.12389700634193886</v>
+        <v>0.12368259470864723</v>
       </c>
       <c r="G23" s="85">
         <f ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*(YEAR('Input Data'!AD3:AD24)=2030)*('Input Data'!AE3:AE24&gt;0)*'Input Data'!F3:F24)</f>
@@ -10870,7 +10892,7 @@
       </c>
       <c r="H23" s="84">
         <f ca="1">IFERROR(G23/(SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!F3:F24)),0)</f>
-        <v>0.11989806076534064</v>
+        <v>0.11970739076849679</v>
       </c>
       <c r="I23" s="86">
         <f ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*(YEAR('Input Data'!AD3:AD24)=2030)*('Input Data'!AE3:AE24&gt;0)*1)</f>
@@ -10880,33 +10902,33 @@
         <f ca="1">IFERROR(MID(IF(('Input Data'!AD3&gt;TODAY())*(YEAR('Input Data'!AD3)=2030)*('Input Data'!AE3&gt;0),", "&amp;'Input Data'!AF3&amp;" ("&amp;'Input Data'!C3&amp;")","")&amp;IF(('Input Data'!AD4&gt;TODAY())*(YEAR('Input Data'!AD4)=2030)*('Input Data'!AE4&gt;0),", "&amp;'Input Data'!AF4&amp;" ("&amp;'Input Data'!C4&amp;")","")&amp;IF(('Input Data'!AD5&gt;TODAY())*(YEAR('Input Data'!AD5)=2030)*('Input Data'!AE5&gt;0),", "&amp;'Input Data'!AF5&amp;" ("&amp;'Input Data'!C5&amp;")","")&amp;IF(('Input Data'!AD6&gt;TODAY())*(YEAR('Input Data'!AD6)=2030)*('Input Data'!AE6&gt;0),", "&amp;'Input Data'!AF6&amp;" ("&amp;'Input Data'!C6&amp;")","")&amp;IF(('Input Data'!AD7&gt;TODAY())*(YEAR('Input Data'!AD7)=2030)*('Input Data'!AE7&gt;0),", "&amp;'Input Data'!AF7&amp;" ("&amp;'Input Data'!C7&amp;")","")&amp;IF(('Input Data'!AD8&gt;TODAY())*(YEAR('Input Data'!AD8)=2030)*('Input Data'!AE8&gt;0),", "&amp;'Input Data'!AF8&amp;" ("&amp;'Input Data'!C8&amp;")","")&amp;IF(('Input Data'!AD9&gt;TODAY())*(YEAR('Input Data'!AD9)=2030)*('Input Data'!AE9&gt;0),", "&amp;'Input Data'!AF9&amp;" ("&amp;'Input Data'!C9&amp;")","")&amp;IF(('Input Data'!AD10&gt;TODAY())*(YEAR('Input Data'!AD10)=2030)*('Input Data'!AE10&gt;0),", "&amp;'Input Data'!AF10&amp;" ("&amp;'Input Data'!C10&amp;")","")&amp;IF(('Input Data'!AD11&gt;TODAY())*(YEAR('Input Data'!AD11)=2030)*('Input Data'!AE11&gt;0),", "&amp;'Input Data'!AF11&amp;" ("&amp;'Input Data'!C11&amp;")","")&amp;IF(('Input Data'!AD12&gt;TODAY())*(YEAR('Input Data'!AD12)=2030)*('Input Data'!AE12&gt;0),", "&amp;'Input Data'!AF12&amp;" ("&amp;'Input Data'!C12&amp;")","")&amp;IF(('Input Data'!AD13&gt;TODAY())*(YEAR('Input Data'!AD13)=2030)*('Input Data'!AE13&gt;0),", "&amp;'Input Data'!AF13&amp;" ("&amp;'Input Data'!C13&amp;")","")&amp;IF(('Input Data'!AD14&gt;TODAY())*(YEAR('Input Data'!AD14)=2030)*('Input Data'!AE14&gt;0),", "&amp;'Input Data'!AF14&amp;" ("&amp;'Input Data'!C14&amp;")","")&amp;IF(('Input Data'!AD15&gt;TODAY())*(YEAR('Input Data'!AD15)=2030)*('Input Data'!AE15&gt;0),", "&amp;'Input Data'!AF15&amp;" ("&amp;'Input Data'!C15&amp;")","")&amp;IF(('Input Data'!AD16&gt;TODAY())*(YEAR('Input Data'!AD16)=2030)*('Input Data'!AE16&gt;0),", "&amp;'Input Data'!AF16&amp;" ("&amp;'Input Data'!C16&amp;")","")&amp;IF(('Input Data'!AD17&gt;TODAY())*(YEAR('Input Data'!AD17)=2030)*('Input Data'!AE17&gt;0),", "&amp;'Input Data'!AF17&amp;" ("&amp;'Input Data'!C17&amp;")","")&amp;IF(('Input Data'!AD18&gt;TODAY())*(YEAR('Input Data'!AD18)=2030)*('Input Data'!AE18&gt;0),", "&amp;'Input Data'!AF18&amp;" ("&amp;'Input Data'!C18&amp;")","")&amp;IF(('Input Data'!AD19&gt;TODAY())*(YEAR('Input Data'!AD19)=2030)*('Input Data'!AE19&gt;0),", "&amp;'Input Data'!AF19&amp;" ("&amp;'Input Data'!C19&amp;")","")&amp;IF(('Input Data'!AD20&gt;TODAY())*(YEAR('Input Data'!AD20)=2030)*('Input Data'!AE20&gt;0),", "&amp;'Input Data'!AF20&amp;" ("&amp;'Input Data'!C20&amp;")","")&amp;IF(('Input Data'!AD21&gt;TODAY())*(YEAR('Input Data'!AD21)=2030)*('Input Data'!AE21&gt;0),", "&amp;'Input Data'!AF21&amp;" ("&amp;'Input Data'!C21&amp;")","")&amp;IF(('Input Data'!AD22&gt;TODAY())*(YEAR('Input Data'!AD22)=2030)*('Input Data'!AE22&gt;0),", "&amp;'Input Data'!AF22&amp;" ("&amp;'Input Data'!C22&amp;")","")&amp;IF(('Input Data'!AD23&gt;TODAY())*(YEAR('Input Data'!AD23)=2030)*('Input Data'!AE23&gt;0),", "&amp;'Input Data'!AF23&amp;" ("&amp;'Input Data'!C23&amp;")","")&amp;IF(('Input Data'!AD24&gt;TODAY())*(YEAR('Input Data'!AD24)=2030)*('Input Data'!AE24&gt;0),", "&amp;'Input Data'!AF24&amp;" ("&amp;'Input Data'!C24&amp;")",""),3,999),"—")</f>
         <v>Can Too Foundation (8.03), Smile Partners Australia (9.02), AEI Insurance Group (12.02)</v>
       </c>
-      <c r="K23" s="190"/>
-      <c r="L23" s="190"/>
-      <c r="M23" s="190"/>
+      <c r="K23" s="191"/>
+      <c r="L23" s="191"/>
+      <c r="M23" s="191"/>
       <c r="N23" s="6"/>
     </row>
     <row r="24" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6"/>
-      <c r="B24" s="209" t="s">
+      <c r="B24" s="214" t="s">
         <v>265</v>
       </c>
       <c r="C24" s="183"/>
       <c r="D24" s="201">
         <f ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*(YEAR('Input Data'!AD3:AD24)&gt;=2031)*('Input Data'!AE3:AE24&gt;0)*'Input Data'!AE3:AE24*'Input Data'!F3:F24)</f>
-        <v>2926049.7199999997</v>
-      </c>
-      <c r="E24" s="190"/>
+        <v>2938529.7199999997</v>
+      </c>
+      <c r="E24" s="191"/>
       <c r="F24" s="84">
         <f ca="1">IFERROR(D24/(SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!AE3:AE24*'Input Data'!F3:F24)),0)</f>
-        <v>0.406449761997072</v>
+        <v>0.40747693835692378</v>
       </c>
       <c r="G24" s="85">
         <f ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*(YEAR('Input Data'!AD3:AD24)&gt;=2031)*('Input Data'!AE3:AE24&gt;0)*'Input Data'!F3:F24)</f>
-        <v>3269.9</v>
+        <v>3281.9</v>
       </c>
       <c r="H24" s="84">
         <f ca="1">IFERROR(G24/(SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!F3:F24)),0)</f>
-        <v>0.43402487423512387</v>
+        <v>0.4349249261188195</v>
       </c>
       <c r="I24" s="86">
         <f ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*(YEAR('Input Data'!AD3:AD24)&gt;=2031)*('Input Data'!AE3:AE24&gt;0)*1)</f>
@@ -10916,9 +10938,9 @@
         <f ca="1">IFERROR(MID(IF(('Input Data'!AD3&gt;TODAY())*(YEAR('Input Data'!AD3)&gt;=2031)*('Input Data'!AE3&gt;0),", "&amp;'Input Data'!AF3&amp;" ("&amp;'Input Data'!C3&amp;")","")&amp;IF(('Input Data'!AD4&gt;TODAY())*(YEAR('Input Data'!AD4)&gt;=2031)*('Input Data'!AE4&gt;0),", "&amp;'Input Data'!AF4&amp;" ("&amp;'Input Data'!C4&amp;")","")&amp;IF(('Input Data'!AD5&gt;TODAY())*(YEAR('Input Data'!AD5)&gt;=2031)*('Input Data'!AE5&gt;0),", "&amp;'Input Data'!AF5&amp;" ("&amp;'Input Data'!C5&amp;")","")&amp;IF(('Input Data'!AD6&gt;TODAY())*(YEAR('Input Data'!AD6)&gt;=2031)*('Input Data'!AE6&gt;0),", "&amp;'Input Data'!AF6&amp;" ("&amp;'Input Data'!C6&amp;")","")&amp;IF(('Input Data'!AD7&gt;TODAY())*(YEAR('Input Data'!AD7)&gt;=2031)*('Input Data'!AE7&gt;0),", "&amp;'Input Data'!AF7&amp;" ("&amp;'Input Data'!C7&amp;")","")&amp;IF(('Input Data'!AD8&gt;TODAY())*(YEAR('Input Data'!AD8)&gt;=2031)*('Input Data'!AE8&gt;0),", "&amp;'Input Data'!AF8&amp;" ("&amp;'Input Data'!C8&amp;")","")&amp;IF(('Input Data'!AD9&gt;TODAY())*(YEAR('Input Data'!AD9)&gt;=2031)*('Input Data'!AE9&gt;0),", "&amp;'Input Data'!AF9&amp;" ("&amp;'Input Data'!C9&amp;")","")&amp;IF(('Input Data'!AD10&gt;TODAY())*(YEAR('Input Data'!AD10)&gt;=2031)*('Input Data'!AE10&gt;0),", "&amp;'Input Data'!AF10&amp;" ("&amp;'Input Data'!C10&amp;")","")&amp;IF(('Input Data'!AD11&gt;TODAY())*(YEAR('Input Data'!AD11)&gt;=2031)*('Input Data'!AE11&gt;0),", "&amp;'Input Data'!AF11&amp;" ("&amp;'Input Data'!C11&amp;")","")&amp;IF(('Input Data'!AD12&gt;TODAY())*(YEAR('Input Data'!AD12)&gt;=2031)*('Input Data'!AE12&gt;0),", "&amp;'Input Data'!AF12&amp;" ("&amp;'Input Data'!C12&amp;")","")&amp;IF(('Input Data'!AD13&gt;TODAY())*(YEAR('Input Data'!AD13)&gt;=2031)*('Input Data'!AE13&gt;0),", "&amp;'Input Data'!AF13&amp;" ("&amp;'Input Data'!C13&amp;")","")&amp;IF(('Input Data'!AD14&gt;TODAY())*(YEAR('Input Data'!AD14)&gt;=2031)*('Input Data'!AE14&gt;0),", "&amp;'Input Data'!AF14&amp;" ("&amp;'Input Data'!C14&amp;")","")&amp;IF(('Input Data'!AD15&gt;TODAY())*(YEAR('Input Data'!AD15)&gt;=2031)*('Input Data'!AE15&gt;0),", "&amp;'Input Data'!AF15&amp;" ("&amp;'Input Data'!C15&amp;")","")&amp;IF(('Input Data'!AD16&gt;TODAY())*(YEAR('Input Data'!AD16)&gt;=2031)*('Input Data'!AE16&gt;0),", "&amp;'Input Data'!AF16&amp;" ("&amp;'Input Data'!C16&amp;")","")&amp;IF(('Input Data'!AD17&gt;TODAY())*(YEAR('Input Data'!AD17)&gt;=2031)*('Input Data'!AE17&gt;0),", "&amp;'Input Data'!AF17&amp;" ("&amp;'Input Data'!C17&amp;")","")&amp;IF(('Input Data'!AD18&gt;TODAY())*(YEAR('Input Data'!AD18)&gt;=2031)*('Input Data'!AE18&gt;0),", "&amp;'Input Data'!AF18&amp;" ("&amp;'Input Data'!C18&amp;")","")&amp;IF(('Input Data'!AD19&gt;TODAY())*(YEAR('Input Data'!AD19)&gt;=2031)*('Input Data'!AE19&gt;0),", "&amp;'Input Data'!AF19&amp;" ("&amp;'Input Data'!C19&amp;")","")&amp;IF(('Input Data'!AD20&gt;TODAY())*(YEAR('Input Data'!AD20)&gt;=2031)*('Input Data'!AE20&gt;0),", "&amp;'Input Data'!AF20&amp;" ("&amp;'Input Data'!C20&amp;")","")&amp;IF(('Input Data'!AD21&gt;TODAY())*(YEAR('Input Data'!AD21)&gt;=2031)*('Input Data'!AE21&gt;0),", "&amp;'Input Data'!AF21&amp;" ("&amp;'Input Data'!C21&amp;")","")&amp;IF(('Input Data'!AD22&gt;TODAY())*(YEAR('Input Data'!AD22)&gt;=2031)*('Input Data'!AE22&gt;0),", "&amp;'Input Data'!AF22&amp;" ("&amp;'Input Data'!C22&amp;")","")&amp;IF(('Input Data'!AD23&gt;TODAY())*(YEAR('Input Data'!AD23)&gt;=2031)*('Input Data'!AE23&gt;0),", "&amp;'Input Data'!AF23&amp;" ("&amp;'Input Data'!C23&amp;")","")&amp;IF(('Input Data'!AD24&gt;TODAY())*(YEAR('Input Data'!AD24)&gt;=2031)*('Input Data'!AE24&gt;0),", "&amp;'Input Data'!AF24&amp;" ("&amp;'Input Data'!C24&amp;")",""),3,999),"—")</f>
         <v>Fitness First (L3) (3.02), Fitness First (L4) (4.01), Fitness First N. Sydney (5.01), Elekta (6.04), Caladas Constructions (6.01), Haskoning Australia (11.02)</v>
       </c>
-      <c r="K24" s="190"/>
-      <c r="L24" s="190"/>
-      <c r="M24" s="190"/>
+      <c r="K24" s="191"/>
+      <c r="L24" s="191"/>
+      <c r="M24" s="191"/>
       <c r="N24" s="6"/>
     </row>
     <row r="25" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10927,9 +10949,9 @@
         <v>266</v>
       </c>
       <c r="C25" s="183"/>
-      <c r="D25" s="249">
+      <c r="D25" s="224">
         <f ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!AE3:AE24*'Input Data'!F3:F24)</f>
-        <v>7199043.9990000008</v>
+        <v>7211523.9990000008</v>
       </c>
       <c r="E25" s="183"/>
       <c r="F25" s="87">
@@ -10937,7 +10959,7 @@
       </c>
       <c r="G25" s="62">
         <f ca="1">SUMPRODUCT(('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!F3:F24)</f>
-        <v>7533.9000000000005</v>
+        <v>7545.9000000000005</v>
       </c>
       <c r="H25" s="87">
         <v>1</v>
@@ -10967,7 +10989,7 @@
     </row>
     <row r="27" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6"/>
-      <c r="B27" s="199" t="s">
+      <c r="B27" s="189" t="s">
         <v>267</v>
       </c>
       <c r="C27" s="183"/>
@@ -10988,7 +11010,7 @@
       <c r="B28" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C28" s="213" t="s">
+      <c r="C28" s="218" t="s">
         <v>269</v>
       </c>
       <c r="D28" s="183"/>
@@ -11007,7 +11029,7 @@
       <c r="I28" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="J28" s="213" t="s">
+      <c r="J28" s="218" t="s">
         <v>275</v>
       </c>
       <c r="K28" s="183"/>
@@ -11021,11 +11043,11 @@
         <f>'Input Data'!C3</f>
         <v>3.01</v>
       </c>
-      <c r="C29" s="217" t="str">
+      <c r="C29" s="216" t="str">
         <f>'Input Data'!D3</f>
         <v>Sydney Smiletree Pty Ltd</v>
       </c>
-      <c r="D29" s="190"/>
+      <c r="D29" s="191"/>
       <c r="E29" s="51">
         <f>'Input Data'!F3</f>
         <v>107.7</v>
@@ -11046,13 +11068,13 @@
         <f>'Input Data'!Z3</f>
         <v>0.41289473684210526</v>
       </c>
-      <c r="J29" s="217" t="str">
+      <c r="J29" s="216" t="str">
         <f>IF('Input Data'!Y3&gt;0,"▲ Above Mkt",IF('Input Data'!Y3&lt;0,"▼ Below Mkt","≈ At Market"))</f>
         <v>▲ Above Mkt</v>
       </c>
-      <c r="K29" s="190"/>
-      <c r="L29" s="190"/>
-      <c r="M29" s="190"/>
+      <c r="K29" s="191"/>
+      <c r="L29" s="191"/>
+      <c r="M29" s="191"/>
       <c r="N29" s="6"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11061,11 +11083,11 @@
         <f>'Input Data'!C4</f>
         <v>3.02</v>
       </c>
-      <c r="C30" s="195" t="str">
+      <c r="C30" s="200" t="str">
         <f>'Input Data'!D4</f>
         <v>Fitness First Australia Pty Limited</v>
       </c>
-      <c r="D30" s="190"/>
+      <c r="D30" s="191"/>
       <c r="E30" s="34">
         <f>'Input Data'!F4</f>
         <v>795.5</v>
@@ -11086,13 +11108,13 @@
         <f>'Input Data'!Z4</f>
         <v>-1.6436781609195351E-2</v>
       </c>
-      <c r="J30" s="195" t="str">
+      <c r="J30" s="200" t="str">
         <f>IF('Input Data'!Y4&gt;0,"▲ Above Mkt",IF('Input Data'!Y4&lt;0,"▼ Below Mkt","≈ At Market"))</f>
         <v>▼ Below Mkt</v>
       </c>
-      <c r="K30" s="190"/>
-      <c r="L30" s="190"/>
-      <c r="M30" s="190"/>
+      <c r="K30" s="191"/>
+      <c r="L30" s="191"/>
+      <c r="M30" s="191"/>
       <c r="N30" s="6"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11101,11 +11123,11 @@
         <f>'Input Data'!C5</f>
         <v>4.01</v>
       </c>
-      <c r="C31" s="208" t="str">
+      <c r="C31" s="202" t="str">
         <f>'Input Data'!D5</f>
         <v>Fitness First Australia Pty Limited</v>
       </c>
-      <c r="D31" s="190"/>
+      <c r="D31" s="191"/>
       <c r="E31" s="22">
         <f>'Input Data'!F5</f>
         <v>1047</v>
@@ -11126,13 +11148,13 @@
         <f>'Input Data'!Z5</f>
         <v>-1.6436781609195351E-2</v>
       </c>
-      <c r="J31" s="208" t="str">
+      <c r="J31" s="202" t="str">
         <f>IF('Input Data'!Y5&gt;0,"▲ Above Mkt",IF('Input Data'!Y5&lt;0,"▼ Below Mkt","≈ At Market"))</f>
         <v>▼ Below Mkt</v>
       </c>
-      <c r="K31" s="190"/>
-      <c r="L31" s="190"/>
-      <c r="M31" s="190"/>
+      <c r="K31" s="191"/>
+      <c r="L31" s="191"/>
+      <c r="M31" s="191"/>
       <c r="N31" s="6"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11141,11 +11163,11 @@
         <f>'Input Data'!C6</f>
         <v>5.01</v>
       </c>
-      <c r="C32" s="195" t="str">
+      <c r="C32" s="200" t="str">
         <f>'Input Data'!D6</f>
         <v>Fitness First Australia Pty Limited</v>
       </c>
-      <c r="D32" s="190"/>
+      <c r="D32" s="191"/>
       <c r="E32" s="34">
         <f>'Input Data'!F6</f>
         <v>437.1</v>
@@ -11166,13 +11188,13 @@
         <f>'Input Data'!Z6</f>
         <v>-1.6436781609195351E-2</v>
       </c>
-      <c r="J32" s="195" t="str">
+      <c r="J32" s="200" t="str">
         <f>IF('Input Data'!Y6&gt;0,"▲ Above Mkt",IF('Input Data'!Y6&lt;0,"▼ Below Mkt","≈ At Market"))</f>
         <v>▼ Below Mkt</v>
       </c>
-      <c r="K32" s="190"/>
-      <c r="L32" s="190"/>
-      <c r="M32" s="190"/>
+      <c r="K32" s="191"/>
+      <c r="L32" s="191"/>
+      <c r="M32" s="191"/>
       <c r="N32" s="6"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11181,11 +11203,11 @@
         <f>'Input Data'!C7</f>
         <v>5.03</v>
       </c>
-      <c r="C33" s="212" t="str">
+      <c r="C33" s="220" t="str">
         <f>'Input Data'!D7</f>
         <v>Asterx Pty Ltd</v>
       </c>
-      <c r="D33" s="190"/>
+      <c r="D33" s="191"/>
       <c r="E33" s="90">
         <f>'Input Data'!F7</f>
         <v>229.8</v>
@@ -11206,13 +11228,13 @@
         <f>'Input Data'!Z7</f>
         <v>-7.6831578947368431E-2</v>
       </c>
-      <c r="J33" s="212" t="str">
+      <c r="J33" s="220" t="str">
         <f>IF('Input Data'!Y7&gt;0,"▲ Above Mkt",IF('Input Data'!Y7&lt;0,"▼ Below Mkt","≈ At Market"))</f>
         <v>▼ Below Mkt</v>
       </c>
-      <c r="K33" s="190"/>
-      <c r="L33" s="190"/>
-      <c r="M33" s="190"/>
+      <c r="K33" s="191"/>
+      <c r="L33" s="191"/>
+      <c r="M33" s="191"/>
       <c r="N33" s="6"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11221,11 +11243,11 @@
         <f>'Input Data'!C8</f>
         <v>5.04</v>
       </c>
-      <c r="C34" s="195" t="str">
+      <c r="C34" s="200" t="str">
         <f>'Input Data'!D8</f>
         <v>Auctionsplus Pty Ltd</v>
       </c>
-      <c r="D34" s="190"/>
+      <c r="D34" s="191"/>
       <c r="E34" s="34">
         <f>'Input Data'!F8</f>
         <v>413.5</v>
@@ -11246,13 +11268,13 @@
         <f>'Input Data'!Z8</f>
         <v>1.6050505050505037E-2</v>
       </c>
-      <c r="J34" s="195" t="str">
+      <c r="J34" s="200" t="str">
         <f>IF('Input Data'!Y8&gt;0,"▲ Above Mkt",IF('Input Data'!Y8&lt;0,"▼ Below Mkt","≈ At Market"))</f>
         <v>▲ Above Mkt</v>
       </c>
-      <c r="K34" s="190"/>
-      <c r="L34" s="190"/>
-      <c r="M34" s="190"/>
+      <c r="K34" s="191"/>
+      <c r="L34" s="191"/>
+      <c r="M34" s="191"/>
       <c r="N34" s="6"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11261,11 +11283,11 @@
         <f>'Input Data'!C9</f>
         <v>6.02</v>
       </c>
-      <c r="C35" s="208" t="str">
+      <c r="C35" s="202" t="str">
         <f>'Input Data'!D9</f>
         <v>Sungrow Australia Group</v>
       </c>
-      <c r="D35" s="190"/>
+      <c r="D35" s="191"/>
       <c r="E35" s="22">
         <f>'Input Data'!F9</f>
         <v>451.7</v>
@@ -11286,13 +11308,13 @@
         <f>'Input Data'!Z9</f>
         <v>-5.2356020942408382E-4</v>
       </c>
-      <c r="J35" s="208" t="str">
+      <c r="J35" s="202" t="str">
         <f>IF('Input Data'!Y9&gt;0,"▲ Above Mkt",IF('Input Data'!Y9&lt;0,"▼ Below Mkt","≈ At Market"))</f>
         <v>▼ Below Mkt</v>
       </c>
-      <c r="K35" s="190"/>
-      <c r="L35" s="190"/>
-      <c r="M35" s="190"/>
+      <c r="K35" s="191"/>
+      <c r="L35" s="191"/>
+      <c r="M35" s="191"/>
       <c r="N35" s="6"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11301,11 +11323,11 @@
         <f>'Input Data'!C10</f>
         <v>6.03</v>
       </c>
-      <c r="C36" s="195" t="str">
+      <c r="C36" s="200" t="str">
         <f>'Input Data'!D10</f>
         <v>Keeping Company Pty Ltd</v>
       </c>
-      <c r="D36" s="190"/>
+      <c r="D36" s="191"/>
       <c r="E36" s="34">
         <f>'Input Data'!F10</f>
         <v>189.4</v>
@@ -11326,13 +11348,13 @@
         <f>'Input Data'!Z10</f>
         <v>3.0323232323232304E-2</v>
       </c>
-      <c r="J36" s="195" t="str">
+      <c r="J36" s="200" t="str">
         <f>IF('Input Data'!Y10&gt;0,"▲ Above Mkt",IF('Input Data'!Y10&lt;0,"▼ Below Mkt","≈ At Market"))</f>
         <v>▲ Above Mkt</v>
       </c>
-      <c r="K36" s="190"/>
-      <c r="L36" s="190"/>
-      <c r="M36" s="190"/>
+      <c r="K36" s="191"/>
+      <c r="L36" s="191"/>
+      <c r="M36" s="191"/>
       <c r="N36" s="6"/>
     </row>
     <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11341,11 +11363,11 @@
         <f>'Input Data'!C11</f>
         <v>6.04</v>
       </c>
-      <c r="C37" s="208" t="str">
+      <c r="C37" s="202" t="str">
         <f>'Input Data'!D11</f>
         <v>Elekta Pty Limited</v>
       </c>
-      <c r="D37" s="190"/>
+      <c r="D37" s="191"/>
       <c r="E37" s="22">
         <f>'Input Data'!F11</f>
         <v>267.89999999999998</v>
@@ -11366,13 +11388,13 @@
         <f>'Input Data'!Z11</f>
         <v>-3.6649214659685861E-2</v>
       </c>
-      <c r="J37" s="208" t="str">
+      <c r="J37" s="202" t="str">
         <f>IF('Input Data'!Y11&gt;0,"▲ Above Mkt",IF('Input Data'!Y11&lt;0,"▼ Below Mkt","≈ At Market"))</f>
         <v>▼ Below Mkt</v>
       </c>
-      <c r="K37" s="190"/>
-      <c r="L37" s="190"/>
-      <c r="M37" s="190"/>
+      <c r="K37" s="191"/>
+      <c r="L37" s="191"/>
+      <c r="M37" s="191"/>
       <c r="N37" s="6"/>
     </row>
     <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11381,11 +11403,11 @@
         <f>'Input Data'!C12</f>
         <v>7.01</v>
       </c>
-      <c r="C38" s="195" t="str">
+      <c r="C38" s="200" t="str">
         <f>'Input Data'!D12</f>
         <v>Sungrow Australia Group</v>
       </c>
-      <c r="D38" s="190"/>
+      <c r="D38" s="191"/>
       <c r="E38" s="34">
         <f>'Input Data'!F12</f>
         <v>484.1</v>
@@ -11406,13 +11428,13 @@
         <f>'Input Data'!Z12</f>
         <v>2.9186274509803902E-2</v>
       </c>
-      <c r="J38" s="195" t="str">
+      <c r="J38" s="200" t="str">
         <f>IF('Input Data'!Y12&gt;0,"▲ Above Mkt",IF('Input Data'!Y12&lt;0,"▼ Below Mkt","≈ At Market"))</f>
         <v>▲ Above Mkt</v>
       </c>
-      <c r="K38" s="190"/>
-      <c r="L38" s="190"/>
-      <c r="M38" s="190"/>
+      <c r="K38" s="191"/>
+      <c r="L38" s="191"/>
+      <c r="M38" s="191"/>
       <c r="N38" s="6"/>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11421,11 +11443,11 @@
         <f>'Input Data'!C14</f>
         <v>8.01</v>
       </c>
-      <c r="C39" s="208" t="str">
+      <c r="C39" s="202" t="str">
         <f>'Input Data'!D14</f>
         <v>Vanderlande Industries Australia Pty Ltd</v>
       </c>
-      <c r="D39" s="190"/>
+      <c r="D39" s="191"/>
       <c r="E39" s="22">
         <f>'Input Data'!F14</f>
         <v>686.7</v>
@@ -11446,13 +11468,13 @@
         <f>'Input Data'!Z14</f>
         <v>-3.434343434343756E-4</v>
       </c>
-      <c r="J39" s="208" t="str">
+      <c r="J39" s="202" t="str">
         <f>IF('Input Data'!Y14&gt;0,"▲ Above Mkt",IF('Input Data'!Y14&lt;0,"▼ Below Mkt","≈ At Market"))</f>
         <v>▼ Below Mkt</v>
       </c>
-      <c r="K39" s="190"/>
-      <c r="L39" s="190"/>
-      <c r="M39" s="190"/>
+      <c r="K39" s="191"/>
+      <c r="L39" s="191"/>
+      <c r="M39" s="191"/>
       <c r="N39" s="6"/>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11461,11 +11483,11 @@
         <f>'Input Data'!C15</f>
         <v>8.03</v>
       </c>
-      <c r="C40" s="195" t="str">
+      <c r="C40" s="200" t="str">
         <f>'Input Data'!D15</f>
         <v>Can Too Foundation Limited</v>
       </c>
-      <c r="D40" s="190"/>
+      <c r="D40" s="191"/>
       <c r="E40" s="34">
         <f>'Input Data'!F15</f>
         <v>116.3</v>
@@ -11486,13 +11508,13 @@
         <f>'Input Data'!Z15</f>
         <v>0</v>
       </c>
-      <c r="J40" s="195" t="str">
+      <c r="J40" s="200" t="str">
         <f>IF('Input Data'!Y15&gt;0,"▲ Above Mkt",IF('Input Data'!Y15&lt;0,"▼ Below Mkt","≈ At Market"))</f>
         <v>≈ At Market</v>
       </c>
-      <c r="K40" s="190"/>
-      <c r="L40" s="190"/>
-      <c r="M40" s="190"/>
+      <c r="K40" s="191"/>
+      <c r="L40" s="191"/>
+      <c r="M40" s="191"/>
       <c r="N40" s="6"/>
     </row>
     <row r="41" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11501,11 +11523,11 @@
         <f>'Input Data'!C16</f>
         <v>9.01</v>
       </c>
-      <c r="C41" s="208" t="str">
+      <c r="C41" s="202" t="str">
         <f>'Input Data'!D16</f>
         <v>Pitt &amp; Sherry (Operations) Pty Ltd</v>
       </c>
-      <c r="D41" s="190"/>
+      <c r="D41" s="191"/>
       <c r="E41" s="22">
         <f>'Input Data'!F16</f>
         <v>453.3</v>
@@ -11526,13 +11548,13 @@
         <f>'Input Data'!Z16</f>
         <v>-1.20865384615384E-2</v>
       </c>
-      <c r="J41" s="208" t="str">
+      <c r="J41" s="202" t="str">
         <f>IF('Input Data'!Y16&gt;0,"▲ Above Mkt",IF('Input Data'!Y16&lt;0,"▼ Below Mkt","≈ At Market"))</f>
         <v>▼ Below Mkt</v>
       </c>
-      <c r="K41" s="190"/>
-      <c r="L41" s="190"/>
-      <c r="M41" s="190"/>
+      <c r="K41" s="191"/>
+      <c r="L41" s="191"/>
+      <c r="M41" s="191"/>
       <c r="N41" s="6"/>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11541,11 +11563,11 @@
         <f>'Input Data'!C17</f>
         <v>12.01</v>
       </c>
-      <c r="C42" s="195" t="str">
+      <c r="C42" s="200" t="str">
         <f>'Input Data'!D17</f>
         <v>Hulsbosch Design Pty Ltd</v>
       </c>
-      <c r="D42" s="190"/>
+      <c r="D42" s="191"/>
       <c r="E42" s="34">
         <f>'Input Data'!F17</f>
         <v>344.5</v>
@@ -11566,13 +11588,13 @@
         <f>'Input Data'!Z17</f>
         <v>-4.7798076923076957E-2</v>
       </c>
-      <c r="J42" s="195" t="str">
+      <c r="J42" s="200" t="str">
         <f>IF('Input Data'!Y17&gt;0,"▲ Above Mkt",IF('Input Data'!Y17&lt;0,"▼ Below Mkt","≈ At Market"))</f>
         <v>▼ Below Mkt</v>
       </c>
-      <c r="K42" s="190"/>
-      <c r="L42" s="190"/>
-      <c r="M42" s="190"/>
+      <c r="K42" s="191"/>
+      <c r="L42" s="191"/>
+      <c r="M42" s="191"/>
       <c r="N42" s="6"/>
     </row>
     <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11581,11 +11603,11 @@
         <f>'Input Data'!C18</f>
         <v>9.02</v>
       </c>
-      <c r="C43" s="208" t="str">
+      <c r="C43" s="202" t="str">
         <f>'Input Data'!D18</f>
         <v>Smile Partners Australia</v>
       </c>
-      <c r="D43" s="190"/>
+      <c r="D43" s="191"/>
       <c r="E43" s="22">
         <f>'Input Data'!F18</f>
         <v>251</v>
@@ -11606,13 +11628,13 @@
         <f>'Input Data'!Z18</f>
         <v>-5.0505050505050509E-3</v>
       </c>
-      <c r="J43" s="208" t="str">
+      <c r="J43" s="202" t="str">
         <f>IF('Input Data'!Y18&gt;0,"▲ Above Mkt",IF('Input Data'!Y18&lt;0,"▼ Below Mkt","≈ At Market"))</f>
         <v>▼ Below Mkt</v>
       </c>
-      <c r="K43" s="190"/>
-      <c r="L43" s="190"/>
-      <c r="M43" s="190"/>
+      <c r="K43" s="191"/>
+      <c r="L43" s="191"/>
+      <c r="M43" s="191"/>
       <c r="N43" s="6"/>
     </row>
     <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11621,11 +11643,11 @@
         <f>'Input Data'!C19</f>
         <v>12.02</v>
       </c>
-      <c r="C44" s="195" t="str">
+      <c r="C44" s="200" t="str">
         <f>'Input Data'!D19</f>
         <v>Aei Insurance Group Pty Ltd</v>
       </c>
-      <c r="D44" s="190"/>
+      <c r="D44" s="191"/>
       <c r="E44" s="34">
         <f>'Input Data'!F19</f>
         <v>536</v>
@@ -11646,13 +11668,13 @@
         <f>'Input Data'!Z19</f>
         <v>-2.1782178217821781E-2</v>
       </c>
-      <c r="J44" s="195" t="str">
+      <c r="J44" s="200" t="str">
         <f>IF('Input Data'!Y19&gt;0,"▲ Above Mkt",IF('Input Data'!Y19&lt;0,"▼ Below Mkt","≈ At Market"))</f>
         <v>▼ Below Mkt</v>
       </c>
-      <c r="K44" s="190"/>
-      <c r="L44" s="190"/>
-      <c r="M44" s="190"/>
+      <c r="K44" s="191"/>
+      <c r="L44" s="191"/>
+      <c r="M44" s="191"/>
       <c r="N44" s="6"/>
     </row>
     <row r="45" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -11673,7 +11695,7 @@
     </row>
     <row r="46" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="6"/>
-      <c r="B46" s="199" t="s">
+      <c r="B46" s="189" t="s">
         <v>276</v>
       </c>
       <c r="C46" s="183"/>
@@ -11691,7 +11713,7 @@
     </row>
     <row r="47" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="6"/>
-      <c r="B47" s="213" t="s">
+      <c r="B47" s="218" t="s">
         <v>277</v>
       </c>
       <c r="C47" s="183"/>
@@ -11704,7 +11726,7 @@
       <c r="F47" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="G47" s="213" t="s">
+      <c r="G47" s="218" t="s">
         <v>281</v>
       </c>
       <c r="H47" s="183"/>
@@ -11717,10 +11739,10 @@
     </row>
     <row r="48" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="6"/>
-      <c r="B48" s="226" t="s">
+      <c r="B48" s="209" t="s">
         <v>282</v>
       </c>
-      <c r="C48" s="190"/>
+      <c r="C48" s="191"/>
       <c r="D48" s="41" t="s">
         <v>283</v>
       </c>
@@ -11729,25 +11751,25 @@
       </c>
       <c r="F48" s="93">
         <f t="shared" ref="F48:F60" ca="1" si="0">IFERROR(INT(E48-TODAY()),"")</f>
-        <v>1</v>
-      </c>
-      <c r="G48" s="226" t="s">
+        <v>-33</v>
+      </c>
+      <c r="G48" s="209" t="s">
         <v>284</v>
       </c>
-      <c r="H48" s="190"/>
-      <c r="I48" s="190"/>
-      <c r="J48" s="190"/>
-      <c r="K48" s="190"/>
-      <c r="L48" s="190"/>
-      <c r="M48" s="190"/>
+      <c r="H48" s="191"/>
+      <c r="I48" s="191"/>
+      <c r="J48" s="191"/>
+      <c r="K48" s="191"/>
+      <c r="L48" s="191"/>
+      <c r="M48" s="191"/>
       <c r="N48" s="6"/>
     </row>
     <row r="49" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="6"/>
-      <c r="B49" s="189" t="s">
+      <c r="B49" s="199" t="s">
         <v>285</v>
       </c>
-      <c r="C49" s="190"/>
+      <c r="C49" s="191"/>
       <c r="D49" s="94" t="s">
         <v>8</v>
       </c>
@@ -11756,25 +11778,25 @@
       </c>
       <c r="F49" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>335</v>
-      </c>
-      <c r="G49" s="189" t="s">
+        <v>301</v>
+      </c>
+      <c r="G49" s="199" t="s">
         <v>286</v>
       </c>
-      <c r="H49" s="190"/>
-      <c r="I49" s="190"/>
-      <c r="J49" s="190"/>
-      <c r="K49" s="190"/>
-      <c r="L49" s="190"/>
-      <c r="M49" s="190"/>
+      <c r="H49" s="191"/>
+      <c r="I49" s="191"/>
+      <c r="J49" s="191"/>
+      <c r="K49" s="191"/>
+      <c r="L49" s="191"/>
+      <c r="M49" s="191"/>
       <c r="N49" s="6"/>
     </row>
     <row r="50" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="6"/>
-      <c r="B50" s="208" t="s">
+      <c r="B50" s="202" t="s">
         <v>287</v>
       </c>
-      <c r="C50" s="190"/>
+      <c r="C50" s="191"/>
       <c r="D50" s="13" t="s">
         <v>288</v>
       </c>
@@ -11783,25 +11805,25 @@
       </c>
       <c r="F50" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>244</v>
-      </c>
-      <c r="G50" s="208" t="s">
+        <v>210</v>
+      </c>
+      <c r="G50" s="202" t="s">
         <v>289</v>
       </c>
-      <c r="H50" s="190"/>
-      <c r="I50" s="190"/>
-      <c r="J50" s="190"/>
-      <c r="K50" s="190"/>
-      <c r="L50" s="190"/>
-      <c r="M50" s="190"/>
+      <c r="H50" s="191"/>
+      <c r="I50" s="191"/>
+      <c r="J50" s="191"/>
+      <c r="K50" s="191"/>
+      <c r="L50" s="191"/>
+      <c r="M50" s="191"/>
       <c r="N50" s="6"/>
     </row>
     <row r="51" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="6"/>
-      <c r="B51" s="217" t="s">
+      <c r="B51" s="216" t="s">
         <v>290</v>
       </c>
-      <c r="C51" s="190"/>
+      <c r="C51" s="191"/>
       <c r="D51" s="49" t="s">
         <v>291</v>
       </c>
@@ -11810,25 +11832,25 @@
       </c>
       <c r="F51" s="99">
         <f t="shared" ca="1" si="0"/>
-        <v>-394</v>
-      </c>
-      <c r="G51" s="217" t="s">
+        <v>-428</v>
+      </c>
+      <c r="G51" s="216" t="s">
         <v>292</v>
       </c>
-      <c r="H51" s="190"/>
-      <c r="I51" s="190"/>
-      <c r="J51" s="190"/>
-      <c r="K51" s="190"/>
-      <c r="L51" s="190"/>
-      <c r="M51" s="190"/>
+      <c r="H51" s="191"/>
+      <c r="I51" s="191"/>
+      <c r="J51" s="191"/>
+      <c r="K51" s="191"/>
+      <c r="L51" s="191"/>
+      <c r="M51" s="191"/>
       <c r="N51" s="6"/>
     </row>
     <row r="52" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="6"/>
-      <c r="B52" s="226" t="s">
+      <c r="B52" s="209" t="s">
         <v>285</v>
       </c>
-      <c r="C52" s="190"/>
+      <c r="C52" s="191"/>
       <c r="D52" s="41" t="s">
         <v>291</v>
       </c>
@@ -11837,25 +11859,25 @@
       </c>
       <c r="F52" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>-29</v>
-      </c>
-      <c r="G52" s="226" t="s">
+        <v>-63</v>
+      </c>
+      <c r="G52" s="209" t="s">
         <v>293</v>
       </c>
-      <c r="H52" s="190"/>
-      <c r="I52" s="190"/>
-      <c r="J52" s="190"/>
-      <c r="K52" s="190"/>
-      <c r="L52" s="190"/>
-      <c r="M52" s="190"/>
+      <c r="H52" s="191"/>
+      <c r="I52" s="191"/>
+      <c r="J52" s="191"/>
+      <c r="K52" s="191"/>
+      <c r="L52" s="191"/>
+      <c r="M52" s="191"/>
       <c r="N52" s="6"/>
     </row>
     <row r="53" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="6"/>
-      <c r="B53" s="226" t="s">
+      <c r="B53" s="209" t="s">
         <v>294</v>
       </c>
-      <c r="C53" s="190"/>
+      <c r="C53" s="191"/>
       <c r="D53" s="41" t="s">
         <v>288</v>
       </c>
@@ -11864,25 +11886,25 @@
       </c>
       <c r="F53" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G53" s="226" t="s">
+        <v>-33</v>
+      </c>
+      <c r="G53" s="209" t="s">
         <v>295</v>
       </c>
-      <c r="H53" s="190"/>
-      <c r="I53" s="190"/>
-      <c r="J53" s="190"/>
-      <c r="K53" s="190"/>
-      <c r="L53" s="190"/>
-      <c r="M53" s="190"/>
+      <c r="H53" s="191"/>
+      <c r="I53" s="191"/>
+      <c r="J53" s="191"/>
+      <c r="K53" s="191"/>
+      <c r="L53" s="191"/>
+      <c r="M53" s="191"/>
       <c r="N53" s="6"/>
     </row>
     <row r="54" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="6"/>
-      <c r="B54" s="226" t="s">
+      <c r="B54" s="209" t="s">
         <v>296</v>
       </c>
-      <c r="C54" s="190"/>
+      <c r="C54" s="191"/>
       <c r="D54" s="41" t="s">
         <v>297</v>
       </c>
@@ -11891,25 +11913,25 @@
       </c>
       <c r="F54" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G54" s="226" t="s">
+        <v>-30</v>
+      </c>
+      <c r="G54" s="209" t="s">
         <v>298</v>
       </c>
-      <c r="H54" s="190"/>
-      <c r="I54" s="190"/>
-      <c r="J54" s="190"/>
-      <c r="K54" s="190"/>
-      <c r="L54" s="190"/>
-      <c r="M54" s="190"/>
+      <c r="H54" s="191"/>
+      <c r="I54" s="191"/>
+      <c r="J54" s="191"/>
+      <c r="K54" s="191"/>
+      <c r="L54" s="191"/>
+      <c r="M54" s="191"/>
       <c r="N54" s="6"/>
     </row>
     <row r="55" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="6"/>
-      <c r="B55" s="226" t="s">
+      <c r="B55" s="209" t="s">
         <v>299</v>
       </c>
-      <c r="C55" s="190"/>
+      <c r="C55" s="191"/>
       <c r="D55" s="41" t="s">
         <v>288</v>
       </c>
@@ -11918,25 +11940,25 @@
       </c>
       <c r="F55" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G55" s="226" t="s">
+        <v>-33</v>
+      </c>
+      <c r="G55" s="209" t="s">
         <v>300</v>
       </c>
-      <c r="H55" s="190"/>
-      <c r="I55" s="190"/>
-      <c r="J55" s="190"/>
-      <c r="K55" s="190"/>
-      <c r="L55" s="190"/>
-      <c r="M55" s="190"/>
+      <c r="H55" s="191"/>
+      <c r="I55" s="191"/>
+      <c r="J55" s="191"/>
+      <c r="K55" s="191"/>
+      <c r="L55" s="191"/>
+      <c r="M55" s="191"/>
       <c r="N55" s="6"/>
     </row>
     <row r="56" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="6"/>
-      <c r="B56" s="208" t="s">
+      <c r="B56" s="202" t="s">
         <v>296</v>
       </c>
-      <c r="C56" s="190"/>
+      <c r="C56" s="191"/>
       <c r="D56" s="13" t="s">
         <v>8</v>
       </c>
@@ -11945,25 +11967,25 @@
       </c>
       <c r="F56" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>368</v>
-      </c>
-      <c r="G56" s="208" t="s">
+        <v>334</v>
+      </c>
+      <c r="G56" s="202" t="s">
         <v>301</v>
       </c>
-      <c r="H56" s="190"/>
-      <c r="I56" s="190"/>
-      <c r="J56" s="190"/>
-      <c r="K56" s="190"/>
-      <c r="L56" s="190"/>
-      <c r="M56" s="190"/>
+      <c r="H56" s="191"/>
+      <c r="I56" s="191"/>
+      <c r="J56" s="191"/>
+      <c r="K56" s="191"/>
+      <c r="L56" s="191"/>
+      <c r="M56" s="191"/>
       <c r="N56" s="6"/>
     </row>
     <row r="57" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="6"/>
-      <c r="B57" s="226" t="s">
+      <c r="B57" s="209" t="s">
         <v>302</v>
       </c>
-      <c r="C57" s="190"/>
+      <c r="C57" s="191"/>
       <c r="D57" s="41" t="s">
         <v>297</v>
       </c>
@@ -11972,25 +11994,25 @@
       </c>
       <c r="F57" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>-29</v>
-      </c>
-      <c r="G57" s="226" t="s">
+        <v>-63</v>
+      </c>
+      <c r="G57" s="209" t="s">
         <v>295</v>
       </c>
-      <c r="H57" s="190"/>
-      <c r="I57" s="190"/>
-      <c r="J57" s="190"/>
-      <c r="K57" s="190"/>
-      <c r="L57" s="190"/>
-      <c r="M57" s="190"/>
+      <c r="H57" s="191"/>
+      <c r="I57" s="191"/>
+      <c r="J57" s="191"/>
+      <c r="K57" s="191"/>
+      <c r="L57" s="191"/>
+      <c r="M57" s="191"/>
       <c r="N57" s="6"/>
     </row>
     <row r="58" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="6"/>
-      <c r="B58" s="217" t="s">
+      <c r="B58" s="216" t="s">
         <v>303</v>
       </c>
-      <c r="C58" s="190"/>
+      <c r="C58" s="191"/>
       <c r="D58" s="49" t="s">
         <v>304</v>
       </c>
@@ -12001,23 +12023,23 @@
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="G58" s="217" t="s">
+      <c r="G58" s="216" t="s">
         <v>306</v>
       </c>
-      <c r="H58" s="190"/>
-      <c r="I58" s="190"/>
-      <c r="J58" s="190"/>
-      <c r="K58" s="190"/>
-      <c r="L58" s="190"/>
-      <c r="M58" s="190"/>
+      <c r="H58" s="191"/>
+      <c r="I58" s="191"/>
+      <c r="J58" s="191"/>
+      <c r="K58" s="191"/>
+      <c r="L58" s="191"/>
+      <c r="M58" s="191"/>
       <c r="N58" s="6"/>
     </row>
     <row r="59" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="6"/>
-      <c r="B59" s="217" t="s">
+      <c r="B59" s="216" t="s">
         <v>307</v>
       </c>
-      <c r="C59" s="190"/>
+      <c r="C59" s="191"/>
       <c r="D59" s="49" t="s">
         <v>304</v>
       </c>
@@ -12028,15 +12050,15 @@
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="G59" s="217" t="s">
+      <c r="G59" s="216" t="s">
         <v>308</v>
       </c>
-      <c r="H59" s="190"/>
-      <c r="I59" s="190"/>
-      <c r="J59" s="190"/>
-      <c r="K59" s="190"/>
-      <c r="L59" s="190"/>
-      <c r="M59" s="190"/>
+      <c r="H59" s="191"/>
+      <c r="I59" s="191"/>
+      <c r="J59" s="191"/>
+      <c r="K59" s="191"/>
+      <c r="L59" s="191"/>
+      <c r="M59" s="191"/>
       <c r="N59" s="6"/>
     </row>
     <row r="60" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -12053,7 +12075,7 @@
       </c>
       <c r="F60" s="59">
         <f t="shared" ca="1" si="0"/>
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="G60" s="59" t="s">
         <v>310</v>
@@ -12068,7 +12090,7 @@
     </row>
     <row r="61" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="100"/>
-      <c r="B61" s="199" t="s">
+      <c r="B61" s="189" t="s">
         <v>311</v>
       </c>
       <c r="C61" s="183"/>
@@ -12089,26 +12111,26 @@
       <c r="B62" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="C62" s="204" t="s">
+      <c r="C62" s="211" t="s">
         <v>312</v>
       </c>
       <c r="D62" s="183"/>
-      <c r="E62" s="204" t="s">
+      <c r="E62" s="211" t="s">
         <v>6</v>
       </c>
       <c r="F62" s="183"/>
-      <c r="G62" s="204" t="s">
+      <c r="G62" s="211" t="s">
         <v>313</v>
       </c>
       <c r="H62" s="183"/>
-      <c r="I62" s="204" t="s">
+      <c r="I62" s="211" t="s">
         <v>256</v>
       </c>
       <c r="J62" s="183"/>
       <c r="K62" s="101" t="s">
         <v>314</v>
       </c>
-      <c r="L62" s="204" t="s">
+      <c r="L62" s="211" t="s">
         <v>28</v>
       </c>
       <c r="M62" s="183"/>
@@ -12123,24 +12145,24 @@
         <f ca="1">IFERROR(MID(IF(('Input Data'!AD18&gt;TODAY())*('Input Data'!AE18&gt;0),", "&amp;'Input Data'!AF18&amp;" ("&amp;'Input Data'!C18&amp;")","")&amp;IF(('Input Data'!AD19&gt;TODAY())*('Input Data'!AE19&gt;0),", "&amp;'Input Data'!AF19&amp;" ("&amp;'Input Data'!C19&amp;")",""),3,999),"—")</f>
         <v>Smile Partners Australia (9.02), AEI Insurance Group (12.02)</v>
       </c>
-      <c r="D63" s="190"/>
-      <c r="E63" s="207">
+      <c r="D63" s="191"/>
+      <c r="E63" s="212">
         <f>SUMPRODUCT(('Input Data'!B3:B24="L12")*'Input Data'!F3:F24)</f>
         <v>880.5</v>
       </c>
-      <c r="F63" s="190"/>
+      <c r="F63" s="191"/>
       <c r="G63" s="201">
         <f ca="1">SUMPRODUCT(('Input Data'!B3:B24="L12")*('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!Q3:Q24)</f>
         <v>898518.89500000002</v>
       </c>
-      <c r="H63" s="190"/>
-      <c r="I63" s="219"/>
+      <c r="H63" s="191"/>
+      <c r="I63" s="205"/>
       <c r="J63" s="186"/>
       <c r="K63" s="86" t="str">
         <f ca="1">IFERROR(IF(SUMPRODUCT(('Input Data'!B3:B24="L12")*('Input Data'!AE3:AE24&gt;0)*('Input Data'!AD3:AD24&gt;TODAY()))=0,"VACANT",TEXT(_xludf.minifs('Input Data'!AD3:AD24,'Input Data'!B3:B24,"L12",'Input Data'!AD3:AD24,"&gt;"&amp;TODAY(),'Input Data'!AE3:AE24,"&gt;0"),"YYYY")),"—")</f>
         <v>—</v>
       </c>
-      <c r="L63" s="206"/>
+      <c r="L63" s="203"/>
       <c r="M63" s="186"/>
       <c r="N63" s="100"/>
     </row>
@@ -12153,24 +12175,24 @@
         <f ca="1">IFERROR(MID(IF(('Input Data'!AD23&gt;TODAY())*('Input Data'!AE23&gt;0),", "&amp;'Input Data'!AF23&amp;" ("&amp;'Input Data'!C23&amp;")","")&amp;IF(('Input Data'!AD24&gt;TODAY())*('Input Data'!AE24&gt;0),", "&amp;'Input Data'!AF24&amp;" ("&amp;'Input Data'!C24&amp;")",""),3,999),"—")</f>
         <v>Haskoning Australia (11.02)</v>
       </c>
-      <c r="D64" s="190"/>
-      <c r="E64" s="207">
+      <c r="D64" s="191"/>
+      <c r="E64" s="212">
         <f>SUMPRODUCT(('Input Data'!B3:B24="L11")*'Input Data'!F3:F24)</f>
-        <v>772</v>
-      </c>
-      <c r="F64" s="190"/>
+        <v>790.5</v>
+      </c>
+      <c r="F64" s="191"/>
       <c r="G64" s="201">
         <f ca="1">SUMPRODUCT(('Input Data'!B3:B24="L11")*('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!Q3:Q24)</f>
-        <v>-113632</v>
-      </c>
-      <c r="H64" s="190"/>
-      <c r="I64" s="219"/>
+        <v>-101152</v>
+      </c>
+      <c r="H64" s="191"/>
+      <c r="I64" s="205"/>
       <c r="J64" s="186"/>
       <c r="K64" s="86" t="str">
         <f ca="1">IFERROR(IF(SUMPRODUCT(('Input Data'!B3:B24="L11")*('Input Data'!AE3:AE24&gt;0)*('Input Data'!AD3:AD24&gt;TODAY()))=0,"VACANT",TEXT(_xludf.minifs('Input Data'!AD3:AD24,'Input Data'!B3:B24,"L11",'Input Data'!AD3:AD24,"&gt;"&amp;TODAY(),'Input Data'!AE3:AE24,"&gt;0"),"YYYY")),"—")</f>
         <v>—</v>
       </c>
-      <c r="L64" s="206"/>
+      <c r="L64" s="203"/>
       <c r="M64" s="186"/>
       <c r="N64" s="1"/>
     </row>
@@ -12183,24 +12205,24 @@
         <f ca="1">IFERROR(MID(IF(('Input Data'!AD21&gt;TODAY())*('Input Data'!AE21&gt;0),", "&amp;'Input Data'!AF21&amp;" ("&amp;'Input Data'!C21&amp;")","")&amp;IF(('Input Data'!AD22&gt;TODAY())*('Input Data'!AE22&gt;0),", "&amp;'Input Data'!AF22&amp;" ("&amp;'Input Data'!C22&amp;")",""),3,999),"—")</f>
         <v/>
       </c>
-      <c r="D65" s="190"/>
-      <c r="E65" s="207">
+      <c r="D65" s="191"/>
+      <c r="E65" s="212">
         <f>SUMPRODUCT(('Input Data'!B3:B24="L10")*'Input Data'!F3:F24)</f>
         <v>787</v>
       </c>
-      <c r="F65" s="190"/>
+      <c r="F65" s="191"/>
       <c r="G65" s="201">
         <f ca="1">SUMPRODUCT(('Input Data'!B3:B24="L10")*('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!Q3:Q24)</f>
         <v>0</v>
       </c>
-      <c r="H65" s="190"/>
-      <c r="I65" s="219"/>
+      <c r="H65" s="191"/>
+      <c r="I65" s="205"/>
       <c r="J65" s="186"/>
       <c r="K65" s="86" t="str">
         <f ca="1">IFERROR(IF(SUMPRODUCT(('Input Data'!B3:B24="L10")*('Input Data'!AE3:AE24&gt;0)*('Input Data'!AD3:AD24&gt;TODAY()))=0,"VACANT",TEXT(_xludf.minifs('Input Data'!AD3:AD24,'Input Data'!B3:B24,"L10",'Input Data'!AD3:AD24,"&gt;"&amp;TODAY(),'Input Data'!AE3:AE24,"&gt;0"),"YYYY")),"—")</f>
         <v>VACANT</v>
       </c>
-      <c r="L65" s="206"/>
+      <c r="L65" s="203"/>
       <c r="M65" s="186"/>
       <c r="N65" s="100"/>
     </row>
@@ -12213,24 +12235,24 @@
         <f ca="1">IFERROR(MID(IF(('Input Data'!AD16&gt;TODAY())*('Input Data'!AE16&gt;0),", "&amp;'Input Data'!AF16&amp;" ("&amp;'Input Data'!C16&amp;")","")&amp;IF(('Input Data'!AD17&gt;TODAY())*('Input Data'!AE17&gt;0),", "&amp;'Input Data'!AF17&amp;" ("&amp;'Input Data'!C17&amp;")",""),3,999),"—")</f>
         <v>Pitt &amp; Sherry (9.01), Hulsbosch Design (12.01)</v>
       </c>
-      <c r="D66" s="190"/>
-      <c r="E66" s="207">
+      <c r="D66" s="191"/>
+      <c r="E66" s="212">
         <f>SUMPRODUCT(('Input Data'!B3:B24="L09")*'Input Data'!F3:F24)</f>
         <v>704.3</v>
       </c>
-      <c r="F66" s="190"/>
+      <c r="F66" s="191"/>
       <c r="G66" s="201">
         <f ca="1">SUMPRODUCT(('Input Data'!B3:B24="L09")*('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!Q3:Q24)</f>
         <v>569217.00899999996</v>
       </c>
-      <c r="H66" s="190"/>
-      <c r="I66" s="219"/>
+      <c r="H66" s="191"/>
+      <c r="I66" s="205"/>
       <c r="J66" s="186"/>
       <c r="K66" s="86" t="str">
         <f ca="1">IFERROR(IF(SUMPRODUCT(('Input Data'!B3:B24="L09")*('Input Data'!AE3:AE24&gt;0)*('Input Data'!AD3:AD24&gt;TODAY()))=0,"VACANT",TEXT(_xludf.minifs('Input Data'!AD3:AD24,'Input Data'!B3:B24,"L09",'Input Data'!AD3:AD24,"&gt;"&amp;TODAY(),'Input Data'!AE3:AE24,"&gt;0"),"YYYY")),"—")</f>
         <v>—</v>
       </c>
-      <c r="L66" s="206"/>
+      <c r="L66" s="203"/>
       <c r="M66" s="186"/>
       <c r="N66" s="1"/>
     </row>
@@ -12243,24 +12265,24 @@
         <f ca="1">IFERROR(MID(IF(('Input Data'!AD14&gt;TODAY())*('Input Data'!AE14&gt;0),", "&amp;'Input Data'!AF14&amp;" ("&amp;'Input Data'!C14&amp;")","")&amp;IF(('Input Data'!AD15&gt;TODAY())*('Input Data'!AE15&gt;0),", "&amp;'Input Data'!AF15&amp;" ("&amp;'Input Data'!C15&amp;")",""),3,999),"—")</f>
         <v>Vanderlande Industries (8.01), Can Too Foundation (8.03)</v>
       </c>
-      <c r="D67" s="190"/>
-      <c r="E67" s="207">
+      <c r="D67" s="191"/>
+      <c r="E67" s="212">
         <f>SUMPRODUCT(('Input Data'!B3:B24="L08")*'Input Data'!F3:F24)</f>
         <v>803</v>
       </c>
-      <c r="F67" s="190"/>
+      <c r="F67" s="191"/>
       <c r="G67" s="201">
         <f ca="1">SUMPRODUCT(('Input Data'!B3:B24="L08")*('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!Q3:Q24)</f>
         <v>607413.31200000003</v>
       </c>
-      <c r="H67" s="190"/>
-      <c r="I67" s="219"/>
+      <c r="H67" s="191"/>
+      <c r="I67" s="205"/>
       <c r="J67" s="186"/>
       <c r="K67" s="86" t="str">
         <f ca="1">IFERROR(IF(SUMPRODUCT(('Input Data'!B3:B24="L08")*('Input Data'!AE3:AE24&gt;0)*('Input Data'!AD3:AD24&gt;TODAY()))=0,"VACANT",TEXT(_xludf.minifs('Input Data'!AD3:AD24,'Input Data'!B3:B24,"L08",'Input Data'!AD3:AD24,"&gt;"&amp;TODAY(),'Input Data'!AE3:AE24,"&gt;0"),"YYYY")),"—")</f>
         <v>—</v>
       </c>
-      <c r="L67" s="206"/>
+      <c r="L67" s="203"/>
       <c r="M67" s="186"/>
       <c r="N67" s="100"/>
     </row>
@@ -12273,24 +12295,24 @@
         <f ca="1">IFERROR(MID(IF(('Input Data'!AD12&gt;TODAY())*('Input Data'!AE12&gt;0),", "&amp;'Input Data'!AF12&amp;" ("&amp;'Input Data'!C12&amp;")","")&amp;IF(('Input Data'!AD13&gt;TODAY())*('Input Data'!AE13&gt;0),", "&amp;'Input Data'!AF13&amp;" ("&amp;'Input Data'!C13&amp;")",""),3,999),"—")</f>
         <v>Sungrow (L7 Main) (7.01)</v>
       </c>
-      <c r="D68" s="190"/>
-      <c r="E68" s="207">
+      <c r="D68" s="191"/>
+      <c r="E68" s="212">
         <f>SUMPRODUCT(('Input Data'!B3:B24="L07")*'Input Data'!F3:F24)</f>
         <v>849.6</v>
       </c>
-      <c r="F68" s="190"/>
+      <c r="F68" s="191"/>
       <c r="G68" s="201">
         <f ca="1">SUMPRODUCT(('Input Data'!B3:B24="L07")*('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!Q3:Q24)</f>
         <v>399443.10699999996</v>
       </c>
-      <c r="H68" s="190"/>
-      <c r="I68" s="219"/>
+      <c r="H68" s="191"/>
+      <c r="I68" s="205"/>
       <c r="J68" s="186"/>
       <c r="K68" s="86" t="str">
         <f ca="1">IFERROR(IF(SUMPRODUCT(('Input Data'!B3:B24="L07")*('Input Data'!AE3:AE24&gt;0)*('Input Data'!AD3:AD24&gt;TODAY()))=0,"VACANT",TEXT(_xludf.minifs('Input Data'!AD3:AD24,'Input Data'!B3:B24,"L07",'Input Data'!AD3:AD24,"&gt;"&amp;TODAY(),'Input Data'!AE3:AE24,"&gt;0"),"YYYY")),"—")</f>
         <v>—</v>
       </c>
-      <c r="L68" s="206"/>
+      <c r="L68" s="203"/>
       <c r="M68" s="186"/>
       <c r="N68" s="1"/>
     </row>
@@ -12303,24 +12325,24 @@
         <f ca="1">IFERROR(MID(IF(('Input Data'!AD9&gt;TODAY())*('Input Data'!AE9&gt;0),", "&amp;'Input Data'!AF9&amp;" ("&amp;'Input Data'!C9&amp;")","")&amp;IF(('Input Data'!AD10&gt;TODAY())*('Input Data'!AE10&gt;0),", "&amp;'Input Data'!AF10&amp;" ("&amp;'Input Data'!C10&amp;")","")&amp;IF(('Input Data'!AD11&gt;TODAY())*('Input Data'!AE11&gt;0),", "&amp;'Input Data'!AF11&amp;" ("&amp;'Input Data'!C11&amp;")","")&amp;IF(('Input Data'!AD20&gt;TODAY())*('Input Data'!AE20&gt;0),", "&amp;'Input Data'!AF20&amp;" ("&amp;'Input Data'!C20&amp;")",""),3,999),"—")</f>
         <v>Sungrow (L6) (6.02), Keeping Company (6.03), Elekta (6.04), Caladas Constructions (6.01)</v>
       </c>
-      <c r="D69" s="190"/>
-      <c r="E69" s="207">
+      <c r="D69" s="191"/>
+      <c r="E69" s="212">
         <f>SUMPRODUCT(('Input Data'!B3:B24="L06")*'Input Data'!F3:F24)</f>
         <v>1095.4000000000001</v>
       </c>
-      <c r="F69" s="190"/>
+      <c r="F69" s="191"/>
       <c r="G69" s="201">
         <f ca="1">SUMPRODUCT(('Input Data'!B3:B24="L06")*('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!Q3:Q24)</f>
         <v>307681.48800000001</v>
       </c>
-      <c r="H69" s="190"/>
-      <c r="I69" s="219"/>
+      <c r="H69" s="191"/>
+      <c r="I69" s="205"/>
       <c r="J69" s="186"/>
       <c r="K69" s="86" t="str">
         <f ca="1">IFERROR(IF(SUMPRODUCT(('Input Data'!B3:B24="L06")*('Input Data'!AE3:AE24&gt;0)*('Input Data'!AD3:AD24&gt;TODAY()))=0,"VACANT",TEXT(_xludf.minifs('Input Data'!AD3:AD24,'Input Data'!B3:B24,"L06",'Input Data'!AD3:AD24,"&gt;"&amp;TODAY(),'Input Data'!AE3:AE24,"&gt;0"),"YYYY")),"—")</f>
         <v>—</v>
       </c>
-      <c r="L69" s="206"/>
+      <c r="L69" s="203"/>
       <c r="M69" s="186"/>
       <c r="N69" s="100"/>
     </row>
@@ -12333,24 +12355,24 @@
         <f ca="1">IFERROR(MID(IF(('Input Data'!AD6&gt;TODAY())*('Input Data'!AE6&gt;0),", "&amp;'Input Data'!AF6&amp;" ("&amp;'Input Data'!C6&amp;")","")&amp;IF(('Input Data'!AD7&gt;TODAY())*('Input Data'!AE7&gt;0),", "&amp;'Input Data'!AF7&amp;" ("&amp;'Input Data'!C7&amp;")","")&amp;IF(('Input Data'!AD8&gt;TODAY())*('Input Data'!AE8&gt;0),", "&amp;'Input Data'!AF8&amp;" ("&amp;'Input Data'!C8&amp;")",""),3,999),"—")</f>
         <v>Fitness First N. Sydney (5.01), Asterx (MediRecords) (5.03), Auctionsplus (5.04)</v>
       </c>
-      <c r="D70" s="190"/>
-      <c r="E70" s="207">
+      <c r="D70" s="191"/>
+      <c r="E70" s="212">
         <f>SUMPRODUCT(('Input Data'!B3:B24="L05")*'Input Data'!F3:F24)</f>
         <v>1080.4000000000001</v>
       </c>
-      <c r="F70" s="190"/>
+      <c r="F70" s="191"/>
       <c r="G70" s="201">
         <f ca="1">SUMPRODUCT(('Input Data'!B3:B24="L05")*('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!Q3:Q24)</f>
         <v>958919.05300000007</v>
       </c>
-      <c r="H70" s="190"/>
-      <c r="I70" s="219"/>
+      <c r="H70" s="191"/>
+      <c r="I70" s="205"/>
       <c r="J70" s="186"/>
       <c r="K70" s="86" t="str">
         <f ca="1">IFERROR(IF(SUMPRODUCT(('Input Data'!B3:B24="L05")*('Input Data'!AE3:AE24&gt;0)*('Input Data'!AD3:AD24&gt;TODAY()))=0,"VACANT",TEXT(_xludf.minifs('Input Data'!AD3:AD24,'Input Data'!B3:B24,"L05",'Input Data'!AD3:AD24,"&gt;"&amp;TODAY(),'Input Data'!AE3:AE24,"&gt;0"),"YYYY")),"—")</f>
         <v>—</v>
       </c>
-      <c r="L70" s="206"/>
+      <c r="L70" s="203"/>
       <c r="M70" s="186"/>
       <c r="N70" s="1"/>
     </row>
@@ -12363,24 +12385,24 @@
         <f ca="1">IFERROR(MID(IF(('Input Data'!AD5&gt;TODAY())*('Input Data'!AE5&gt;0),", "&amp;'Input Data'!AF5&amp;" ("&amp;'Input Data'!C5&amp;")",""),3,999),"—")</f>
         <v>Fitness First (L4) (4.01)</v>
       </c>
-      <c r="D71" s="190"/>
-      <c r="E71" s="207">
+      <c r="D71" s="191"/>
+      <c r="E71" s="212">
         <f>SUMPRODUCT(('Input Data'!B3:B24="L04")*'Input Data'!F3:F24)</f>
         <v>1047</v>
       </c>
-      <c r="F71" s="190"/>
+      <c r="F71" s="191"/>
       <c r="G71" s="201">
         <f ca="1">SUMPRODUCT(('Input Data'!B3:B24="L04")*('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!Q3:Q24)</f>
         <v>906078.3</v>
       </c>
-      <c r="H71" s="190"/>
-      <c r="I71" s="219"/>
+      <c r="H71" s="191"/>
+      <c r="I71" s="205"/>
       <c r="J71" s="186"/>
       <c r="K71" s="86" t="str">
         <f ca="1">IFERROR(IF(SUMPRODUCT(('Input Data'!B3:B24="L04")*('Input Data'!AE3:AE24&gt;0)*('Input Data'!AD3:AD24&gt;TODAY()))=0,"VACANT",TEXT(_xludf.minifs('Input Data'!AD3:AD24,'Input Data'!B3:B24,"L04",'Input Data'!AD3:AD24,"&gt;"&amp;TODAY(),'Input Data'!AE3:AE24,"&gt;0"),"YYYY")),"—")</f>
         <v>—</v>
       </c>
-      <c r="L71" s="206"/>
+      <c r="L71" s="203"/>
       <c r="M71" s="186"/>
       <c r="N71" s="100"/>
     </row>
@@ -12393,24 +12415,24 @@
         <f ca="1">IFERROR(MID(IF(('Input Data'!AD3&gt;TODAY())*('Input Data'!AE3&gt;0),", "&amp;'Input Data'!AF3&amp;" ("&amp;'Input Data'!C3&amp;")","")&amp;IF(('Input Data'!AD4&gt;TODAY())*('Input Data'!AE4&gt;0),", "&amp;'Input Data'!AF4&amp;" ("&amp;'Input Data'!C4&amp;")",""),3,999),"—")</f>
         <v>Sydney Smiletree (3.01), Fitness First (L3) (3.02)</v>
       </c>
-      <c r="D72" s="190"/>
-      <c r="E72" s="207">
+      <c r="D72" s="191"/>
+      <c r="E72" s="212">
         <f>SUMPRODUCT(('Input Data'!B3:B24="L03")*'Input Data'!F3:F24)</f>
         <v>903.2</v>
       </c>
-      <c r="F72" s="190"/>
+      <c r="F72" s="191"/>
       <c r="G72" s="201">
         <f ca="1">SUMPRODUCT(('Input Data'!B3:B24="L03")*('Input Data'!AD3:AD24&gt;TODAY())*('Input Data'!AE3:AE24&gt;0)*'Input Data'!Q3:Q24)</f>
         <v>844228.81500000006</v>
       </c>
-      <c r="H72" s="190"/>
-      <c r="I72" s="219"/>
+      <c r="H72" s="191"/>
+      <c r="I72" s="205"/>
       <c r="J72" s="186"/>
       <c r="K72" s="86" t="str">
         <f ca="1">IFERROR(IF(SUMPRODUCT(('Input Data'!B3:B24="L03")*('Input Data'!AE3:AE24&gt;0)*('Input Data'!AD3:AD24&gt;TODAY()))=0,"VACANT",TEXT(_xludf.minifs('Input Data'!AD3:AD24,'Input Data'!B3:B24,"L03",'Input Data'!AD3:AD24,"&gt;"&amp;TODAY(),'Input Data'!AE3:AE24,"&gt;0"),"YYYY")),"—")</f>
         <v>—</v>
       </c>
-      <c r="L72" s="206"/>
+      <c r="L72" s="203"/>
       <c r="M72" s="186"/>
       <c r="N72" s="1"/>
     </row>
@@ -12421,17 +12443,17 @@
       </c>
       <c r="C73" s="183"/>
       <c r="D73" s="183"/>
-      <c r="E73" s="215">
+      <c r="E73" s="256">
         <f>SUM('Input Data'!F3:F24)</f>
-        <v>8922.4000000000015</v>
+        <v>8940.9000000000015</v>
       </c>
       <c r="F73" s="183"/>
-      <c r="G73" s="249">
+      <c r="G73" s="224">
         <f>SUM('Input Data'!Q3:Q24)</f>
-        <v>5377867.9789999994</v>
+        <v>5390347.9789999994</v>
       </c>
       <c r="H73" s="183"/>
-      <c r="I73" s="228" t="s">
+      <c r="I73" s="251" t="s">
         <v>316</v>
       </c>
       <c r="J73" s="183"/>
@@ -12458,7 +12480,7 @@
     </row>
     <row r="75" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="100"/>
-      <c r="B75" s="237" t="s">
+      <c r="B75" s="246" t="s">
         <v>317</v>
       </c>
       <c r="C75" s="183"/>
@@ -12476,21 +12498,21 @@
     </row>
     <row r="76" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="6"/>
-      <c r="B76" s="204"/>
+      <c r="B76" s="211"/>
       <c r="C76" s="183"/>
       <c r="D76" s="183"/>
       <c r="E76" s="101" t="s">
         <v>318</v>
       </c>
-      <c r="F76" s="204" t="s">
+      <c r="F76" s="211" t="s">
         <v>319</v>
       </c>
       <c r="G76" s="183"/>
-      <c r="H76" s="204" t="s">
+      <c r="H76" s="211" t="s">
         <v>320</v>
       </c>
       <c r="I76" s="183"/>
-      <c r="J76" s="204" t="s">
+      <c r="J76" s="211" t="s">
         <v>321</v>
       </c>
       <c r="K76" s="183"/>
@@ -12500,11 +12522,11 @@
     </row>
     <row r="77" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="6"/>
-      <c r="B77" s="224" t="s">
+      <c r="B77" s="204" t="s">
         <v>322</v>
       </c>
-      <c r="C77" s="190"/>
-      <c r="D77" s="190"/>
+      <c r="C77" s="191"/>
+      <c r="D77" s="191"/>
       <c r="E77" s="103">
         <f>Valuations!C6</f>
         <v>0</v>
@@ -12513,155 +12535,155 @@
         <f>Valuations!D6</f>
         <v>0</v>
       </c>
-      <c r="G77" s="190"/>
+      <c r="G77" s="191"/>
       <c r="H77" s="201">
         <f>Valuations!E6</f>
         <v>0</v>
       </c>
-      <c r="I77" s="190"/>
-      <c r="J77" s="203">
+      <c r="I77" s="191"/>
+      <c r="J77" s="234">
         <f>IFERROR(E77-G77,"")</f>
         <v>0</v>
       </c>
-      <c r="K77" s="190"/>
-      <c r="L77" s="205" t="str">
+      <c r="K77" s="191"/>
+      <c r="L77" s="217" t="str">
         <f>IFERROR((E77-G77)/G77,"")</f>
         <v/>
       </c>
-      <c r="M77" s="190"/>
+      <c r="M77" s="191"/>
       <c r="N77" s="6"/>
     </row>
     <row r="78" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="6"/>
-      <c r="B78" s="224" t="s">
+      <c r="B78" s="204" t="s">
         <v>323</v>
       </c>
-      <c r="C78" s="190"/>
-      <c r="D78" s="190"/>
+      <c r="C78" s="191"/>
+      <c r="D78" s="191"/>
       <c r="E78" s="105">
         <f>Valuations!C7</f>
         <v>0</v>
       </c>
-      <c r="F78" s="253">
+      <c r="F78" s="207">
         <f>Valuations!D7</f>
         <v>0</v>
       </c>
-      <c r="G78" s="190"/>
-      <c r="H78" s="253">
+      <c r="G78" s="191"/>
+      <c r="H78" s="207">
         <f>Valuations!E7</f>
         <v>0</v>
       </c>
-      <c r="I78" s="190"/>
-      <c r="J78" s="239" t="s">
+      <c r="I78" s="191"/>
+      <c r="J78" s="206" t="s">
         <v>178</v>
       </c>
-      <c r="K78" s="190"/>
-      <c r="L78" s="190"/>
-      <c r="M78" s="190"/>
+      <c r="K78" s="191"/>
+      <c r="L78" s="191"/>
+      <c r="M78" s="191"/>
       <c r="N78" s="6"/>
     </row>
     <row r="79" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="6"/>
-      <c r="B79" s="224" t="s">
+      <c r="B79" s="204" t="s">
         <v>324</v>
       </c>
-      <c r="C79" s="190"/>
-      <c r="D79" s="190"/>
+      <c r="C79" s="191"/>
+      <c r="D79" s="191"/>
       <c r="E79" s="83">
         <f>Valuations!C8</f>
         <v>0</v>
       </c>
-      <c r="F79" s="221">
+      <c r="F79" s="232">
         <f>Valuations!D8</f>
         <v>0</v>
       </c>
-      <c r="G79" s="190"/>
-      <c r="H79" s="221">
+      <c r="G79" s="191"/>
+      <c r="H79" s="232">
         <f>Valuations!E8</f>
         <v>0</v>
       </c>
-      <c r="I79" s="190"/>
-      <c r="J79" s="239" t="s">
+      <c r="I79" s="191"/>
+      <c r="J79" s="206" t="s">
         <v>178</v>
       </c>
-      <c r="K79" s="190"/>
-      <c r="L79" s="190"/>
-      <c r="M79" s="190"/>
+      <c r="K79" s="191"/>
+      <c r="L79" s="191"/>
+      <c r="M79" s="191"/>
       <c r="N79" s="6"/>
     </row>
     <row r="80" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="6"/>
-      <c r="B80" s="224" t="s">
+      <c r="B80" s="204" t="s">
         <v>325</v>
       </c>
-      <c r="C80" s="190"/>
-      <c r="D80" s="190"/>
+      <c r="C80" s="191"/>
+      <c r="D80" s="191"/>
       <c r="E80" s="106">
         <f>Valuations!C10</f>
         <v>0</v>
       </c>
-      <c r="F80" s="216">
+      <c r="F80" s="245">
         <f>Valuations!D10</f>
         <v>0</v>
       </c>
-      <c r="G80" s="190"/>
-      <c r="H80" s="216">
+      <c r="G80" s="191"/>
+      <c r="H80" s="245">
         <f>Valuations!E10</f>
         <v>0</v>
       </c>
-      <c r="I80" s="190"/>
-      <c r="J80" s="243">
+      <c r="I80" s="191"/>
+      <c r="J80" s="258">
         <f>IFERROR(E80-G80,"")</f>
         <v>0</v>
       </c>
-      <c r="K80" s="190"/>
-      <c r="L80" s="205" t="str">
+      <c r="K80" s="191"/>
+      <c r="L80" s="217" t="str">
         <f>IFERROR((E80-G80)/G80,"")</f>
         <v/>
       </c>
-      <c r="M80" s="190"/>
+      <c r="M80" s="191"/>
       <c r="N80" s="6"/>
     </row>
     <row r="81" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="6"/>
-      <c r="B81" s="224" t="s">
+      <c r="B81" s="204" t="s">
         <v>326</v>
       </c>
-      <c r="C81" s="190"/>
-      <c r="D81" s="190"/>
+      <c r="C81" s="191"/>
+      <c r="D81" s="191"/>
       <c r="E81" s="106">
         <f>Valuations!C11</f>
         <v>0</v>
       </c>
-      <c r="F81" s="216">
+      <c r="F81" s="245">
         <f>Valuations!D11</f>
         <v>0</v>
       </c>
-      <c r="G81" s="190"/>
-      <c r="H81" s="216">
+      <c r="G81" s="191"/>
+      <c r="H81" s="245">
         <f>Valuations!E11</f>
         <v>0</v>
       </c>
-      <c r="I81" s="190"/>
-      <c r="J81" s="243">
+      <c r="I81" s="191"/>
+      <c r="J81" s="258">
         <f>IFERROR(E81-G81,"")</f>
         <v>0</v>
       </c>
-      <c r="K81" s="190"/>
-      <c r="L81" s="205" t="str">
+      <c r="K81" s="191"/>
+      <c r="L81" s="217" t="str">
         <f>IFERROR((E81-G81)/G81,"")</f>
         <v/>
       </c>
-      <c r="M81" s="190"/>
+      <c r="M81" s="191"/>
       <c r="N81" s="6"/>
     </row>
     <row r="82" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="6"/>
-      <c r="B82" s="224" t="s">
+      <c r="B82" s="204" t="s">
         <v>327</v>
       </c>
-      <c r="C82" s="190"/>
-      <c r="D82" s="190"/>
+      <c r="C82" s="191"/>
+      <c r="D82" s="191"/>
       <c r="E82" s="80">
         <f>Valuations!C12</f>
         <v>0</v>
@@ -12670,51 +12692,51 @@
         <f>Valuations!D12</f>
         <v>0</v>
       </c>
-      <c r="G82" s="190"/>
+      <c r="G82" s="191"/>
       <c r="H82" s="201">
         <f>Valuations!E12</f>
         <v>0</v>
       </c>
-      <c r="I82" s="190"/>
-      <c r="J82" s="203">
+      <c r="I82" s="191"/>
+      <c r="J82" s="234">
         <f>IFERROR(E82-G82,"")</f>
         <v>0</v>
       </c>
-      <c r="K82" s="190"/>
-      <c r="L82" s="205" t="str">
+      <c r="K82" s="191"/>
+      <c r="L82" s="217" t="str">
         <f>IFERROR((E82-G82)/G82,"")</f>
         <v/>
       </c>
-      <c r="M82" s="190"/>
+      <c r="M82" s="191"/>
       <c r="N82" s="6"/>
     </row>
     <row r="83" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="6"/>
-      <c r="B83" s="224" t="s">
+      <c r="B83" s="204" t="s">
         <v>328</v>
       </c>
-      <c r="C83" s="190"/>
-      <c r="D83" s="190"/>
+      <c r="C83" s="191"/>
+      <c r="D83" s="191"/>
       <c r="E83" s="83">
         <f>Valuations!C9</f>
         <v>0</v>
       </c>
-      <c r="F83" s="221">
+      <c r="F83" s="232">
         <f>Valuations!D9</f>
         <v>0</v>
       </c>
-      <c r="G83" s="190"/>
-      <c r="H83" s="221">
+      <c r="G83" s="191"/>
+      <c r="H83" s="232">
         <f>Valuations!E9</f>
         <v>0</v>
       </c>
-      <c r="I83" s="190"/>
-      <c r="J83" s="239" t="s">
+      <c r="I83" s="191"/>
+      <c r="J83" s="206" t="s">
         <v>178</v>
       </c>
-      <c r="K83" s="190"/>
-      <c r="L83" s="190"/>
-      <c r="M83" s="190"/>
+      <c r="K83" s="191"/>
+      <c r="L83" s="191"/>
+      <c r="M83" s="191"/>
       <c r="N83" s="6"/>
     </row>
     <row r="84" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -12735,7 +12757,7 @@
     </row>
     <row r="85" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="6"/>
-      <c r="B85" s="199" t="s">
+      <c r="B85" s="189" t="s">
         <v>329</v>
       </c>
       <c r="C85" s="183"/>
@@ -12753,21 +12775,21 @@
     </row>
     <row r="86" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="6"/>
-      <c r="B86" s="204"/>
+      <c r="B86" s="211"/>
       <c r="C86" s="183"/>
       <c r="D86" s="183"/>
       <c r="E86" s="101" t="s">
         <v>330</v>
       </c>
-      <c r="F86" s="204" t="s">
+      <c r="F86" s="211" t="s">
         <v>331</v>
       </c>
       <c r="G86" s="183"/>
-      <c r="H86" s="204" t="s">
+      <c r="H86" s="211" t="s">
         <v>332</v>
       </c>
       <c r="I86" s="183"/>
-      <c r="J86" s="204" t="s">
+      <c r="J86" s="211" t="s">
         <v>333</v>
       </c>
       <c r="K86" s="183"/>
@@ -12777,40 +12799,40 @@
     </row>
     <row r="87" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="6"/>
-      <c r="B87" s="224" t="s">
+      <c r="B87" s="204" t="s">
         <v>334</v>
       </c>
-      <c r="C87" s="190"/>
-      <c r="D87" s="190"/>
+      <c r="C87" s="191"/>
+      <c r="D87" s="191"/>
       <c r="E87" s="83">
         <f>Valuations!C20</f>
         <v>0</v>
       </c>
-      <c r="F87" s="221">
+      <c r="F87" s="232">
         <f>Valuations!D20</f>
         <v>0</v>
       </c>
-      <c r="G87" s="190"/>
-      <c r="H87" s="221">
+      <c r="G87" s="191"/>
+      <c r="H87" s="232">
         <f>Valuations!E20</f>
         <v>0</v>
       </c>
-      <c r="I87" s="190"/>
-      <c r="J87" s="232" t="s">
+      <c r="I87" s="191"/>
+      <c r="J87" s="208" t="s">
         <v>178</v>
       </c>
-      <c r="K87" s="190"/>
-      <c r="L87" s="190"/>
-      <c r="M87" s="190"/>
+      <c r="K87" s="191"/>
+      <c r="L87" s="191"/>
+      <c r="M87" s="191"/>
       <c r="N87" s="6"/>
     </row>
     <row r="88" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="6"/>
-      <c r="B88" s="224" t="s">
+      <c r="B88" s="204" t="s">
         <v>335</v>
       </c>
-      <c r="C88" s="190"/>
-      <c r="D88" s="190"/>
+      <c r="C88" s="191"/>
+      <c r="D88" s="191"/>
       <c r="E88" s="103">
         <f>Valuations!C21</f>
         <v>0</v>
@@ -12819,31 +12841,31 @@
         <f>Valuations!D21</f>
         <v>0</v>
       </c>
-      <c r="G88" s="190"/>
+      <c r="G88" s="191"/>
       <c r="H88" s="201">
         <f>Valuations!E21</f>
         <v>0</v>
       </c>
-      <c r="I88" s="190"/>
-      <c r="J88" s="203">
+      <c r="I88" s="191"/>
+      <c r="J88" s="234">
         <f>IFERROR(E88-G88,"")</f>
         <v>0</v>
       </c>
-      <c r="K88" s="190"/>
-      <c r="L88" s="205" t="str">
+      <c r="K88" s="191"/>
+      <c r="L88" s="217" t="str">
         <f>IFERROR((E88-G88)/G88,"")</f>
         <v/>
       </c>
-      <c r="M88" s="190"/>
+      <c r="M88" s="191"/>
       <c r="N88" s="6"/>
     </row>
     <row r="89" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="6"/>
-      <c r="B89" s="224" t="s">
+      <c r="B89" s="204" t="s">
         <v>336</v>
       </c>
-      <c r="C89" s="190"/>
-      <c r="D89" s="190"/>
+      <c r="C89" s="191"/>
+      <c r="D89" s="191"/>
       <c r="E89" s="80">
         <f>Valuations!C22</f>
         <v>0</v>
@@ -12852,51 +12874,51 @@
         <f>Valuations!D22</f>
         <v>0</v>
       </c>
-      <c r="G89" s="190"/>
+      <c r="G89" s="191"/>
       <c r="H89" s="201">
         <f>Valuations!E22</f>
         <v>0</v>
       </c>
-      <c r="I89" s="190"/>
-      <c r="J89" s="203">
+      <c r="I89" s="191"/>
+      <c r="J89" s="234">
         <f>IFERROR(E89-G89,"")</f>
         <v>0</v>
       </c>
-      <c r="K89" s="190"/>
-      <c r="L89" s="205" t="str">
+      <c r="K89" s="191"/>
+      <c r="L89" s="217" t="str">
         <f>IFERROR((E89-G89)/G89,"")</f>
         <v/>
       </c>
-      <c r="M89" s="190"/>
+      <c r="M89" s="191"/>
       <c r="N89" s="6"/>
     </row>
     <row r="90" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="6"/>
-      <c r="B90" s="224" t="s">
+      <c r="B90" s="204" t="s">
         <v>337</v>
       </c>
-      <c r="C90" s="190"/>
-      <c r="D90" s="190"/>
+      <c r="C90" s="191"/>
+      <c r="D90" s="191"/>
       <c r="E90" s="105">
         <f>Valuations!C23</f>
         <v>0</v>
       </c>
-      <c r="F90" s="253">
+      <c r="F90" s="207">
         <f>Valuations!D23</f>
         <v>0</v>
       </c>
-      <c r="G90" s="190"/>
-      <c r="H90" s="253">
+      <c r="G90" s="191"/>
+      <c r="H90" s="207">
         <f>Valuations!E23</f>
         <v>0</v>
       </c>
-      <c r="I90" s="190"/>
-      <c r="J90" s="232" t="s">
+      <c r="I90" s="191"/>
+      <c r="J90" s="208" t="s">
         <v>178</v>
       </c>
-      <c r="K90" s="190"/>
-      <c r="L90" s="190"/>
-      <c r="M90" s="190"/>
+      <c r="K90" s="191"/>
+      <c r="L90" s="191"/>
+      <c r="M90" s="191"/>
       <c r="N90" s="6"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.35">
@@ -12917,24 +12939,252 @@
     </row>
     <row r="92" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="6"/>
-      <c r="B92" s="220" t="s">
+      <c r="B92" s="248" t="s">
         <v>338</v>
       </c>
-      <c r="C92" s="190"/>
-      <c r="D92" s="190"/>
-      <c r="E92" s="190"/>
-      <c r="F92" s="190"/>
-      <c r="G92" s="190"/>
-      <c r="H92" s="190"/>
-      <c r="I92" s="190"/>
-      <c r="J92" s="190"/>
-      <c r="K92" s="190"/>
-      <c r="L92" s="190"/>
-      <c r="M92" s="190"/>
+      <c r="C92" s="191"/>
+      <c r="D92" s="191"/>
+      <c r="E92" s="191"/>
+      <c r="F92" s="191"/>
+      <c r="G92" s="191"/>
+      <c r="H92" s="191"/>
+      <c r="I92" s="191"/>
+      <c r="J92" s="191"/>
+      <c r="K92" s="191"/>
+      <c r="L92" s="191"/>
+      <c r="M92" s="191"/>
       <c r="N92" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="252">
+    <mergeCell ref="H82:I82"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="J82:K82"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="L82:M82"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="J76:M76"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="J42:M42"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="L71:M71"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="G59:M59"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="J44:M44"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="I71:J71"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="L81:M81"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="J86:M86"/>
+    <mergeCell ref="G49:M49"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B92:M92"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="H79:I79"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="G48:M48"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="I73:M73"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="L72:M72"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B17:M17"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="J88:K88"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="H80:I80"/>
+    <mergeCell ref="B75:M75"/>
+    <mergeCell ref="J83:M83"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="B46:M46"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="L80:M80"/>
+    <mergeCell ref="J90:M90"/>
+    <mergeCell ref="G50:M50"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="H83:I83"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="F15:M15"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="G52:M52"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="B85:M85"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="F13:M13"/>
+    <mergeCell ref="L69:M69"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="L70:M70"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="G55:M55"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F14:M14"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="G51:M51"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="G54:M54"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="G56:M56"/>
+    <mergeCell ref="J89:K89"/>
+    <mergeCell ref="L89:M89"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="L88:M88"/>
+    <mergeCell ref="J40:M40"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="G53:M53"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="G58:M58"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B12:M12"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="B61:M61"/>
+    <mergeCell ref="G47:M47"/>
     <mergeCell ref="H88:I88"/>
     <mergeCell ref="J37:M37"/>
     <mergeCell ref="L64:M64"/>
@@ -12959,234 +13209,6 @@
     <mergeCell ref="B50:C50"/>
     <mergeCell ref="J41:M41"/>
     <mergeCell ref="G72:H72"/>
-    <mergeCell ref="H86:I86"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="G58:M58"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B12:M12"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="B61:M61"/>
-    <mergeCell ref="G47:M47"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="G53:M53"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="G51:M51"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="G54:M54"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="G56:M56"/>
-    <mergeCell ref="J89:K89"/>
-    <mergeCell ref="L89:M89"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="L88:M88"/>
-    <mergeCell ref="J40:M40"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="L70:M70"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="G55:M55"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F14:M14"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="J90:M90"/>
-    <mergeCell ref="G50:M50"/>
-    <mergeCell ref="I70:J70"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="F83:G83"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="H83:I83"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="F15:M15"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="G52:M52"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="B85:M85"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="F13:M13"/>
-    <mergeCell ref="L69:M69"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B17:M17"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="J88:K88"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="B75:M75"/>
-    <mergeCell ref="J83:M83"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="B46:M46"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="L80:M80"/>
-    <mergeCell ref="B92:M92"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="H79:I79"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="G48:M48"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="I73:M73"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="L72:M72"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="G59:M59"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="J44:M44"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="I71:J71"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="L81:M81"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="J86:M86"/>
-    <mergeCell ref="G49:M49"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="I69:J69"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="J42:M42"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="L71:M71"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="H82:I82"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="J82:K82"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="L82:M82"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="J76:M76"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="J80:K80"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -13222,16 +13244,16 @@
       <c r="H1" s="183"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="266" t="s">
+      <c r="A2" s="265" t="s">
         <v>340</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="190"/>
-      <c r="D2" s="190"/>
-      <c r="E2" s="190"/>
-      <c r="F2" s="190"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="190"/>
+      <c r="B2" s="191"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
     </row>
     <row r="3" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
@@ -13245,7 +13267,7 @@
     </row>
     <row r="4" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="246" t="s">
         <v>341</v>
       </c>
       <c r="C4" s="183"/>
@@ -13267,7 +13289,7 @@
       <c r="E5" s="101" t="s">
         <v>344</v>
       </c>
-      <c r="F5" s="204" t="s">
+      <c r="F5" s="211" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="183"/>
@@ -13281,7 +13303,7 @@
       <c r="C6" s="107"/>
       <c r="D6" s="107"/>
       <c r="E6" s="107"/>
-      <c r="F6" s="200"/>
+      <c r="F6" s="193"/>
       <c r="G6" s="186"/>
       <c r="H6" s="6"/>
     </row>
@@ -13293,7 +13315,7 @@
       <c r="C7" s="57"/>
       <c r="D7" s="57"/>
       <c r="E7" s="57"/>
-      <c r="F7" s="259"/>
+      <c r="F7" s="260"/>
       <c r="G7" s="186"/>
       <c r="H7" s="6"/>
     </row>
@@ -13305,7 +13327,7 @@
       <c r="C8" s="108"/>
       <c r="D8" s="108"/>
       <c r="E8" s="108"/>
-      <c r="F8" s="200"/>
+      <c r="F8" s="193"/>
       <c r="G8" s="186"/>
       <c r="H8" s="6"/>
     </row>
@@ -13317,7 +13339,7 @@
       <c r="C9" s="109"/>
       <c r="D9" s="109"/>
       <c r="E9" s="109"/>
-      <c r="F9" s="259"/>
+      <c r="F9" s="260"/>
       <c r="G9" s="186"/>
       <c r="H9" s="6"/>
     </row>
@@ -13329,7 +13351,7 @@
       <c r="C10" s="110"/>
       <c r="D10" s="110"/>
       <c r="E10" s="110"/>
-      <c r="F10" s="200"/>
+      <c r="F10" s="193"/>
       <c r="G10" s="186"/>
       <c r="H10" s="6"/>
     </row>
@@ -13341,7 +13363,7 @@
       <c r="C11" s="111"/>
       <c r="D11" s="111"/>
       <c r="E11" s="111"/>
-      <c r="F11" s="259"/>
+      <c r="F11" s="260"/>
       <c r="G11" s="186"/>
       <c r="H11" s="6"/>
     </row>
@@ -13353,7 +13375,7 @@
       <c r="C12" s="107"/>
       <c r="D12" s="107"/>
       <c r="E12" s="107"/>
-      <c r="F12" s="200"/>
+      <c r="F12" s="193"/>
       <c r="G12" s="186"/>
       <c r="H12" s="6"/>
     </row>
@@ -13365,13 +13387,13 @@
       <c r="C13" s="112"/>
       <c r="D13" s="112"/>
       <c r="E13" s="112"/>
-      <c r="F13" s="259"/>
+      <c r="F13" s="260"/>
       <c r="G13" s="186"/>
       <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
-      <c r="B14" s="260" t="s">
+      <c r="B14" s="268" t="s">
         <v>350</v>
       </c>
       <c r="C14" s="183"/>
@@ -13386,16 +13408,16 @@
       <c r="B15" s="21" t="s">
         <v>351</v>
       </c>
-      <c r="C15" s="203">
+      <c r="C15" s="234">
         <f>IFERROR(C6-D6,"")</f>
         <v>0</v>
       </c>
-      <c r="D15" s="190"/>
+      <c r="D15" s="191"/>
       <c r="E15" s="104" t="str">
         <f>IFERROR((C6-D6)/D6,"")</f>
         <v/>
       </c>
-      <c r="F15" s="261"/>
+      <c r="F15" s="267"/>
       <c r="G15" s="186"/>
       <c r="H15" s="6"/>
     </row>
@@ -13404,16 +13426,16 @@
       <c r="B16" s="33" t="s">
         <v>352</v>
       </c>
-      <c r="C16" s="203">
+      <c r="C16" s="234">
         <f>IFERROR(D6-E6,"")</f>
         <v>0</v>
       </c>
-      <c r="D16" s="190"/>
+      <c r="D16" s="191"/>
       <c r="E16" s="104" t="str">
         <f>IFERROR((D6-E6)/E6,"")</f>
         <v/>
       </c>
-      <c r="F16" s="261"/>
+      <c r="F16" s="267"/>
       <c r="G16" s="186"/>
       <c r="H16" s="6"/>
     </row>
@@ -13429,7 +13451,7 @@
     </row>
     <row r="18" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6"/>
-      <c r="B18" s="237" t="s">
+      <c r="B18" s="246" t="s">
         <v>353</v>
       </c>
       <c r="C18" s="183"/>
@@ -13451,7 +13473,7 @@
       <c r="E19" s="101" t="s">
         <v>332</v>
       </c>
-      <c r="F19" s="204" t="s">
+      <c r="F19" s="211" t="s">
         <v>28</v>
       </c>
       <c r="G19" s="183"/>
@@ -13465,7 +13487,7 @@
       <c r="C20" s="108"/>
       <c r="D20" s="108"/>
       <c r="E20" s="108"/>
-      <c r="F20" s="200"/>
+      <c r="F20" s="193"/>
       <c r="G20" s="186"/>
       <c r="H20" s="6"/>
     </row>
@@ -13477,7 +13499,7 @@
       <c r="C21" s="112"/>
       <c r="D21" s="112"/>
       <c r="E21" s="112"/>
-      <c r="F21" s="259"/>
+      <c r="F21" s="260"/>
       <c r="G21" s="186"/>
       <c r="H21" s="6"/>
     </row>
@@ -13489,7 +13511,7 @@
       <c r="C22" s="107"/>
       <c r="D22" s="107"/>
       <c r="E22" s="107"/>
-      <c r="F22" s="200"/>
+      <c r="F22" s="193"/>
       <c r="G22" s="186"/>
       <c r="H22" s="6"/>
     </row>
@@ -13501,7 +13523,7 @@
       <c r="C23" s="57"/>
       <c r="D23" s="57"/>
       <c r="E23" s="57"/>
-      <c r="F23" s="259"/>
+      <c r="F23" s="260"/>
       <c r="G23" s="186"/>
       <c r="H23" s="6"/>
     </row>
@@ -13513,7 +13535,7 @@
       <c r="C24" s="107"/>
       <c r="D24" s="107"/>
       <c r="E24" s="107"/>
-      <c r="F24" s="200"/>
+      <c r="F24" s="193"/>
       <c r="G24" s="186"/>
       <c r="H24" s="6"/>
     </row>
@@ -13525,7 +13547,7 @@
       <c r="C25" s="115"/>
       <c r="D25" s="115"/>
       <c r="E25" s="115"/>
-      <c r="F25" s="259"/>
+      <c r="F25" s="260"/>
       <c r="G25" s="186"/>
       <c r="H25" s="6"/>
     </row>
@@ -13537,7 +13559,7 @@
       <c r="C26" s="58"/>
       <c r="D26" s="58"/>
       <c r="E26" s="58"/>
-      <c r="F26" s="200"/>
+      <c r="F26" s="193"/>
       <c r="G26" s="186"/>
       <c r="H26" s="6"/>
     </row>
@@ -13549,7 +13571,7 @@
       <c r="C27" s="109"/>
       <c r="D27" s="109"/>
       <c r="E27" s="109"/>
-      <c r="F27" s="259"/>
+      <c r="F27" s="260"/>
       <c r="G27" s="186"/>
       <c r="H27" s="6"/>
     </row>
@@ -13565,7 +13587,7 @@
     </row>
     <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="6"/>
-      <c r="B29" s="260" t="s">
+      <c r="B29" s="268" t="s">
         <v>359</v>
       </c>
       <c r="C29" s="183"/>
@@ -13580,16 +13602,16 @@
       <c r="B30" s="21" t="s">
         <v>360</v>
       </c>
-      <c r="C30" s="203">
+      <c r="C30" s="234">
         <f>IFERROR(C21-D21,"")</f>
         <v>0</v>
       </c>
-      <c r="D30" s="190"/>
+      <c r="D30" s="191"/>
       <c r="E30" s="104" t="str">
         <f>IFERROR((C21-D21)/D21,"")</f>
         <v/>
       </c>
-      <c r="F30" s="261"/>
+      <c r="F30" s="267"/>
       <c r="G30" s="186"/>
       <c r="H30" s="6"/>
     </row>
@@ -13598,16 +13620,16 @@
       <c r="B31" s="116" t="s">
         <v>361</v>
       </c>
-      <c r="C31" s="203">
+      <c r="C31" s="234">
         <f>IFERROR(D21-E21,"")</f>
         <v>0</v>
       </c>
-      <c r="D31" s="190"/>
+      <c r="D31" s="191"/>
       <c r="E31" s="104" t="str">
         <f>IFERROR((D21-E21)/E21,"")</f>
         <v/>
       </c>
-      <c r="F31" s="261"/>
+      <c r="F31" s="267"/>
       <c r="G31" s="186"/>
       <c r="H31" s="6"/>
     </row>
@@ -13623,7 +13645,7 @@
     </row>
     <row r="33" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6"/>
-      <c r="B33" s="237" t="s">
+      <c r="B33" s="246" t="s">
         <v>362</v>
       </c>
       <c r="C33" s="183"/>
@@ -13635,11 +13657,11 @@
     </row>
     <row r="34" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6"/>
-      <c r="B34" s="204" t="s">
+      <c r="B34" s="211" t="s">
         <v>363</v>
       </c>
       <c r="C34" s="183"/>
-      <c r="D34" s="204" t="s">
+      <c r="D34" s="211" t="s">
         <v>364</v>
       </c>
       <c r="E34" s="183"/>
@@ -13651,11 +13673,11 @@
     </row>
     <row r="35" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6"/>
-      <c r="B35" s="224" t="s">
+      <c r="B35" s="204" t="s">
         <v>366</v>
       </c>
-      <c r="C35" s="190"/>
-      <c r="D35" s="262"/>
+      <c r="C35" s="191"/>
+      <c r="D35" s="266"/>
       <c r="E35" s="186"/>
       <c r="F35" s="186"/>
       <c r="G35" s="109"/>
@@ -13663,11 +13685,11 @@
     </row>
     <row r="36" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6"/>
-      <c r="B36" s="224" t="s">
+      <c r="B36" s="204" t="s">
         <v>367</v>
       </c>
-      <c r="C36" s="190"/>
-      <c r="D36" s="269"/>
+      <c r="C36" s="191"/>
+      <c r="D36" s="262"/>
       <c r="E36" s="186"/>
       <c r="F36" s="186"/>
       <c r="G36" s="107"/>
@@ -13675,11 +13697,11 @@
     </row>
     <row r="37" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6"/>
-      <c r="B37" s="224" t="s">
+      <c r="B37" s="204" t="s">
         <v>368</v>
       </c>
-      <c r="C37" s="190"/>
-      <c r="D37" s="263"/>
+      <c r="C37" s="191"/>
+      <c r="D37" s="269"/>
       <c r="E37" s="186"/>
       <c r="F37" s="186"/>
       <c r="G37" s="57"/>
@@ -13687,11 +13709,11 @@
     </row>
     <row r="38" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6"/>
-      <c r="B38" s="224" t="s">
+      <c r="B38" s="204" t="s">
         <v>369</v>
       </c>
-      <c r="C38" s="190"/>
-      <c r="D38" s="265"/>
+      <c r="C38" s="191"/>
+      <c r="D38" s="264"/>
       <c r="E38" s="186"/>
       <c r="F38" s="186"/>
       <c r="G38" s="117"/>
@@ -13699,11 +13721,11 @@
     </row>
     <row r="39" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="6"/>
-      <c r="B39" s="224" t="s">
+      <c r="B39" s="204" t="s">
         <v>370</v>
       </c>
-      <c r="C39" s="190"/>
-      <c r="D39" s="262"/>
+      <c r="C39" s="191"/>
+      <c r="D39" s="266"/>
       <c r="E39" s="186"/>
       <c r="F39" s="186"/>
       <c r="G39" s="109"/>
@@ -13711,11 +13733,11 @@
     </row>
     <row r="40" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="6"/>
-      <c r="B40" s="224" t="s">
+      <c r="B40" s="204" t="s">
         <v>371</v>
       </c>
-      <c r="C40" s="190"/>
-      <c r="D40" s="268"/>
+      <c r="C40" s="191"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="186"/>
       <c r="F40" s="186"/>
       <c r="G40" s="58"/>
@@ -13723,26 +13745,26 @@
     </row>
     <row r="41" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6"/>
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="204" t="s">
         <v>372</v>
       </c>
-      <c r="C41" s="190"/>
-      <c r="D41" s="205" t="str">
+      <c r="C41" s="191"/>
+      <c r="D41" s="217" t="str">
         <f>IFERROR(D36/Valuations!C6,"")</f>
         <v/>
       </c>
-      <c r="E41" s="190"/>
-      <c r="F41" s="190"/>
+      <c r="E41" s="191"/>
+      <c r="F41" s="191"/>
       <c r="G41" s="118"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6"/>
-      <c r="B42" s="224" t="s">
+      <c r="B42" s="204" t="s">
         <v>373</v>
       </c>
-      <c r="C42" s="190"/>
-      <c r="D42" s="264"/>
+      <c r="C42" s="191"/>
+      <c r="D42" s="263"/>
       <c r="E42" s="186"/>
       <c r="F42" s="186"/>
       <c r="G42" s="119"/>
@@ -13750,11 +13772,11 @@
     </row>
     <row r="43" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6"/>
-      <c r="B43" s="224" t="s">
+      <c r="B43" s="204" t="s">
         <v>374</v>
       </c>
-      <c r="C43" s="190"/>
-      <c r="D43" s="262"/>
+      <c r="C43" s="191"/>
+      <c r="D43" s="266"/>
       <c r="E43" s="186"/>
       <c r="F43" s="186"/>
       <c r="G43" s="109"/>
@@ -13772,30 +13794,40 @@
     </row>
     <row r="45" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6"/>
-      <c r="B45" s="267" t="s">
+      <c r="B45" s="259" t="s">
         <v>375</v>
       </c>
-      <c r="C45" s="190"/>
-      <c r="D45" s="190"/>
-      <c r="E45" s="190"/>
-      <c r="F45" s="190"/>
-      <c r="G45" s="190"/>
+      <c r="C45" s="191"/>
+      <c r="D45" s="191"/>
+      <c r="E45" s="191"/>
+      <c r="F45" s="191"/>
+      <c r="G45" s="191"/>
       <c r="H45" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F11:G11"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="D42:F42"/>
     <mergeCell ref="D38:F38"/>
@@ -13812,32 +13844,22 @@
     <mergeCell ref="D39:F39"/>
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="C31:D31"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B33:G33"/>
     <mergeCell ref="D41:F41"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F11:G11"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F19:G19"/>
     <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F20:G20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -13889,18 +13911,18 @@
       <c r="A2" s="270" t="s">
         <v>377</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="190"/>
-      <c r="D2" s="190"/>
-      <c r="E2" s="190"/>
-      <c r="F2" s="190"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="190"/>
-      <c r="I2" s="190"/>
-      <c r="J2" s="190"/>
-      <c r="K2" s="190"/>
-      <c r="L2" s="190"/>
-      <c r="M2" s="190"/>
+      <c r="B2" s="191"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="191"/>
+      <c r="J2" s="191"/>
+      <c r="K2" s="191"/>
+      <c r="L2" s="191"/>
+      <c r="M2" s="191"/>
     </row>
     <row r="3" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
@@ -14945,19 +14967,19 @@
     </row>
     <row r="28" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="6"/>
-      <c r="B28" s="220" t="s">
+      <c r="B28" s="248" t="s">
         <v>392</v>
       </c>
-      <c r="C28" s="190"/>
-      <c r="D28" s="190"/>
-      <c r="E28" s="190"/>
-      <c r="F28" s="190"/>
-      <c r="G28" s="190"/>
-      <c r="H28" s="190"/>
-      <c r="I28" s="190"/>
-      <c r="J28" s="190"/>
-      <c r="K28" s="190"/>
-      <c r="L28" s="190"/>
+      <c r="C28" s="191"/>
+      <c r="D28" s="191"/>
+      <c r="E28" s="191"/>
+      <c r="F28" s="191"/>
+      <c r="G28" s="191"/>
+      <c r="H28" s="191"/>
+      <c r="I28" s="191"/>
+      <c r="J28" s="191"/>
+      <c r="K28" s="191"/>
+      <c r="L28" s="191"/>
       <c r="M28" s="6"/>
     </row>
   </sheetData>
@@ -15057,21 +15079,21 @@
     </row>
     <row r="3" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
-      <c r="B3" s="258" t="s">
+      <c r="B3" s="231" t="s">
         <v>397</v>
       </c>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="190"/>
-      <c r="F3" s="190"/>
-      <c r="G3" s="190"/>
-      <c r="H3" s="190"/>
-      <c r="I3" s="190"/>
-      <c r="J3" s="190"/>
-      <c r="K3" s="190"/>
-      <c r="L3" s="190"/>
-      <c r="M3" s="190"/>
-      <c r="N3" s="190"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
+      <c r="E3" s="191"/>
+      <c r="F3" s="191"/>
+      <c r="G3" s="191"/>
+      <c r="H3" s="191"/>
+      <c r="I3" s="191"/>
+      <c r="J3" s="191"/>
+      <c r="K3" s="191"/>
+      <c r="L3" s="191"/>
+      <c r="M3" s="191"/>
+      <c r="N3" s="191"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
@@ -15101,7 +15123,7 @@
       </c>
       <c r="H4" s="47">
         <f ca="1">'Input Data'!V10</f>
-        <v>0.91718001368925395</v>
+        <v>0.82409308692676253</v>
       </c>
       <c r="I4" s="45">
         <f>'Input Data'!J10</f>
@@ -15156,7 +15178,7 @@
       </c>
       <c r="H5" s="47">
         <f ca="1">'Input Data'!V16</f>
-        <v>1.0075290896646132</v>
+        <v>0.91444216290212188</v>
       </c>
       <c r="I5" s="45">
         <f>'Input Data'!J16</f>
@@ -15185,21 +15207,21 @@
     </row>
     <row r="6" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6"/>
-      <c r="B6" s="191" t="s">
+      <c r="B6" s="190" t="s">
         <v>398</v>
       </c>
-      <c r="C6" s="190"/>
-      <c r="D6" s="190"/>
-      <c r="E6" s="190"/>
-      <c r="F6" s="190"/>
-      <c r="G6" s="190"/>
-      <c r="H6" s="190"/>
-      <c r="I6" s="190"/>
-      <c r="J6" s="190"/>
-      <c r="K6" s="190"/>
-      <c r="L6" s="190"/>
-      <c r="M6" s="190"/>
-      <c r="N6" s="190"/>
+      <c r="C6" s="191"/>
+      <c r="D6" s="191"/>
+      <c r="E6" s="191"/>
+      <c r="F6" s="191"/>
+      <c r="G6" s="191"/>
+      <c r="H6" s="191"/>
+      <c r="I6" s="191"/>
+      <c r="J6" s="191"/>
+      <c r="K6" s="191"/>
+      <c r="L6" s="191"/>
+      <c r="M6" s="191"/>
+      <c r="N6" s="191"/>
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
@@ -15229,7 +15251,7 @@
       </c>
       <c r="H7" s="141">
         <f ca="1">'Input Data'!V14</f>
-        <v>2.001368925393566</v>
+        <v>1.9082819986310746</v>
       </c>
       <c r="I7" s="91">
         <f>'Input Data'!J14</f>
@@ -15284,7 +15306,7 @@
       </c>
       <c r="H8" s="141">
         <f ca="1">'Input Data'!V3</f>
-        <v>2.5051334702258727</v>
+        <v>2.4120465434633811</v>
       </c>
       <c r="I8" s="91">
         <f>'Input Data'!J3</f>
@@ -15313,21 +15335,21 @@
     </row>
     <row r="9" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
-      <c r="B9" s="258" t="s">
+      <c r="B9" s="231" t="s">
         <v>399</v>
       </c>
-      <c r="C9" s="190"/>
-      <c r="D9" s="190"/>
-      <c r="E9" s="190"/>
-      <c r="F9" s="190"/>
-      <c r="G9" s="190"/>
-      <c r="H9" s="190"/>
-      <c r="I9" s="190"/>
-      <c r="J9" s="190"/>
-      <c r="K9" s="190"/>
-      <c r="L9" s="190"/>
-      <c r="M9" s="190"/>
-      <c r="N9" s="190"/>
+      <c r="C9" s="191"/>
+      <c r="D9" s="191"/>
+      <c r="E9" s="191"/>
+      <c r="F9" s="191"/>
+      <c r="G9" s="191"/>
+      <c r="H9" s="191"/>
+      <c r="I9" s="191"/>
+      <c r="J9" s="191"/>
+      <c r="K9" s="191"/>
+      <c r="L9" s="191"/>
+      <c r="M9" s="191"/>
+      <c r="N9" s="191"/>
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6"/>
@@ -15357,7 +15379,7 @@
       </c>
       <c r="H10" s="26">
         <f ca="1">'Input Data'!V8</f>
-        <v>2.6666666666666665</v>
+        <v>2.5735797399041753</v>
       </c>
       <c r="I10" s="25">
         <f>'Input Data'!J8</f>
@@ -15412,7 +15434,7 @@
       </c>
       <c r="H11" s="26">
         <f ca="1">'Input Data'!V7</f>
-        <v>2.9185489390828199</v>
+        <v>2.8254620123203287</v>
       </c>
       <c r="I11" s="25">
         <f>'Input Data'!J7</f>
@@ -15467,7 +15489,7 @@
       </c>
       <c r="H12" s="26">
         <f ca="1">'Input Data'!V9</f>
-        <v>3.2087611225188226</v>
+        <v>3.1156741957563314</v>
       </c>
       <c r="I12" s="25">
         <f>'Input Data'!J9</f>
@@ -15522,7 +15544,7 @@
       </c>
       <c r="H13" s="26">
         <f ca="1">'Input Data'!V12</f>
-        <v>3.2087611225188226</v>
+        <v>3.1156741957563314</v>
       </c>
       <c r="I13" s="25">
         <f>'Input Data'!J12</f>
@@ -15577,7 +15599,7 @@
       </c>
       <c r="H14" s="26">
         <f ca="1">'Input Data'!V13</f>
-        <v>3.2087611225188226</v>
+        <v>3.1156741957563314</v>
       </c>
       <c r="I14" s="25">
         <f>'Input Data'!J13</f>
@@ -15632,7 +15654,7 @@
       </c>
       <c r="H15" s="26">
         <f ca="1">'Input Data'!V17</f>
-        <v>3.5044490075290895</v>
+        <v>3.4113620807665983</v>
       </c>
       <c r="I15" s="25">
         <f>'Input Data'!J17</f>
@@ -15661,21 +15683,21 @@
     </row>
     <row r="16" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6"/>
-      <c r="B16" s="191" t="s">
+      <c r="B16" s="190" t="s">
         <v>400</v>
       </c>
-      <c r="C16" s="190"/>
-      <c r="D16" s="190"/>
-      <c r="E16" s="190"/>
-      <c r="F16" s="190"/>
-      <c r="G16" s="190"/>
-      <c r="H16" s="190"/>
-      <c r="I16" s="190"/>
-      <c r="J16" s="190"/>
-      <c r="K16" s="190"/>
-      <c r="L16" s="190"/>
-      <c r="M16" s="190"/>
-      <c r="N16" s="190"/>
+      <c r="C16" s="191"/>
+      <c r="D16" s="191"/>
+      <c r="E16" s="191"/>
+      <c r="F16" s="191"/>
+      <c r="G16" s="191"/>
+      <c r="H16" s="191"/>
+      <c r="I16" s="191"/>
+      <c r="J16" s="191"/>
+      <c r="K16" s="191"/>
+      <c r="L16" s="191"/>
+      <c r="M16" s="191"/>
+      <c r="N16" s="191"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6"/>
@@ -15705,7 +15727,7 @@
       </c>
       <c r="H17" s="26">
         <f ca="1">'Input Data'!V15</f>
-        <v>4.3367556468172488</v>
+        <v>4.2436687200547567</v>
       </c>
       <c r="I17" s="25">
         <f>'Input Data'!J15</f>
@@ -15760,7 +15782,7 @@
       </c>
       <c r="H18" s="26">
         <f ca="1">'Input Data'!V18</f>
-        <v>4.3367556468172488</v>
+        <v>4.2436687200547567</v>
       </c>
       <c r="I18" s="25">
         <f>'Input Data'!J18</f>
@@ -15815,7 +15837,7 @@
       </c>
       <c r="H19" s="26">
         <f ca="1">'Input Data'!V19</f>
-        <v>4.4599589322381927</v>
+        <v>4.3668720054757015</v>
       </c>
       <c r="I19" s="25">
         <f>'Input Data'!J19</f>
@@ -15844,21 +15866,21 @@
     </row>
     <row r="20" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6"/>
-      <c r="B20" s="191" t="s">
+      <c r="B20" s="190" t="s">
         <v>401</v>
       </c>
-      <c r="C20" s="190"/>
-      <c r="D20" s="190"/>
-      <c r="E20" s="190"/>
-      <c r="F20" s="190"/>
-      <c r="G20" s="190"/>
-      <c r="H20" s="190"/>
-      <c r="I20" s="190"/>
-      <c r="J20" s="190"/>
-      <c r="K20" s="190"/>
-      <c r="L20" s="190"/>
-      <c r="M20" s="190"/>
-      <c r="N20" s="190"/>
+      <c r="C20" s="191"/>
+      <c r="D20" s="191"/>
+      <c r="E20" s="191"/>
+      <c r="F20" s="191"/>
+      <c r="G20" s="191"/>
+      <c r="H20" s="191"/>
+      <c r="I20" s="191"/>
+      <c r="J20" s="191"/>
+      <c r="K20" s="191"/>
+      <c r="L20" s="191"/>
+      <c r="M20" s="191"/>
+      <c r="N20" s="191"/>
     </row>
     <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6"/>
@@ -15888,7 +15910,7 @@
       </c>
       <c r="H21" s="26">
         <f ca="1">'Input Data'!V4</f>
-        <v>4.9993155373032172</v>
+        <v>4.9062286105407251</v>
       </c>
       <c r="I21" s="25">
         <f>'Input Data'!J4</f>
@@ -15943,7 +15965,7 @@
       </c>
       <c r="H22" s="26">
         <f ca="1">'Input Data'!V5</f>
-        <v>4.9993155373032172</v>
+        <v>4.9062286105407251</v>
       </c>
       <c r="I22" s="25">
         <f>'Input Data'!J5</f>
@@ -15998,7 +16020,7 @@
       </c>
       <c r="H23" s="26">
         <f ca="1">'Input Data'!V6</f>
-        <v>4.9993155373032172</v>
+        <v>4.9062286105407251</v>
       </c>
       <c r="I23" s="25">
         <f>'Input Data'!J6</f>
@@ -16053,7 +16075,7 @@
       </c>
       <c r="H24" s="26">
         <f ca="1">'Input Data'!V11</f>
-        <v>6.0862422997946615</v>
+        <v>5.9931553730321694</v>
       </c>
       <c r="I24" s="25">
         <f>'Input Data'!J11</f>
@@ -16092,11 +16114,11 @@
       </c>
       <c r="D25" s="142">
         <f>'Input Data'!F24</f>
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="E25" s="143">
         <f>IFERROR('Input Data'!G24,"")</f>
-        <v>46203</v>
+        <v>46296</v>
       </c>
       <c r="F25" s="143">
         <f>IFERROR('Input Data'!H24,"")</f>
@@ -16108,7 +16130,7 @@
       </c>
       <c r="H25" s="142">
         <f ca="1">'Input Data'!V24</f>
-        <v>9.2511978097193701</v>
+        <v>9.158110882956878</v>
       </c>
       <c r="I25" s="142">
         <f>'Input Data'!J24</f>
@@ -16116,7 +16138,7 @@
       </c>
       <c r="J25" s="142">
         <f>'Input Data'!Q24</f>
-        <v>-113632</v>
+        <v>-101152</v>
       </c>
       <c r="K25" s="142">
         <f>IFERROR(YEAR('Input Data'!H24),"VACANT")</f>
@@ -16255,7 +16277,7 @@
       </c>
       <c r="D30" s="51">
         <f>'Input Data'!F23</f>
-        <v>236</v>
+        <v>242.5</v>
       </c>
       <c r="E30" s="69"/>
       <c r="F30" s="69"/>
@@ -16297,7 +16319,7 @@
       <c r="C32" s="6"/>
       <c r="D32" s="102">
         <f>SUM('Input Data'!F3:F24)</f>
-        <v>8922.4000000000015</v>
+        <v>8940.9000000000015</v>
       </c>
       <c r="E32" s="68"/>
       <c r="F32" s="68"/>
@@ -16305,11 +16327,11 @@
       <c r="H32" s="68"/>
       <c r="I32" s="145">
         <f>SUMPRODUCT(('Input Data'!H3:H24&lt;&gt;"")*'Input Data'!J3:J24*'Input Data'!F3:F24)/SUMPRODUCT(('Input Data'!H3:H24&lt;&gt;"")*'Input Data'!F3:F24)</f>
-        <v>911.34060802086242</v>
+        <v>911.53575839927203</v>
       </c>
       <c r="J32" s="63">
         <f>SUM('Input Data'!Q3:Q24)</f>
-        <v>5377867.9789999994</v>
+        <v>5390347.9789999994</v>
       </c>
       <c r="K32" s="68"/>
       <c r="L32" s="68"/>
@@ -16466,32 +16488,32 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="258" t="s">
+      <c r="A3" s="231" t="s">
         <v>397</v>
       </c>
-      <c r="B3" s="190"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="190"/>
-      <c r="F3" s="190"/>
-      <c r="G3" s="190"/>
-      <c r="H3" s="190"/>
-      <c r="I3" s="190"/>
-      <c r="J3" s="190"/>
-      <c r="K3" s="190"/>
-      <c r="L3" s="190"/>
-      <c r="M3" s="190"/>
-      <c r="N3" s="190"/>
-      <c r="O3" s="190"/>
-      <c r="P3" s="190"/>
-      <c r="Q3" s="190"/>
-      <c r="R3" s="190"/>
-      <c r="S3" s="190"/>
-      <c r="T3" s="190"/>
-      <c r="U3" s="190"/>
-      <c r="V3" s="190"/>
-      <c r="W3" s="190"/>
-      <c r="X3" s="190"/>
+      <c r="B3" s="191"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
+      <c r="E3" s="191"/>
+      <c r="F3" s="191"/>
+      <c r="G3" s="191"/>
+      <c r="H3" s="191"/>
+      <c r="I3" s="191"/>
+      <c r="J3" s="191"/>
+      <c r="K3" s="191"/>
+      <c r="L3" s="191"/>
+      <c r="M3" s="191"/>
+      <c r="N3" s="191"/>
+      <c r="O3" s="191"/>
+      <c r="P3" s="191"/>
+      <c r="Q3" s="191"/>
+      <c r="R3" s="191"/>
+      <c r="S3" s="191"/>
+      <c r="T3" s="191"/>
+      <c r="U3" s="191"/>
+      <c r="V3" s="191"/>
+      <c r="W3" s="191"/>
+      <c r="X3" s="191"/>
     </row>
     <row r="4" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="41" t="str">
@@ -16528,7 +16550,7 @@
       </c>
       <c r="I4" s="47">
         <f ca="1">'Input Data'!V10</f>
-        <v>0.91718001368925395</v>
+        <v>0.82409308692676253</v>
       </c>
       <c r="J4" s="45">
         <f>'Input Data'!J10</f>
@@ -16584,7 +16606,7 @@
       </c>
       <c r="W4" s="43">
         <f ca="1">'Input Data'!W10</f>
-        <v>173.71389459274471</v>
+        <v>156.08323066392882</v>
       </c>
       <c r="X4" s="46" t="str">
         <f>'Input Data'!AB10</f>
@@ -16626,7 +16648,7 @@
       </c>
       <c r="I5" s="47">
         <f ca="1">'Input Data'!V16</f>
-        <v>1.0075290896646132</v>
+        <v>0.91444216290212188</v>
       </c>
       <c r="J5" s="45">
         <f>'Input Data'!J16</f>
@@ -16682,7 +16704,7 @@
       </c>
       <c r="W5" s="43">
         <f ca="1">'Input Data'!W16</f>
-        <v>456.71293634496919</v>
+        <v>414.51663244353188</v>
       </c>
       <c r="X5" s="46" t="str">
         <f>'Input Data'!AB16</f>
@@ -16690,32 +16712,32 @@
       </c>
     </row>
     <row r="6" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="191" t="s">
+      <c r="A6" s="190" t="s">
         <v>398</v>
       </c>
-      <c r="B6" s="190"/>
-      <c r="C6" s="190"/>
-      <c r="D6" s="190"/>
-      <c r="E6" s="190"/>
-      <c r="F6" s="190"/>
-      <c r="G6" s="190"/>
-      <c r="H6" s="190"/>
-      <c r="I6" s="190"/>
-      <c r="J6" s="190"/>
-      <c r="K6" s="190"/>
-      <c r="L6" s="190"/>
-      <c r="M6" s="190"/>
-      <c r="N6" s="190"/>
-      <c r="O6" s="190"/>
-      <c r="P6" s="190"/>
-      <c r="Q6" s="190"/>
-      <c r="R6" s="190"/>
-      <c r="S6" s="190"/>
-      <c r="T6" s="190"/>
-      <c r="U6" s="190"/>
-      <c r="V6" s="190"/>
-      <c r="W6" s="190"/>
-      <c r="X6" s="190"/>
+      <c r="B6" s="191"/>
+      <c r="C6" s="191"/>
+      <c r="D6" s="191"/>
+      <c r="E6" s="191"/>
+      <c r="F6" s="191"/>
+      <c r="G6" s="191"/>
+      <c r="H6" s="191"/>
+      <c r="I6" s="191"/>
+      <c r="J6" s="191"/>
+      <c r="K6" s="191"/>
+      <c r="L6" s="191"/>
+      <c r="M6" s="191"/>
+      <c r="N6" s="191"/>
+      <c r="O6" s="191"/>
+      <c r="P6" s="191"/>
+      <c r="Q6" s="191"/>
+      <c r="R6" s="191"/>
+      <c r="S6" s="191"/>
+      <c r="T6" s="191"/>
+      <c r="U6" s="191"/>
+      <c r="V6" s="191"/>
+      <c r="W6" s="191"/>
+      <c r="X6" s="191"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="88" t="str">
@@ -16752,7 +16774,7 @@
       </c>
       <c r="I7" s="141">
         <f ca="1">'Input Data'!V14</f>
-        <v>2.001368925393566</v>
+        <v>1.9082819986310746</v>
       </c>
       <c r="J7" s="91">
         <f>'Input Data'!J14</f>
@@ -16808,7 +16830,7 @@
       </c>
       <c r="W7" s="90">
         <f ca="1">'Input Data'!W14</f>
-        <v>1374.3400410677618</v>
+        <v>1310.417248459959</v>
       </c>
       <c r="X7" s="89" t="str">
         <f>'Input Data'!AB14</f>
@@ -16850,7 +16872,7 @@
       </c>
       <c r="I8" s="141">
         <f ca="1">'Input Data'!V3</f>
-        <v>2.5051334702258727</v>
+        <v>2.4120465434633811</v>
       </c>
       <c r="J8" s="91">
         <f>'Input Data'!J3</f>
@@ -16906,7 +16928,7 @@
       </c>
       <c r="W8" s="90">
         <f ca="1">'Input Data'!W3</f>
-        <v>269.80287474332653</v>
+        <v>259.77741273100617</v>
       </c>
       <c r="X8" s="89" t="str">
         <f>'Input Data'!AB3</f>
@@ -16914,32 +16936,32 @@
       </c>
     </row>
     <row r="9" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="258" t="s">
+      <c r="A9" s="231" t="s">
         <v>399</v>
       </c>
-      <c r="B9" s="190"/>
-      <c r="C9" s="190"/>
-      <c r="D9" s="190"/>
-      <c r="E9" s="190"/>
-      <c r="F9" s="190"/>
-      <c r="G9" s="190"/>
-      <c r="H9" s="190"/>
-      <c r="I9" s="190"/>
-      <c r="J9" s="190"/>
-      <c r="K9" s="190"/>
-      <c r="L9" s="190"/>
-      <c r="M9" s="190"/>
-      <c r="N9" s="190"/>
-      <c r="O9" s="190"/>
-      <c r="P9" s="190"/>
-      <c r="Q9" s="190"/>
-      <c r="R9" s="190"/>
-      <c r="S9" s="190"/>
-      <c r="T9" s="190"/>
-      <c r="U9" s="190"/>
-      <c r="V9" s="190"/>
-      <c r="W9" s="190"/>
-      <c r="X9" s="190"/>
+      <c r="B9" s="191"/>
+      <c r="C9" s="191"/>
+      <c r="D9" s="191"/>
+      <c r="E9" s="191"/>
+      <c r="F9" s="191"/>
+      <c r="G9" s="191"/>
+      <c r="H9" s="191"/>
+      <c r="I9" s="191"/>
+      <c r="J9" s="191"/>
+      <c r="K9" s="191"/>
+      <c r="L9" s="191"/>
+      <c r="M9" s="191"/>
+      <c r="N9" s="191"/>
+      <c r="O9" s="191"/>
+      <c r="P9" s="191"/>
+      <c r="Q9" s="191"/>
+      <c r="R9" s="191"/>
+      <c r="S9" s="191"/>
+      <c r="T9" s="191"/>
+      <c r="U9" s="191"/>
+      <c r="V9" s="191"/>
+      <c r="W9" s="191"/>
+      <c r="X9" s="191"/>
     </row>
     <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="str">
@@ -16976,7 +16998,7 @@
       </c>
       <c r="I10" s="26">
         <f ca="1">'Input Data'!V8</f>
-        <v>2.6666666666666665</v>
+        <v>2.5735797399041753</v>
       </c>
       <c r="J10" s="25">
         <f>'Input Data'!J8</f>
@@ -17032,7 +17054,7 @@
       </c>
       <c r="W10" s="22">
         <f ca="1">'Input Data'!W8</f>
-        <v>1102.6666666666665</v>
+        <v>1064.1752224503764</v>
       </c>
       <c r="X10" s="14" t="str">
         <f>'Input Data'!AB8</f>
@@ -17074,7 +17096,7 @@
       </c>
       <c r="I11" s="26">
         <f ca="1">'Input Data'!V7</f>
-        <v>2.9185489390828199</v>
+        <v>2.8254620123203287</v>
       </c>
       <c r="J11" s="25">
         <f>'Input Data'!J7</f>
@@ -17130,7 +17152,7 @@
       </c>
       <c r="W11" s="22">
         <f ca="1">'Input Data'!W7</f>
-        <v>670.68254620123207</v>
+        <v>649.29117043121153</v>
       </c>
       <c r="X11" s="14" t="str">
         <f>'Input Data'!AB7</f>
@@ -17172,7 +17194,7 @@
       </c>
       <c r="I12" s="26">
         <f ca="1">'Input Data'!V9</f>
-        <v>3.2087611225188226</v>
+        <v>3.1156741957563314</v>
       </c>
       <c r="J12" s="25">
         <f>'Input Data'!J9</f>
@@ -17228,7 +17250,7 @@
       </c>
       <c r="W12" s="22">
         <f ca="1">'Input Data'!W9</f>
-        <v>1449.3973990417521</v>
+        <v>1407.3500342231348</v>
       </c>
       <c r="X12" s="14" t="str">
         <f>'Input Data'!AB9</f>
@@ -17270,7 +17292,7 @@
       </c>
       <c r="I13" s="26">
         <f ca="1">'Input Data'!V12</f>
-        <v>3.2087611225188226</v>
+        <v>3.1156741957563314</v>
       </c>
       <c r="J13" s="25">
         <f>'Input Data'!J12</f>
@@ -17326,7 +17348,7 @@
       </c>
       <c r="W13" s="22">
         <f ca="1">'Input Data'!W12</f>
-        <v>1553.3612594113622</v>
+        <v>1508.2978781656402</v>
       </c>
       <c r="X13" s="14" t="str">
         <f>'Input Data'!AB12</f>
@@ -17368,7 +17390,7 @@
       </c>
       <c r="I14" s="26">
         <f ca="1">'Input Data'!V13</f>
-        <v>3.2087611225188226</v>
+        <v>3.1156741957563314</v>
       </c>
       <c r="J14" s="25">
         <f>'Input Data'!J13</f>
@@ -17424,7 +17446,7 @@
       </c>
       <c r="W14" s="22">
         <f ca="1">'Input Data'!W13</f>
-        <v>1172.8021902806297</v>
+        <v>1138.7789185489391</v>
       </c>
       <c r="X14" s="14" t="str">
         <f>'Input Data'!AB13</f>
@@ -17466,7 +17488,7 @@
       </c>
       <c r="I15" s="26">
         <f ca="1">'Input Data'!V17</f>
-        <v>3.5044490075290895</v>
+        <v>3.4113620807665983</v>
       </c>
       <c r="J15" s="25">
         <f>'Input Data'!J17</f>
@@ -17522,7 +17544,7 @@
       </c>
       <c r="W15" s="22">
         <f ca="1">'Input Data'!W17</f>
-        <v>1207.2826830937713</v>
+        <v>1175.2142368240932</v>
       </c>
       <c r="X15" s="14" t="str">
         <f>'Input Data'!AB17</f>
@@ -17530,32 +17552,32 @@
       </c>
     </row>
     <row r="16" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="191" t="s">
+      <c r="A16" s="190" t="s">
         <v>400</v>
       </c>
-      <c r="B16" s="190"/>
-      <c r="C16" s="190"/>
-      <c r="D16" s="190"/>
-      <c r="E16" s="190"/>
-      <c r="F16" s="190"/>
-      <c r="G16" s="190"/>
-      <c r="H16" s="190"/>
-      <c r="I16" s="190"/>
-      <c r="J16" s="190"/>
-      <c r="K16" s="190"/>
-      <c r="L16" s="190"/>
-      <c r="M16" s="190"/>
-      <c r="N16" s="190"/>
-      <c r="O16" s="190"/>
-      <c r="P16" s="190"/>
-      <c r="Q16" s="190"/>
-      <c r="R16" s="190"/>
-      <c r="S16" s="190"/>
-      <c r="T16" s="190"/>
-      <c r="U16" s="190"/>
-      <c r="V16" s="190"/>
-      <c r="W16" s="190"/>
-      <c r="X16" s="190"/>
+      <c r="B16" s="191"/>
+      <c r="C16" s="191"/>
+      <c r="D16" s="191"/>
+      <c r="E16" s="191"/>
+      <c r="F16" s="191"/>
+      <c r="G16" s="191"/>
+      <c r="H16" s="191"/>
+      <c r="I16" s="191"/>
+      <c r="J16" s="191"/>
+      <c r="K16" s="191"/>
+      <c r="L16" s="191"/>
+      <c r="M16" s="191"/>
+      <c r="N16" s="191"/>
+      <c r="O16" s="191"/>
+      <c r="P16" s="191"/>
+      <c r="Q16" s="191"/>
+      <c r="R16" s="191"/>
+      <c r="S16" s="191"/>
+      <c r="T16" s="191"/>
+      <c r="U16" s="191"/>
+      <c r="V16" s="191"/>
+      <c r="W16" s="191"/>
+      <c r="X16" s="191"/>
     </row>
     <row r="17" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="str">
@@ -17592,7 +17614,7 @@
       </c>
       <c r="I17" s="26">
         <f ca="1">'Input Data'!V15</f>
-        <v>4.3367556468172488</v>
+        <v>4.2436687200547567</v>
       </c>
       <c r="J17" s="25">
         <f>'Input Data'!J15</f>
@@ -17648,7 +17670,7 @@
       </c>
       <c r="W17" s="22">
         <f ca="1">'Input Data'!W15</f>
-        <v>504.36468172484604</v>
+        <v>493.53867214236817</v>
       </c>
       <c r="X17" s="14" t="str">
         <f>'Input Data'!AB15</f>
@@ -17690,7 +17712,7 @@
       </c>
       <c r="I18" s="26">
         <f ca="1">'Input Data'!V18</f>
-        <v>4.3367556468172488</v>
+        <v>4.2436687200547567</v>
       </c>
       <c r="J18" s="25">
         <f>'Input Data'!J18</f>
@@ -17746,7 +17768,7 @@
       </c>
       <c r="W18" s="22">
         <f ca="1">'Input Data'!W18</f>
-        <v>1088.5256673511294</v>
+        <v>1065.1608487337439</v>
       </c>
       <c r="X18" s="14" t="str">
         <f>'Input Data'!AB18</f>
@@ -17788,7 +17810,7 @@
       </c>
       <c r="I19" s="26">
         <f ca="1">'Input Data'!V19</f>
-        <v>4.4599589322381927</v>
+        <v>4.3668720054757015</v>
       </c>
       <c r="J19" s="25">
         <f>'Input Data'!J19</f>
@@ -17844,7 +17866,7 @@
       </c>
       <c r="W19" s="22">
         <f ca="1">'Input Data'!W19</f>
-        <v>2390.5379876796715</v>
+        <v>2340.6433949349762</v>
       </c>
       <c r="X19" s="14" t="str">
         <f>'Input Data'!AB19</f>
@@ -17852,32 +17874,32 @@
       </c>
     </row>
     <row r="20" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="191" t="s">
+      <c r="A20" s="190" t="s">
         <v>401</v>
       </c>
-      <c r="B20" s="190"/>
-      <c r="C20" s="190"/>
-      <c r="D20" s="190"/>
-      <c r="E20" s="190"/>
-      <c r="F20" s="190"/>
-      <c r="G20" s="190"/>
-      <c r="H20" s="190"/>
-      <c r="I20" s="190"/>
-      <c r="J20" s="190"/>
-      <c r="K20" s="190"/>
-      <c r="L20" s="190"/>
-      <c r="M20" s="190"/>
-      <c r="N20" s="190"/>
-      <c r="O20" s="190"/>
-      <c r="P20" s="190"/>
-      <c r="Q20" s="190"/>
-      <c r="R20" s="190"/>
-      <c r="S20" s="190"/>
-      <c r="T20" s="190"/>
-      <c r="U20" s="190"/>
-      <c r="V20" s="190"/>
-      <c r="W20" s="190"/>
-      <c r="X20" s="190"/>
+      <c r="B20" s="191"/>
+      <c r="C20" s="191"/>
+      <c r="D20" s="191"/>
+      <c r="E20" s="191"/>
+      <c r="F20" s="191"/>
+      <c r="G20" s="191"/>
+      <c r="H20" s="191"/>
+      <c r="I20" s="191"/>
+      <c r="J20" s="191"/>
+      <c r="K20" s="191"/>
+      <c r="L20" s="191"/>
+      <c r="M20" s="191"/>
+      <c r="N20" s="191"/>
+      <c r="O20" s="191"/>
+      <c r="P20" s="191"/>
+      <c r="Q20" s="191"/>
+      <c r="R20" s="191"/>
+      <c r="S20" s="191"/>
+      <c r="T20" s="191"/>
+      <c r="U20" s="191"/>
+      <c r="V20" s="191"/>
+      <c r="W20" s="191"/>
+      <c r="X20" s="191"/>
     </row>
     <row r="21" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="13" t="str">
@@ -17914,7 +17936,7 @@
       </c>
       <c r="I21" s="26">
         <f ca="1">'Input Data'!V4</f>
-        <v>4.9993155373032172</v>
+        <v>4.9062286105407251</v>
       </c>
       <c r="J21" s="25">
         <f>'Input Data'!J4</f>
@@ -17970,7 +17992,7 @@
       </c>
       <c r="W21" s="22">
         <f ca="1">'Input Data'!W4</f>
-        <v>3976.9555099247091</v>
+        <v>3902.9048596851467</v>
       </c>
       <c r="X21" s="14" t="str">
         <f>'Input Data'!AB4</f>
@@ -18012,7 +18034,7 @@
       </c>
       <c r="I22" s="26">
         <f ca="1">'Input Data'!V5</f>
-        <v>4.9993155373032172</v>
+        <v>4.9062286105407251</v>
       </c>
       <c r="J22" s="25">
         <f>'Input Data'!J5</f>
@@ -18068,7 +18090,7 @@
       </c>
       <c r="W22" s="22">
         <f ca="1">'Input Data'!W5</f>
-        <v>5234.283367556468</v>
+        <v>5136.8213552361394</v>
       </c>
       <c r="X22" s="14" t="str">
         <f>'Input Data'!AB5</f>
@@ -18110,7 +18132,7 @@
       </c>
       <c r="I23" s="26">
         <f ca="1">'Input Data'!V6</f>
-        <v>4.9993155373032172</v>
+        <v>4.9062286105407251</v>
       </c>
       <c r="J23" s="25">
         <f>'Input Data'!J6</f>
@@ -18166,7 +18188,7 @@
       </c>
       <c r="W23" s="22">
         <f ca="1">'Input Data'!W6</f>
-        <v>2185.2008213552363</v>
+        <v>2144.5125256673509</v>
       </c>
       <c r="X23" s="14" t="str">
         <f>'Input Data'!AB6</f>
@@ -18208,7 +18230,7 @@
       </c>
       <c r="I24" s="26">
         <f ca="1">'Input Data'!V11</f>
-        <v>6.0862422997946615</v>
+        <v>5.9931553730321694</v>
       </c>
       <c r="J24" s="25">
         <f>'Input Data'!J11</f>
@@ -18264,7 +18286,7 @@
       </c>
       <c r="W24" s="22">
         <f ca="1">'Input Data'!W11</f>
-        <v>1630.5043121149897</v>
+        <v>1605.5663244353179</v>
       </c>
       <c r="X24" s="14" t="str">
         <f>'Input Data'!AB11</f>
@@ -18290,11 +18312,11 @@
       </c>
       <c r="E25" s="142">
         <f>'Input Data'!F24</f>
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="F25" s="143">
         <f>'Input Data'!G24</f>
-        <v>46203</v>
+        <v>46296</v>
       </c>
       <c r="G25" s="143">
         <f>'Input Data'!H24</f>
@@ -18306,7 +18328,7 @@
       </c>
       <c r="I25" s="142">
         <f ca="1">'Input Data'!V24</f>
-        <v>9.2511978097193701</v>
+        <v>9.158110882956878</v>
       </c>
       <c r="J25" s="142">
         <f>'Input Data'!J24</f>
@@ -18318,7 +18340,7 @@
       </c>
       <c r="L25" s="142">
         <f>'Input Data'!Q24</f>
-        <v>-113632</v>
+        <v>-101152</v>
       </c>
       <c r="M25" s="142">
         <f>'Input Data'!L24</f>
@@ -18358,7 +18380,7 @@
       </c>
       <c r="V25" s="142">
         <f ca="1">'Input Data'!W24</f>
-        <v>4958.642026009582</v>
+        <v>5018.6447638603695</v>
       </c>
       <c r="W25" s="142" t="str">
         <f>'Input Data'!AB24</f>
@@ -18531,12 +18553,12 @@
         <f>'Input Data'!B23</f>
         <v>L11</v>
       </c>
-      <c r="B30" s="190"/>
-      <c r="C30" s="190"/>
-      <c r="D30" s="190"/>
+      <c r="B30" s="191"/>
+      <c r="C30" s="191"/>
+      <c r="D30" s="191"/>
       <c r="E30" s="51">
         <f>'Input Data'!F23</f>
-        <v>236</v>
+        <v>242.5</v>
       </c>
       <c r="F30" s="69"/>
       <c r="G30" s="69"/>
@@ -18570,23 +18592,23 @@
       <c r="D31" s="6"/>
       <c r="E31" s="62">
         <f>SUM('Input Data'!F3:F24)</f>
-        <v>8922.4000000000015</v>
+        <v>8940.9000000000015</v>
       </c>
       <c r="F31" s="68"/>
       <c r="G31" s="68"/>
       <c r="H31" s="68"/>
       <c r="I31" s="147">
         <f ca="1">IFERROR(SUMPRODUCT(('Input Data'!H3:H24&lt;&gt;"")*'Input Data'!F3:F24*MAX(('Input Data'!H3:H24-TODAY())/365.25,0))/SUMPRODUCT(('Input Data'!H3:H24&lt;&gt;"")*'Input Data'!F3:F24),0)</f>
-        <v>9.2511978097193683</v>
+        <v>9.1581108829568798</v>
       </c>
       <c r="J31" s="145">
         <f>SUMPRODUCT(('Input Data'!H3:H24&lt;&gt;"")*'Input Data'!J3:J24*'Input Data'!F3:F24)/SUMPRODUCT(('Input Data'!H3:H24&lt;&gt;"")*'Input Data'!F3:F24)</f>
-        <v>911.34060802086242</v>
+        <v>911.53575839927203</v>
       </c>
       <c r="K31" s="68"/>
       <c r="L31" s="63">
         <f>SUM('Input Data'!Q3:Q24)</f>
-        <v>5377867.9789999994</v>
+        <v>5390347.9789999994</v>
       </c>
       <c r="M31" s="68"/>
       <c r="N31" s="68"/>
@@ -18633,7 +18655,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="295" t="s">
+      <c r="A1" s="300" t="s">
         <v>409</v>
       </c>
       <c r="B1" s="183"/>
@@ -18670,35 +18692,35 @@
       <c r="A2" s="270" t="s">
         <v>410</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="190"/>
-      <c r="D2" s="190"/>
-      <c r="E2" s="190"/>
-      <c r="F2" s="190"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="190"/>
-      <c r="I2" s="190"/>
-      <c r="J2" s="190"/>
-      <c r="K2" s="190"/>
-      <c r="L2" s="190"/>
-      <c r="M2" s="190"/>
-      <c r="N2" s="190"/>
-      <c r="O2" s="190"/>
-      <c r="P2" s="190"/>
-      <c r="Q2" s="190"/>
-      <c r="R2" s="190"/>
-      <c r="S2" s="190"/>
-      <c r="T2" s="190"/>
-      <c r="U2" s="190"/>
-      <c r="V2" s="190"/>
-      <c r="W2" s="190"/>
-      <c r="X2" s="190"/>
-      <c r="Y2" s="190"/>
-      <c r="Z2" s="190"/>
-      <c r="AA2" s="190"/>
-      <c r="AB2" s="190"/>
-      <c r="AC2" s="190"/>
-      <c r="AD2" s="190"/>
+      <c r="B2" s="191"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="191"/>
+      <c r="J2" s="191"/>
+      <c r="K2" s="191"/>
+      <c r="L2" s="191"/>
+      <c r="M2" s="191"/>
+      <c r="N2" s="191"/>
+      <c r="O2" s="191"/>
+      <c r="P2" s="191"/>
+      <c r="Q2" s="191"/>
+      <c r="R2" s="191"/>
+      <c r="S2" s="191"/>
+      <c r="T2" s="191"/>
+      <c r="U2" s="191"/>
+      <c r="V2" s="191"/>
+      <c r="W2" s="191"/>
+      <c r="X2" s="191"/>
+      <c r="Y2" s="191"/>
+      <c r="Z2" s="191"/>
+      <c r="AA2" s="191"/>
+      <c r="AB2" s="191"/>
+      <c r="AC2" s="191"/>
+      <c r="AD2" s="191"/>
     </row>
     <row r="3" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
@@ -18708,7 +18730,7 @@
       <c r="C3" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="D3" s="213" t="s">
+      <c r="D3" s="218" t="s">
         <v>412</v>
       </c>
       <c r="E3" s="183"/>
@@ -18742,7 +18764,7 @@
       <c r="A4" s="6"/>
       <c r="B4" s="68"/>
       <c r="C4" s="68"/>
-      <c r="D4" s="279"/>
+      <c r="D4" s="292"/>
       <c r="E4" s="186"/>
       <c r="F4" s="186"/>
       <c r="G4" s="186"/>
@@ -18772,13 +18794,13 @@
     </row>
     <row r="5" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
-      <c r="B5" s="283" t="s">
+      <c r="B5" s="296" t="s">
         <v>413</v>
       </c>
-      <c r="C5" s="281">
+      <c r="C5" s="289">
         <v>787</v>
       </c>
-      <c r="D5" s="293" t="str">
+      <c r="D5" s="285" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("12.01",'Input Data'!C:C,0)),"—")</f>
         <v>Hulsbosch Design Pty Ltd</v>
       </c>
@@ -18789,7 +18811,7 @@
       <c r="I5" s="183"/>
       <c r="J5" s="183"/>
       <c r="K5" s="183"/>
-      <c r="L5" s="290" t="str">
+      <c r="L5" s="299" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("12.02",'Input Data'!C:C,0)),"—")</f>
         <v>Aei Insurance Group Pty Ltd</v>
       </c>
@@ -18816,7 +18838,7 @@
       <c r="A6" s="6"/>
       <c r="B6" s="186"/>
       <c r="C6" s="186"/>
-      <c r="D6" s="275" t="str">
+      <c r="D6" s="280" t="str">
         <f>IFERROR("12.01 — "&amp;INDEX('Input Data'!B:B,MATCH("12.01",'Input Data'!C:C,0)),"—")</f>
         <v>12.01 — L12</v>
       </c>
@@ -18827,7 +18849,7 @@
       <c r="I6" s="183"/>
       <c r="J6" s="183"/>
       <c r="K6" s="183"/>
-      <c r="L6" s="277" t="str">
+      <c r="L6" s="279" t="str">
         <f>IFERROR("12.02 — "&amp;INDEX('Input Data'!B:B,MATCH("12.02",'Input Data'!C:C,0)),"—")</f>
         <v>12.02 — L12</v>
       </c>
@@ -18854,7 +18876,7 @@
       <c r="A7" s="6"/>
       <c r="B7" s="186"/>
       <c r="C7" s="186"/>
-      <c r="D7" s="275" t="str">
+      <c r="D7" s="280" t="str">
         <f>IFERROR(TEXT(INDEX('Input Data'!F:F,MATCH("12.01",'Input Data'!C:C,0)),"#,##0.0")&amp;" sqm","—")</f>
         <v>344.5 sqm</v>
       </c>
@@ -18865,7 +18887,7 @@
       <c r="I7" s="183"/>
       <c r="J7" s="183"/>
       <c r="K7" s="183"/>
-      <c r="L7" s="277" t="str">
+      <c r="L7" s="279" t="str">
         <f>IFERROR(TEXT(INDEX('Input Data'!F:F,MATCH("12.02",'Input Data'!C:C,0)),"#,##0.0")&amp;" sqm","—")</f>
         <v>536.0 sqm</v>
       </c>
@@ -18892,7 +18914,7 @@
       <c r="A8" s="6"/>
       <c r="B8" s="186"/>
       <c r="C8" s="186"/>
-      <c r="D8" s="289" t="str">
+      <c r="D8" s="287" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("12.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("12.01",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $990 | Net $222,616 pa</v>
       </c>
@@ -18903,7 +18925,7 @@
       <c r="I8" s="183"/>
       <c r="J8" s="183"/>
       <c r="K8" s="183"/>
-      <c r="L8" s="288" t="str">
+      <c r="L8" s="284" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("12.02",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("12.02",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $988 | Net $675,903 pa</v>
       </c>
@@ -18930,7 +18952,7 @@
       <c r="A9" s="6"/>
       <c r="B9" s="186"/>
       <c r="C9" s="186"/>
-      <c r="D9" s="289" t="str">
+      <c r="D9" s="287" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("12.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("12.01",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $7,772 | Rev: FIXED 3.5%</v>
       </c>
@@ -18941,7 +18963,7 @@
       <c r="I9" s="183"/>
       <c r="J9" s="183"/>
       <c r="K9" s="183"/>
-      <c r="L9" s="288" t="str">
+      <c r="L9" s="284" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("12.02",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("12.02",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $62,133 | Rev: FIXED 4%</v>
       </c>
@@ -18968,9 +18990,9 @@
       <c r="A10" s="6"/>
       <c r="B10" s="186"/>
       <c r="C10" s="186"/>
-      <c r="D10" s="275" t="str">
+      <c r="D10" s="280" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("12.01",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("12.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Dec-29 (3.5 yrs)</v>
+        <v>Exp: Dec-29 (3.4 yrs)</v>
       </c>
       <c r="E10" s="183"/>
       <c r="F10" s="183"/>
@@ -18979,9 +19001,9 @@
       <c r="I10" s="183"/>
       <c r="J10" s="183"/>
       <c r="K10" s="183"/>
-      <c r="L10" s="277" t="str">
+      <c r="L10" s="279" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("12.02",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("12.02",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Dec-30 (4.5 yrs)</v>
+        <v>Exp: Dec-30 (4.4 yrs)</v>
       </c>
       <c r="M10" s="183"/>
       <c r="N10" s="183"/>
@@ -19006,9 +19028,9 @@
       <c r="A11" s="6"/>
       <c r="B11" s="186"/>
       <c r="C11" s="186"/>
-      <c r="D11" s="275" t="str">
+      <c r="D11" s="280" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("12.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>3.5 yrs remaining</v>
+        <v>3.4 yrs remaining</v>
       </c>
       <c r="E11" s="183"/>
       <c r="F11" s="183"/>
@@ -19017,9 +19039,9 @@
       <c r="I11" s="183"/>
       <c r="J11" s="183"/>
       <c r="K11" s="183"/>
-      <c r="L11" s="277" t="str">
+      <c r="L11" s="279" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("12.02",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>4.5 yrs remaining</v>
+        <v>4.4 yrs remaining</v>
       </c>
       <c r="M11" s="183"/>
       <c r="N11" s="183"/>
@@ -19044,7 +19066,7 @@
       <c r="A12" s="6"/>
       <c r="B12" s="186"/>
       <c r="C12" s="186"/>
-      <c r="D12" s="277"/>
+      <c r="D12" s="279"/>
       <c r="E12" s="183"/>
       <c r="F12" s="183"/>
       <c r="G12" s="183"/>
@@ -19052,7 +19074,7 @@
       <c r="I12" s="183"/>
       <c r="J12" s="183"/>
       <c r="K12" s="183"/>
-      <c r="L12" s="277"/>
+      <c r="L12" s="279"/>
       <c r="M12" s="183"/>
       <c r="N12" s="183"/>
       <c r="O12" s="183"/>
@@ -19106,13 +19128,13 @@
     </row>
     <row r="14" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
-      <c r="B14" s="283" t="s">
+      <c r="B14" s="296" t="s">
         <v>414</v>
       </c>
-      <c r="C14" s="281">
+      <c r="C14" s="289">
         <v>772</v>
       </c>
-      <c r="D14" s="294" t="str">
+      <c r="D14" s="277" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("11.01",'Input Data'!C:C,0)),"—")</f>
         <v>VACANT</v>
       </c>
@@ -19123,7 +19145,7 @@
       <c r="I14" s="183"/>
       <c r="J14" s="183"/>
       <c r="K14" s="183"/>
-      <c r="L14" s="287" t="str">
+      <c r="L14" s="294" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("11.02",'Input Data'!C:C,0)),"—")</f>
         <v>Haskoning Australia Pty Ltd</v>
       </c>
@@ -19150,7 +19172,7 @@
       <c r="A15" s="6"/>
       <c r="B15" s="186"/>
       <c r="C15" s="186"/>
-      <c r="D15" s="285" t="str">
+      <c r="D15" s="275" t="str">
         <f>IFERROR("11.01 — "&amp;INDEX('Input Data'!B:B,MATCH("11.01",'Input Data'!C:C,0)),"—")</f>
         <v>11.01 — L11</v>
       </c>
@@ -19188,9 +19210,9 @@
       <c r="A16" s="6"/>
       <c r="B16" s="186"/>
       <c r="C16" s="186"/>
-      <c r="D16" s="285" t="str">
+      <c r="D16" s="275" t="str">
         <f>IFERROR(TEXT(INDEX('Input Data'!F:F,MATCH("11.01",'Input Data'!C:C,0)),"#,##0.0")&amp;" sqm","—")</f>
-        <v>236.0 sqm</v>
+        <v>242.5 sqm</v>
       </c>
       <c r="E16" s="183"/>
       <c r="F16" s="183"/>
@@ -19201,7 +19223,7 @@
       <c r="K16" s="183"/>
       <c r="L16" s="274" t="str">
         <f>IFERROR(TEXT(INDEX('Input Data'!F:F,MATCH("11.02",'Input Data'!C:C,0)),"#,##0.0")&amp;" sqm","—")</f>
-        <v>536.0 sqm</v>
+        <v>548.0 sqm</v>
       </c>
       <c r="M16" s="183"/>
       <c r="N16" s="183"/>
@@ -19226,7 +19248,7 @@
       <c r="A17" s="6"/>
       <c r="B17" s="186"/>
       <c r="C17" s="186"/>
-      <c r="D17" s="276" t="str">
+      <c r="D17" s="283" t="str">
         <f>IFERROR(IF(INDEX('Input Data'!D:D,MATCH("11.01",'Input Data'!C:C,0))="VACANT","","Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("11.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("11.01",'Input Data'!C:C,0)),"#,##0 pa")),"—")</f>
         <v/>
       </c>
@@ -19237,9 +19259,9 @@
       <c r="I17" s="183"/>
       <c r="J17" s="183"/>
       <c r="K17" s="183"/>
-      <c r="L17" s="284" t="str">
+      <c r="L17" s="286" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("11.02",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("11.02",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
-        <v>Face $1,040 | Net $-113,632 pa</v>
+        <v>Face $1,040 | Net $-101,152 pa</v>
       </c>
       <c r="M17" s="183"/>
       <c r="N17" s="183"/>
@@ -19264,7 +19286,7 @@
       <c r="A18" s="6"/>
       <c r="B18" s="186"/>
       <c r="C18" s="186"/>
-      <c r="D18" s="276" t="str">
+      <c r="D18" s="283" t="str">
         <f>IFERROR(IF(INDEX('Input Data'!D:D,MATCH("11.01",'Input Data'!C:C,0))="VACANT","","Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("11.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("11.01",'Input Data'!C:C,0))),"—")</f>
         <v/>
       </c>
@@ -19275,7 +19297,7 @@
       <c r="I18" s="183"/>
       <c r="J18" s="183"/>
       <c r="K18" s="183"/>
-      <c r="L18" s="284" t="str">
+      <c r="L18" s="286" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("11.02",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("11.02",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $0 | Rev: FIXED 3.5%</v>
       </c>
@@ -19302,7 +19324,7 @@
       <c r="A19" s="6"/>
       <c r="B19" s="186"/>
       <c r="C19" s="186"/>
-      <c r="D19" s="285" t="str">
+      <c r="D19" s="275" t="str">
         <f>IFERROR(IF(INDEX('Input Data'!D:D,MATCH("11.01",'Input Data'!C:C,0))="VACANT","⬤ AVAILABLE NOW","Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("11.01",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("11.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs)"),"—")</f>
         <v>⬤ AVAILABLE NOW</v>
       </c>
@@ -19315,7 +19337,7 @@
       <c r="K19" s="183"/>
       <c r="L19" s="274" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("11.02",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("11.02",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Sep-35 (9.3 yrs)</v>
+        <v>Exp: Sep-35 (9.2 yrs)</v>
       </c>
       <c r="M19" s="183"/>
       <c r="N19" s="183"/>
@@ -19340,7 +19362,7 @@
       <c r="A20" s="6"/>
       <c r="B20" s="186"/>
       <c r="C20" s="186"/>
-      <c r="D20" s="292" t="str">
+      <c r="D20" s="295" t="str">
         <f>IFERROR(IF(INDEX('Input Data'!D:D,MATCH("11.01",'Input Data'!C:C,0))="VACANT","",TEXT(INDEX('Input Data'!V:V,MATCH("11.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining"),"—")</f>
         <v/>
       </c>
@@ -19353,7 +19375,7 @@
       <c r="K20" s="183"/>
       <c r="L20" s="274" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("11.02",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>9.3 yrs remaining</v>
+        <v>9.2 yrs remaining</v>
       </c>
       <c r="M20" s="183"/>
       <c r="N20" s="183"/>
@@ -19378,7 +19400,7 @@
       <c r="A21" s="6"/>
       <c r="B21" s="186"/>
       <c r="C21" s="186"/>
-      <c r="D21" s="285"/>
+      <c r="D21" s="275"/>
       <c r="E21" s="183"/>
       <c r="F21" s="183"/>
       <c r="G21" s="183"/>
@@ -19440,13 +19462,13 @@
     </row>
     <row r="23" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
-      <c r="B23" s="283" t="s">
+      <c r="B23" s="296" t="s">
         <v>415</v>
       </c>
-      <c r="C23" s="281">
+      <c r="C23" s="289">
         <v>787</v>
       </c>
-      <c r="D23" s="294" t="s">
+      <c r="D23" s="277" t="s">
         <v>155</v>
       </c>
       <c r="E23" s="183"/>
@@ -19462,7 +19484,7 @@
       <c r="O23" s="183"/>
       <c r="P23" s="183"/>
       <c r="Q23" s="183"/>
-      <c r="R23" s="294" t="s">
+      <c r="R23" s="277" t="s">
         <v>155</v>
       </c>
       <c r="S23" s="183"/>
@@ -19482,7 +19504,7 @@
       <c r="A24" s="6"/>
       <c r="B24" s="186"/>
       <c r="C24" s="186"/>
-      <c r="D24" s="285" t="s">
+      <c r="D24" s="275" t="s">
         <v>416</v>
       </c>
       <c r="E24" s="183"/>
@@ -19498,7 +19520,7 @@
       <c r="O24" s="183"/>
       <c r="P24" s="183"/>
       <c r="Q24" s="183"/>
-      <c r="R24" s="285" t="s">
+      <c r="R24" s="275" t="s">
         <v>417</v>
       </c>
       <c r="S24" s="183"/>
@@ -19518,7 +19540,7 @@
       <c r="A25" s="6"/>
       <c r="B25" s="186"/>
       <c r="C25" s="186"/>
-      <c r="D25" s="285"/>
+      <c r="D25" s="275"/>
       <c r="E25" s="183"/>
       <c r="F25" s="183"/>
       <c r="G25" s="183"/>
@@ -19532,7 +19554,7 @@
       <c r="O25" s="183"/>
       <c r="P25" s="183"/>
       <c r="Q25" s="183"/>
-      <c r="R25" s="285"/>
+      <c r="R25" s="275"/>
       <c r="S25" s="183"/>
       <c r="T25" s="183"/>
       <c r="U25" s="183"/>
@@ -19550,7 +19572,7 @@
       <c r="A26" s="6"/>
       <c r="B26" s="186"/>
       <c r="C26" s="186"/>
-      <c r="D26" s="276"/>
+      <c r="D26" s="283"/>
       <c r="E26" s="183"/>
       <c r="F26" s="183"/>
       <c r="G26" s="183"/>
@@ -19564,7 +19586,7 @@
       <c r="O26" s="183"/>
       <c r="P26" s="183"/>
       <c r="Q26" s="183"/>
-      <c r="R26" s="276"/>
+      <c r="R26" s="283"/>
       <c r="S26" s="183"/>
       <c r="T26" s="183"/>
       <c r="U26" s="183"/>
@@ -19582,7 +19604,7 @@
       <c r="A27" s="6"/>
       <c r="B27" s="186"/>
       <c r="C27" s="186"/>
-      <c r="D27" s="276"/>
+      <c r="D27" s="283"/>
       <c r="E27" s="183"/>
       <c r="F27" s="183"/>
       <c r="G27" s="183"/>
@@ -19596,7 +19618,7 @@
       <c r="O27" s="183"/>
       <c r="P27" s="183"/>
       <c r="Q27" s="183"/>
-      <c r="R27" s="276"/>
+      <c r="R27" s="283"/>
       <c r="S27" s="183"/>
       <c r="T27" s="183"/>
       <c r="U27" s="183"/>
@@ -19614,7 +19636,7 @@
       <c r="A28" s="6"/>
       <c r="B28" s="186"/>
       <c r="C28" s="186"/>
-      <c r="D28" s="285"/>
+      <c r="D28" s="275"/>
       <c r="E28" s="183"/>
       <c r="F28" s="183"/>
       <c r="G28" s="183"/>
@@ -19628,7 +19650,7 @@
       <c r="O28" s="183"/>
       <c r="P28" s="183"/>
       <c r="Q28" s="183"/>
-      <c r="R28" s="285"/>
+      <c r="R28" s="275"/>
       <c r="S28" s="183"/>
       <c r="T28" s="183"/>
       <c r="U28" s="183"/>
@@ -19646,7 +19668,7 @@
       <c r="A29" s="6"/>
       <c r="B29" s="186"/>
       <c r="C29" s="186"/>
-      <c r="D29" s="292" t="s">
+      <c r="D29" s="295" t="s">
         <v>418</v>
       </c>
       <c r="E29" s="183"/>
@@ -19662,7 +19684,7 @@
       <c r="O29" s="183"/>
       <c r="P29" s="183"/>
       <c r="Q29" s="183"/>
-      <c r="R29" s="292" t="s">
+      <c r="R29" s="295" t="s">
         <v>418</v>
       </c>
       <c r="S29" s="183"/>
@@ -19682,7 +19704,7 @@
       <c r="A30" s="6"/>
       <c r="B30" s="186"/>
       <c r="C30" s="186"/>
-      <c r="D30" s="285"/>
+      <c r="D30" s="275"/>
       <c r="E30" s="183"/>
       <c r="F30" s="183"/>
       <c r="G30" s="183"/>
@@ -19696,7 +19718,7 @@
       <c r="O30" s="183"/>
       <c r="P30" s="183"/>
       <c r="Q30" s="183"/>
-      <c r="R30" s="285"/>
+      <c r="R30" s="275"/>
       <c r="S30" s="183"/>
       <c r="T30" s="183"/>
       <c r="U30" s="183"/>
@@ -19744,13 +19766,13 @@
     </row>
     <row r="32" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6"/>
-      <c r="B32" s="283" t="s">
+      <c r="B32" s="296" t="s">
         <v>419</v>
       </c>
-      <c r="C32" s="281">
+      <c r="C32" s="289">
         <v>797.8</v>
       </c>
-      <c r="D32" s="286" t="str">
+      <c r="D32" s="297" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("9.01",'Input Data'!C:C,0)),"—")</f>
         <v>Pitt &amp; Sherry (Operations) Pty Ltd</v>
       </c>
@@ -19767,7 +19789,7 @@
       <c r="O32" s="183"/>
       <c r="P32" s="183"/>
       <c r="Q32" s="183"/>
-      <c r="R32" s="290" t="str">
+      <c r="R32" s="299" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("9.02",'Input Data'!C:C,0)),"—")</f>
         <v>Smile Partners Australia</v>
       </c>
@@ -19788,7 +19810,7 @@
       <c r="A33" s="6"/>
       <c r="B33" s="186"/>
       <c r="C33" s="186"/>
-      <c r="D33" s="280" t="str">
+      <c r="D33" s="278" t="str">
         <f>IFERROR("9.01 — "&amp;INDEX('Input Data'!B:B,MATCH("9.01",'Input Data'!C:C,0)),"—")</f>
         <v>9.01 — L09</v>
       </c>
@@ -19805,7 +19827,7 @@
       <c r="O33" s="183"/>
       <c r="P33" s="183"/>
       <c r="Q33" s="183"/>
-      <c r="R33" s="277" t="str">
+      <c r="R33" s="279" t="str">
         <f>IFERROR("9.02 — "&amp;INDEX('Input Data'!B:B,MATCH("9.02",'Input Data'!C:C,0)),"—")</f>
         <v>9.02 — L09</v>
       </c>
@@ -19826,7 +19848,7 @@
       <c r="A34" s="6"/>
       <c r="B34" s="186"/>
       <c r="C34" s="186"/>
-      <c r="D34" s="280" t="str">
+      <c r="D34" s="278" t="str">
         <f>IFERROR(TEXT(INDEX('Input Data'!F:F,MATCH("9.01",'Input Data'!C:C,0)),"#,##0.0")&amp;" sqm","—")</f>
         <v>453.3 sqm</v>
       </c>
@@ -19843,7 +19865,7 @@
       <c r="O34" s="183"/>
       <c r="P34" s="183"/>
       <c r="Q34" s="183"/>
-      <c r="R34" s="277" t="str">
+      <c r="R34" s="279" t="str">
         <f>IFERROR(TEXT(INDEX('Input Data'!F:F,MATCH("9.02",'Input Data'!C:C,0)),"#,##0.0")&amp;" sqm","—")</f>
         <v>251.0 sqm</v>
       </c>
@@ -19864,7 +19886,7 @@
       <c r="A35" s="6"/>
       <c r="B35" s="186"/>
       <c r="C35" s="186"/>
-      <c r="D35" s="278" t="str">
+      <c r="D35" s="290" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("9.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("9.01",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $1,027 | Net $379,155 pa</v>
       </c>
@@ -19881,7 +19903,7 @@
       <c r="O35" s="183"/>
       <c r="P35" s="183"/>
       <c r="Q35" s="183"/>
-      <c r="R35" s="288" t="str">
+      <c r="R35" s="284" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("9.02",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("9.02",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $985 | Net $190,062 pa</v>
       </c>
@@ -19902,7 +19924,7 @@
       <c r="A36" s="6"/>
       <c r="B36" s="186"/>
       <c r="C36" s="186"/>
-      <c r="D36" s="278" t="str">
+      <c r="D36" s="290" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("9.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("9.01",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $39,972 | Rev: FIXED 3.75%</v>
       </c>
@@ -19919,7 +19941,7 @@
       <c r="O36" s="183"/>
       <c r="P36" s="183"/>
       <c r="Q36" s="183"/>
-      <c r="R36" s="288" t="str">
+      <c r="R36" s="284" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("9.02",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("9.02",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $5,620 | Rev: FIXED 3.5%</v>
       </c>
@@ -19940,9 +19962,9 @@
       <c r="A37" s="6"/>
       <c r="B37" s="186"/>
       <c r="C37" s="186"/>
-      <c r="D37" s="280" t="str">
+      <c r="D37" s="278" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("9.01",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("9.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Jul-27 (1.0 yrs)</v>
+        <v>Exp: Jul-27 (0.9 yrs)</v>
       </c>
       <c r="E37" s="183"/>
       <c r="F37" s="183"/>
@@ -19957,9 +19979,9 @@
       <c r="O37" s="183"/>
       <c r="P37" s="183"/>
       <c r="Q37" s="183"/>
-      <c r="R37" s="277" t="str">
+      <c r="R37" s="279" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("9.02",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("9.02",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Oct-30 (4.3 yrs)</v>
+        <v>Exp: Oct-30 (4.2 yrs)</v>
       </c>
       <c r="S37" s="183"/>
       <c r="T37" s="183"/>
@@ -19978,9 +20000,9 @@
       <c r="A38" s="6"/>
       <c r="B38" s="186"/>
       <c r="C38" s="186"/>
-      <c r="D38" s="280" t="str">
+      <c r="D38" s="278" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("9.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>1.0 yrs remaining</v>
+        <v>0.9 yrs remaining</v>
       </c>
       <c r="E38" s="183"/>
       <c r="F38" s="183"/>
@@ -19995,9 +20017,9 @@
       <c r="O38" s="183"/>
       <c r="P38" s="183"/>
       <c r="Q38" s="183"/>
-      <c r="R38" s="277" t="str">
+      <c r="R38" s="279" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("9.02",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>4.3 yrs remaining</v>
+        <v>4.2 yrs remaining</v>
       </c>
       <c r="S38" s="183"/>
       <c r="T38" s="183"/>
@@ -20016,7 +20038,7 @@
       <c r="A39" s="6"/>
       <c r="B39" s="186"/>
       <c r="C39" s="186"/>
-      <c r="D39" s="280"/>
+      <c r="D39" s="278"/>
       <c r="E39" s="183"/>
       <c r="F39" s="183"/>
       <c r="G39" s="183"/>
@@ -20030,7 +20052,7 @@
       <c r="O39" s="183"/>
       <c r="P39" s="183"/>
       <c r="Q39" s="183"/>
-      <c r="R39" s="275"/>
+      <c r="R39" s="280"/>
       <c r="S39" s="183"/>
       <c r="T39" s="183"/>
       <c r="U39" s="183"/>
@@ -20078,13 +20100,13 @@
     </row>
     <row r="41" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6"/>
-      <c r="B41" s="283" t="s">
+      <c r="B41" s="296" t="s">
         <v>420</v>
       </c>
-      <c r="C41" s="281">
+      <c r="C41" s="289">
         <v>803</v>
       </c>
-      <c r="D41" s="300" t="str">
+      <c r="D41" s="282" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("8.01",'Input Data'!C:C,0)),"—")</f>
         <v>Vanderlande Industries Australia Pty Ltd</v>
       </c>
@@ -20107,7 +20129,7 @@
       <c r="U41" s="183"/>
       <c r="V41" s="183"/>
       <c r="W41" s="183"/>
-      <c r="X41" s="290" t="str">
+      <c r="X41" s="299" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("8.03",'Input Data'!C:C,0)),"—")</f>
         <v>Can Too Foundation Limited</v>
       </c>
@@ -20122,7 +20144,7 @@
       <c r="A42" s="6"/>
       <c r="B42" s="186"/>
       <c r="C42" s="186"/>
-      <c r="D42" s="291" t="str">
+      <c r="D42" s="281" t="str">
         <f>IFERROR("8.01 — "&amp;INDEX('Input Data'!B:B,MATCH("8.01",'Input Data'!C:C,0)),"—")</f>
         <v>8.01 — L08</v>
       </c>
@@ -20145,7 +20167,7 @@
       <c r="U42" s="183"/>
       <c r="V42" s="183"/>
       <c r="W42" s="183"/>
-      <c r="X42" s="277" t="str">
+      <c r="X42" s="279" t="str">
         <f>IFERROR("8.03 — "&amp;INDEX('Input Data'!B:B,MATCH("8.03",'Input Data'!C:C,0)),"—")</f>
         <v>8.03 — L08</v>
       </c>
@@ -20160,7 +20182,7 @@
       <c r="A43" s="6"/>
       <c r="B43" s="186"/>
       <c r="C43" s="186"/>
-      <c r="D43" s="291" t="str">
+      <c r="D43" s="281" t="str">
         <f>IFERROR(TEXT(INDEX('Input Data'!F:F,MATCH("8.01",'Input Data'!C:C,0)),"#,##0.0")&amp;" sqm","—")</f>
         <v>686.7 sqm</v>
       </c>
@@ -20183,7 +20205,7 @@
       <c r="U43" s="183"/>
       <c r="V43" s="183"/>
       <c r="W43" s="183"/>
-      <c r="X43" s="277" t="str">
+      <c r="X43" s="279" t="str">
         <f>IFERROR(TEXT(INDEX('Input Data'!F:F,MATCH("8.03",'Input Data'!C:C,0)),"#,##0.0")&amp;" sqm","—")</f>
         <v>116.3 sqm</v>
       </c>
@@ -20198,7 +20220,7 @@
       <c r="A44" s="6"/>
       <c r="B44" s="186"/>
       <c r="C44" s="186"/>
-      <c r="D44" s="282" t="str">
+      <c r="D44" s="276" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("8.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("8.01",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $990 | Net $536,203 pa</v>
       </c>
@@ -20221,7 +20243,7 @@
       <c r="U44" s="183"/>
       <c r="V44" s="183"/>
       <c r="W44" s="183"/>
-      <c r="X44" s="288" t="str">
+      <c r="X44" s="284" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("8.03",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("8.03",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $990 | Net $71,210 pa</v>
       </c>
@@ -20236,7 +20258,7 @@
       <c r="A45" s="6"/>
       <c r="B45" s="186"/>
       <c r="C45" s="186"/>
-      <c r="D45" s="282" t="str">
+      <c r="D45" s="276" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("8.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("8.01",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $66,218 | Rev: FIXED 4%</v>
       </c>
@@ -20259,7 +20281,7 @@
       <c r="U45" s="183"/>
       <c r="V45" s="183"/>
       <c r="W45" s="183"/>
-      <c r="X45" s="288" t="str">
+      <c r="X45" s="284" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("8.03",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("8.03",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $2,597 | Rev: FIXED 3.75%</v>
       </c>
@@ -20274,9 +20296,9 @@
       <c r="A46" s="6"/>
       <c r="B46" s="186"/>
       <c r="C46" s="186"/>
-      <c r="D46" s="291" t="str">
+      <c r="D46" s="281" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("8.01",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("8.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Jun-28 (2.0 yrs)</v>
+        <v>Exp: Jun-28 (1.9 yrs)</v>
       </c>
       <c r="E46" s="183"/>
       <c r="F46" s="183"/>
@@ -20297,9 +20319,9 @@
       <c r="U46" s="183"/>
       <c r="V46" s="183"/>
       <c r="W46" s="183"/>
-      <c r="X46" s="277" t="str">
+      <c r="X46" s="279" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("8.03",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("8.03",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Oct-30 (4.3 yrs)</v>
+        <v>Exp: Oct-30 (4.2 yrs)</v>
       </c>
       <c r="Y46" s="183"/>
       <c r="Z46" s="183"/>
@@ -20312,9 +20334,9 @@
       <c r="A47" s="6"/>
       <c r="B47" s="186"/>
       <c r="C47" s="186"/>
-      <c r="D47" s="291" t="str">
+      <c r="D47" s="281" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("8.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>2.0 yrs remaining</v>
+        <v>1.9 yrs remaining</v>
       </c>
       <c r="E47" s="183"/>
       <c r="F47" s="183"/>
@@ -20335,9 +20357,9 @@
       <c r="U47" s="183"/>
       <c r="V47" s="183"/>
       <c r="W47" s="183"/>
-      <c r="X47" s="277" t="str">
+      <c r="X47" s="279" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("8.03",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>4.3 yrs remaining</v>
+        <v>4.2 yrs remaining</v>
       </c>
       <c r="Y47" s="183"/>
       <c r="Z47" s="183"/>
@@ -20350,7 +20372,7 @@
       <c r="A48" s="6"/>
       <c r="B48" s="186"/>
       <c r="C48" s="186"/>
-      <c r="D48" s="291"/>
+      <c r="D48" s="281"/>
       <c r="E48" s="183"/>
       <c r="F48" s="183"/>
       <c r="G48" s="183"/>
@@ -20370,7 +20392,7 @@
       <c r="U48" s="183"/>
       <c r="V48" s="183"/>
       <c r="W48" s="183"/>
-      <c r="X48" s="277"/>
+      <c r="X48" s="279"/>
       <c r="Y48" s="183"/>
       <c r="Z48" s="183"/>
       <c r="AA48" s="183"/>
@@ -20412,13 +20434,13 @@
     </row>
     <row r="50" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="6"/>
-      <c r="B50" s="283" t="s">
+      <c r="B50" s="296" t="s">
         <v>421</v>
       </c>
-      <c r="C50" s="281">
+      <c r="C50" s="289">
         <v>849.6</v>
       </c>
-      <c r="D50" s="293" t="str">
+      <c r="D50" s="285" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("7.01",'Input Data'!C:C,0)),"—")</f>
         <v>Sungrow Australia Group</v>
       </c>
@@ -20435,7 +20457,7 @@
       <c r="O50" s="183"/>
       <c r="P50" s="183"/>
       <c r="Q50" s="183"/>
-      <c r="R50" s="293" t="str">
+      <c r="R50" s="285" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("7.02",'Input Data'!C:C,0)),"—")</f>
         <v>Sungrow Australia Group</v>
       </c>
@@ -20456,7 +20478,7 @@
       <c r="A51" s="6"/>
       <c r="B51" s="186"/>
       <c r="C51" s="186"/>
-      <c r="D51" s="275" t="str">
+      <c r="D51" s="280" t="str">
         <f>IFERROR("7.01 — "&amp;INDEX('Input Data'!B:B,MATCH("7.01",'Input Data'!C:C,0)),"—")</f>
         <v>7.01 — L07</v>
       </c>
@@ -20473,7 +20495,7 @@
       <c r="O51" s="183"/>
       <c r="P51" s="183"/>
       <c r="Q51" s="183"/>
-      <c r="R51" s="275" t="str">
+      <c r="R51" s="280" t="str">
         <f>IFERROR("7.02 — "&amp;INDEX('Input Data'!B:B,MATCH("7.02",'Input Data'!C:C,0)),"—")</f>
         <v>7.02 — L07</v>
       </c>
@@ -20494,7 +20516,7 @@
       <c r="A52" s="6"/>
       <c r="B52" s="186"/>
       <c r="C52" s="186"/>
-      <c r="D52" s="275" t="str">
+      <c r="D52" s="280" t="str">
         <f>IFERROR(TEXT(INDEX('Input Data'!F:F,MATCH("7.01",'Input Data'!C:C,0)),"#,##0.0")&amp;" sqm","—")</f>
         <v>484.1 sqm</v>
       </c>
@@ -20511,7 +20533,7 @@
       <c r="O52" s="183"/>
       <c r="P52" s="183"/>
       <c r="Q52" s="183"/>
-      <c r="R52" s="275" t="str">
+      <c r="R52" s="280" t="str">
         <f>IFERROR(TEXT(INDEX('Input Data'!F:F,MATCH("7.02",'Input Data'!C:C,0)),"#,##0.0")&amp;" sqm","—")</f>
         <v>365.5 sqm</v>
       </c>
@@ -20532,7 +20554,7 @@
       <c r="A53" s="6"/>
       <c r="B53" s="186"/>
       <c r="C53" s="186"/>
-      <c r="D53" s="289" t="str">
+      <c r="D53" s="287" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("7.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("7.01",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $1,050 | Net $399,443 pa</v>
       </c>
@@ -20549,7 +20571,7 @@
       <c r="O53" s="183"/>
       <c r="P53" s="183"/>
       <c r="Q53" s="183"/>
-      <c r="R53" s="289" t="str">
+      <c r="R53" s="287" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("7.02",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("7.02",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $0 | Net $0 pa</v>
       </c>
@@ -20570,7 +20592,7 @@
       <c r="A54" s="6"/>
       <c r="B54" s="186"/>
       <c r="C54" s="186"/>
-      <c r="D54" s="289" t="str">
+      <c r="D54" s="287" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("7.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("7.01",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $42,635 | Rev: FIXED 3.75%</v>
       </c>
@@ -20587,7 +20609,7 @@
       <c r="O54" s="183"/>
       <c r="P54" s="183"/>
       <c r="Q54" s="183"/>
-      <c r="R54" s="289" t="str">
+      <c r="R54" s="287" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("7.02",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("7.02",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $0 | Rev: FIXED 3.75%</v>
       </c>
@@ -20608,9 +20630,9 @@
       <c r="A55" s="6"/>
       <c r="B55" s="186"/>
       <c r="C55" s="186"/>
-      <c r="D55" s="275" t="str">
+      <c r="D55" s="280" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("7.01",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("7.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Sep-29 (3.2 yrs)</v>
+        <v>Exp: Sep-29 (3.1 yrs)</v>
       </c>
       <c r="E55" s="183"/>
       <c r="F55" s="183"/>
@@ -20625,9 +20647,9 @@
       <c r="O55" s="183"/>
       <c r="P55" s="183"/>
       <c r="Q55" s="183"/>
-      <c r="R55" s="275" t="str">
+      <c r="R55" s="280" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("7.02",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("7.02",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Sep-29 (3.2 yrs)</v>
+        <v>Exp: Sep-29 (3.1 yrs)</v>
       </c>
       <c r="S55" s="183"/>
       <c r="T55" s="183"/>
@@ -20646,9 +20668,9 @@
       <c r="A56" s="6"/>
       <c r="B56" s="186"/>
       <c r="C56" s="186"/>
-      <c r="D56" s="275" t="str">
+      <c r="D56" s="280" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("7.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>3.2 yrs remaining</v>
+        <v>3.1 yrs remaining</v>
       </c>
       <c r="E56" s="183"/>
       <c r="F56" s="183"/>
@@ -20663,9 +20685,9 @@
       <c r="O56" s="183"/>
       <c r="P56" s="183"/>
       <c r="Q56" s="183"/>
-      <c r="R56" s="275" t="str">
+      <c r="R56" s="280" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("7.02",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>3.2 yrs remaining</v>
+        <v>3.1 yrs remaining</v>
       </c>
       <c r="S56" s="183"/>
       <c r="T56" s="183"/>
@@ -20684,7 +20706,7 @@
       <c r="A57" s="6"/>
       <c r="B57" s="186"/>
       <c r="C57" s="186"/>
-      <c r="D57" s="275"/>
+      <c r="D57" s="280"/>
       <c r="E57" s="183"/>
       <c r="F57" s="183"/>
       <c r="G57" s="183"/>
@@ -20698,7 +20720,7 @@
       <c r="O57" s="183"/>
       <c r="P57" s="183"/>
       <c r="Q57" s="183"/>
-      <c r="R57" s="275"/>
+      <c r="R57" s="280"/>
       <c r="S57" s="183"/>
       <c r="T57" s="183"/>
       <c r="U57" s="183"/>
@@ -20746,13 +20768,13 @@
     </row>
     <row r="59" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="6"/>
-      <c r="B59" s="283" t="s">
+      <c r="B59" s="296" t="s">
         <v>422</v>
       </c>
-      <c r="C59" s="281">
+      <c r="C59" s="289">
         <v>1095.4000000000001</v>
       </c>
-      <c r="D59" s="287" t="str">
+      <c r="D59" s="294" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("6.01",'Input Data'!C:C,0)),"—")</f>
         <v>Caladas Constructions</v>
       </c>
@@ -20760,7 +20782,7 @@
       <c r="F59" s="183"/>
       <c r="G59" s="183"/>
       <c r="H59" s="183"/>
-      <c r="I59" s="293" t="str">
+      <c r="I59" s="285" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("6.02",'Input Data'!C:C,0)),"—")</f>
         <v>Sungrow Australia Group</v>
       </c>
@@ -20772,7 +20794,7 @@
       <c r="O59" s="183"/>
       <c r="P59" s="183"/>
       <c r="Q59" s="183"/>
-      <c r="R59" s="286" t="str">
+      <c r="R59" s="297" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("6.03",'Input Data'!C:C,0)),"—")</f>
         <v>Keeping Company Pty Ltd</v>
       </c>
@@ -20780,7 +20802,7 @@
       <c r="T59" s="183"/>
       <c r="U59" s="183"/>
       <c r="V59" s="183"/>
-      <c r="W59" s="287" t="str">
+      <c r="W59" s="294" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("6.04",'Input Data'!C:C,0)),"—")</f>
         <v>Elekta Pty Limited</v>
       </c>
@@ -20804,7 +20826,7 @@
       <c r="F60" s="183"/>
       <c r="G60" s="183"/>
       <c r="H60" s="183"/>
-      <c r="I60" s="275" t="str">
+      <c r="I60" s="280" t="str">
         <f>IFERROR("6.02 — "&amp;INDEX('Input Data'!B:B,MATCH("6.02",'Input Data'!C:C,0)),"—")</f>
         <v>6.02 — L06</v>
       </c>
@@ -20816,7 +20838,7 @@
       <c r="O60" s="183"/>
       <c r="P60" s="183"/>
       <c r="Q60" s="183"/>
-      <c r="R60" s="280" t="str">
+      <c r="R60" s="278" t="str">
         <f>IFERROR("6.03 — "&amp;INDEX('Input Data'!B:B,MATCH("6.03",'Input Data'!C:C,0)),"—")</f>
         <v>6.03 — L06</v>
       </c>
@@ -20848,7 +20870,7 @@
       <c r="F61" s="183"/>
       <c r="G61" s="183"/>
       <c r="H61" s="183"/>
-      <c r="I61" s="275" t="str">
+      <c r="I61" s="280" t="str">
         <f>IFERROR(TEXT(INDEX('Input Data'!F:F,MATCH("6.02",'Input Data'!C:C,0)),"#,##0.0")&amp;" sqm","—")</f>
         <v>451.7 sqm</v>
       </c>
@@ -20860,7 +20882,7 @@
       <c r="O61" s="183"/>
       <c r="P61" s="183"/>
       <c r="Q61" s="183"/>
-      <c r="R61" s="280" t="str">
+      <c r="R61" s="278" t="str">
         <f>IFERROR(TEXT(INDEX('Input Data'!F:F,MATCH("6.03",'Input Data'!C:C,0)),"#,##0.0")&amp;" sqm","—")</f>
         <v>189.4 sqm</v>
       </c>
@@ -20884,7 +20906,7 @@
       <c r="A62" s="6"/>
       <c r="B62" s="186"/>
       <c r="C62" s="186"/>
-      <c r="D62" s="284" t="str">
+      <c r="D62" s="286" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("6.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("6.01",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $920 | Net $-340,767 pa</v>
       </c>
@@ -20892,7 +20914,7 @@
       <c r="F62" s="183"/>
       <c r="G62" s="183"/>
       <c r="H62" s="183"/>
-      <c r="I62" s="289" t="str">
+      <c r="I62" s="287" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("6.02",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("6.02",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $955 | Net $276,809 pa</v>
       </c>
@@ -20904,7 +20926,7 @@
       <c r="O62" s="183"/>
       <c r="P62" s="183"/>
       <c r="Q62" s="183"/>
-      <c r="R62" s="278" t="str">
+      <c r="R62" s="290" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("6.03",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("6.03",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $1,020 | Net $206,139 pa</v>
       </c>
@@ -20912,7 +20934,7 @@
       <c r="T62" s="183"/>
       <c r="U62" s="183"/>
       <c r="V62" s="183"/>
-      <c r="W62" s="284" t="str">
+      <c r="W62" s="286" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("6.04",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("6.04",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $920 | Net $165,501 pa</v>
       </c>
@@ -20928,7 +20950,7 @@
       <c r="A63" s="6"/>
       <c r="B63" s="186"/>
       <c r="C63" s="186"/>
-      <c r="D63" s="284" t="str">
+      <c r="D63" s="286" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("6.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("6.01",'Input Data'!C:C,0)),"—")</f>
         <v xml:space="preserve">Outg $0 | Rev: </v>
       </c>
@@ -20936,7 +20958,7 @@
       <c r="F63" s="183"/>
       <c r="G63" s="183"/>
       <c r="H63" s="183"/>
-      <c r="I63" s="289" t="str">
+      <c r="I63" s="287" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("6.02",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("6.02",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $39,813 | Rev: FIXED 3.75%</v>
       </c>
@@ -20948,7 +20970,7 @@
       <c r="O63" s="183"/>
       <c r="P63" s="183"/>
       <c r="Q63" s="183"/>
-      <c r="R63" s="278" t="str">
+      <c r="R63" s="290" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("6.03",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("6.03",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $16,709 | Rev: FIXED 3.5%</v>
       </c>
@@ -20956,7 +20978,7 @@
       <c r="T63" s="183"/>
       <c r="U63" s="183"/>
       <c r="V63" s="183"/>
-      <c r="W63" s="284" t="str">
+      <c r="W63" s="286" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("6.04",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("6.04",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $17,620 | Rev: FIXED (3.75%)</v>
       </c>
@@ -20974,15 +20996,15 @@
       <c r="C64" s="186"/>
       <c r="D64" s="274" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("6.01",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("6.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Jun-32 (6.0 yrs)</v>
+        <v>Exp: Jun-32 (5.9 yrs)</v>
       </c>
       <c r="E64" s="183"/>
       <c r="F64" s="183"/>
       <c r="G64" s="183"/>
       <c r="H64" s="183"/>
-      <c r="I64" s="275" t="str">
+      <c r="I64" s="280" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("6.02",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("6.02",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Sep-29 (3.2 yrs)</v>
+        <v>Exp: Sep-29 (3.1 yrs)</v>
       </c>
       <c r="J64" s="183"/>
       <c r="K64" s="183"/>
@@ -20992,9 +21014,9 @@
       <c r="O64" s="183"/>
       <c r="P64" s="183"/>
       <c r="Q64" s="183"/>
-      <c r="R64" s="280" t="str">
+      <c r="R64" s="278" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("6.03",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("6.03",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: May-27 (0.9 yrs)</v>
+        <v>Exp: May-27 (0.8 yrs)</v>
       </c>
       <c r="S64" s="183"/>
       <c r="T64" s="183"/>
@@ -21002,7 +21024,7 @@
       <c r="V64" s="183"/>
       <c r="W64" s="274" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("6.04",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("6.04",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Jul-32 (6.1 yrs)</v>
+        <v>Exp: Jul-32 (6.0 yrs)</v>
       </c>
       <c r="X64" s="183"/>
       <c r="Y64" s="183"/>
@@ -21018,15 +21040,15 @@
       <c r="C65" s="186"/>
       <c r="D65" s="274" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("6.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>6.0 yrs remaining</v>
+        <v>5.9 yrs remaining</v>
       </c>
       <c r="E65" s="183"/>
       <c r="F65" s="183"/>
       <c r="G65" s="183"/>
       <c r="H65" s="183"/>
-      <c r="I65" s="275" t="str">
+      <c r="I65" s="280" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("6.02",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>3.2 yrs remaining</v>
+        <v>3.1 yrs remaining</v>
       </c>
       <c r="J65" s="183"/>
       <c r="K65" s="183"/>
@@ -21036,9 +21058,9 @@
       <c r="O65" s="183"/>
       <c r="P65" s="183"/>
       <c r="Q65" s="183"/>
-      <c r="R65" s="280" t="str">
+      <c r="R65" s="278" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("6.03",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>0.9 yrs remaining</v>
+        <v>0.8 yrs remaining</v>
       </c>
       <c r="S65" s="183"/>
       <c r="T65" s="183"/>
@@ -21046,7 +21068,7 @@
       <c r="V65" s="183"/>
       <c r="W65" s="274" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("6.04",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>6.1 yrs remaining</v>
+        <v>6.0 yrs remaining</v>
       </c>
       <c r="X65" s="183"/>
       <c r="Y65" s="183"/>
@@ -21060,12 +21082,12 @@
       <c r="A66" s="6"/>
       <c r="B66" s="186"/>
       <c r="C66" s="186"/>
-      <c r="D66" s="285"/>
+      <c r="D66" s="275"/>
       <c r="E66" s="183"/>
       <c r="F66" s="183"/>
       <c r="G66" s="183"/>
       <c r="H66" s="183"/>
-      <c r="I66" s="275"/>
+      <c r="I66" s="280"/>
       <c r="J66" s="183"/>
       <c r="K66" s="183"/>
       <c r="L66" s="183"/>
@@ -21074,7 +21096,7 @@
       <c r="O66" s="183"/>
       <c r="P66" s="183"/>
       <c r="Q66" s="183"/>
-      <c r="R66" s="280"/>
+      <c r="R66" s="278"/>
       <c r="S66" s="183"/>
       <c r="T66" s="183"/>
       <c r="U66" s="183"/>
@@ -21122,13 +21144,13 @@
     </row>
     <row r="68" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="6"/>
-      <c r="B68" s="283" t="s">
+      <c r="B68" s="296" t="s">
         <v>423</v>
       </c>
-      <c r="C68" s="281">
+      <c r="C68" s="289">
         <v>1080.4000000000001</v>
       </c>
-      <c r="D68" s="287" t="str">
+      <c r="D68" s="294" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("5.01",'Input Data'!C:C,0)),"—")</f>
         <v>Fitness First Australia Pty Limited</v>
       </c>
@@ -21141,7 +21163,7 @@
       <c r="K68" s="183"/>
       <c r="L68" s="183"/>
       <c r="M68" s="183"/>
-      <c r="N68" s="293" t="str">
+      <c r="N68" s="285" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("5.03",'Input Data'!C:C,0)),"—")</f>
         <v>Asterx Pty Ltd</v>
       </c>
@@ -21149,7 +21171,7 @@
       <c r="P68" s="183"/>
       <c r="Q68" s="183"/>
       <c r="R68" s="183"/>
-      <c r="S68" s="293" t="str">
+      <c r="S68" s="285" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("5.04",'Input Data'!C:C,0)),"—")</f>
         <v>Auctionsplus Pty Ltd</v>
       </c>
@@ -21182,7 +21204,7 @@
       <c r="K69" s="183"/>
       <c r="L69" s="183"/>
       <c r="M69" s="183"/>
-      <c r="N69" s="275" t="str">
+      <c r="N69" s="280" t="str">
         <f>IFERROR("5.03 — "&amp;INDEX('Input Data'!B:B,MATCH("5.03",'Input Data'!C:C,0)),"—")</f>
         <v>5.03 — L05</v>
       </c>
@@ -21190,7 +21212,7 @@
       <c r="P69" s="183"/>
       <c r="Q69" s="183"/>
       <c r="R69" s="183"/>
-      <c r="S69" s="275" t="str">
+      <c r="S69" s="280" t="str">
         <f>IFERROR("5.04 — "&amp;INDEX('Input Data'!B:B,MATCH("5.04",'Input Data'!C:C,0)),"—")</f>
         <v>5.04 — L05</v>
       </c>
@@ -21223,7 +21245,7 @@
       <c r="K70" s="183"/>
       <c r="L70" s="183"/>
       <c r="M70" s="183"/>
-      <c r="N70" s="275" t="str">
+      <c r="N70" s="280" t="str">
         <f>IFERROR(TEXT(INDEX('Input Data'!F:F,MATCH("5.03",'Input Data'!C:C,0)),"#,##0.0")&amp;" sqm","—")</f>
         <v>229.8 sqm</v>
       </c>
@@ -21231,7 +21253,7 @@
       <c r="P70" s="183"/>
       <c r="Q70" s="183"/>
       <c r="R70" s="183"/>
-      <c r="S70" s="275" t="str">
+      <c r="S70" s="280" t="str">
         <f>IFERROR(TEXT(INDEX('Input Data'!F:F,MATCH("5.04",'Input Data'!C:C,0)),"#,##0.0")&amp;" sqm","—")</f>
         <v>413.5 sqm</v>
       </c>
@@ -21251,7 +21273,7 @@
       <c r="A71" s="6"/>
       <c r="B71" s="186"/>
       <c r="C71" s="186"/>
-      <c r="D71" s="284" t="str">
+      <c r="D71" s="286" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("5.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("5.01",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $856 | Net $377,056 pa</v>
       </c>
@@ -21264,7 +21286,7 @@
       <c r="K71" s="183"/>
       <c r="L71" s="183"/>
       <c r="M71" s="183"/>
-      <c r="N71" s="289" t="str">
+      <c r="N71" s="287" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("5.03",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("5.03",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $877 | Net $223,316 pa</v>
       </c>
@@ -21272,7 +21294,7 @@
       <c r="P71" s="183"/>
       <c r="Q71" s="183"/>
       <c r="R71" s="183"/>
-      <c r="S71" s="289" t="str">
+      <c r="S71" s="287" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("5.04",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("5.04",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $1,006 | Net $358,546 pa</v>
       </c>
@@ -21292,7 +21314,7 @@
       <c r="A72" s="6"/>
       <c r="B72" s="186"/>
       <c r="C72" s="186"/>
-      <c r="D72" s="284" t="str">
+      <c r="D72" s="286" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("5.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("5.01",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $0 | Rev: FIXED 4%</v>
       </c>
@@ -21305,7 +21327,7 @@
       <c r="K72" s="183"/>
       <c r="L72" s="183"/>
       <c r="M72" s="183"/>
-      <c r="N72" s="289" t="str">
+      <c r="N72" s="287" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("5.03",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("5.03",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $15,475 | Rev: FIXED 3.5%</v>
       </c>
@@ -21313,7 +21335,7 @@
       <c r="P72" s="183"/>
       <c r="Q72" s="183"/>
       <c r="R72" s="183"/>
-      <c r="S72" s="289" t="str">
+      <c r="S72" s="287" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("5.04",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("5.04",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $32,592 | Rev: FIXED 4%</v>
       </c>
@@ -21335,7 +21357,7 @@
       <c r="C73" s="186"/>
       <c r="D73" s="274" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("5.01",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("5.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Jun-31 (5.0 yrs)</v>
+        <v>Exp: Jun-31 (4.9 yrs)</v>
       </c>
       <c r="E73" s="183"/>
       <c r="F73" s="183"/>
@@ -21346,17 +21368,17 @@
       <c r="K73" s="183"/>
       <c r="L73" s="183"/>
       <c r="M73" s="183"/>
-      <c r="N73" s="275" t="str">
+      <c r="N73" s="280" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("5.03",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("5.03",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: May-29 (2.9 yrs)</v>
+        <v>Exp: May-29 (2.8 yrs)</v>
       </c>
       <c r="O73" s="183"/>
       <c r="P73" s="183"/>
       <c r="Q73" s="183"/>
       <c r="R73" s="183"/>
-      <c r="S73" s="275" t="str">
+      <c r="S73" s="280" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("5.04",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("5.04",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Feb-29 (2.7 yrs)</v>
+        <v>Exp: Feb-29 (2.6 yrs)</v>
       </c>
       <c r="T73" s="183"/>
       <c r="U73" s="183"/>
@@ -21376,7 +21398,7 @@
       <c r="C74" s="186"/>
       <c r="D74" s="274" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("5.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>5.0 yrs remaining</v>
+        <v>4.9 yrs remaining</v>
       </c>
       <c r="E74" s="183"/>
       <c r="F74" s="183"/>
@@ -21387,17 +21409,17 @@
       <c r="K74" s="183"/>
       <c r="L74" s="183"/>
       <c r="M74" s="183"/>
-      <c r="N74" s="275" t="str">
+      <c r="N74" s="280" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("5.03",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>2.9 yrs remaining</v>
+        <v>2.8 yrs remaining</v>
       </c>
       <c r="O74" s="183"/>
       <c r="P74" s="183"/>
       <c r="Q74" s="183"/>
       <c r="R74" s="183"/>
-      <c r="S74" s="275" t="str">
+      <c r="S74" s="280" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("5.04",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>2.7 yrs remaining</v>
+        <v>2.6 yrs remaining</v>
       </c>
       <c r="T74" s="183"/>
       <c r="U74" s="183"/>
@@ -21425,12 +21447,12 @@
       <c r="K75" s="183"/>
       <c r="L75" s="183"/>
       <c r="M75" s="183"/>
-      <c r="N75" s="275"/>
+      <c r="N75" s="280"/>
       <c r="O75" s="183"/>
       <c r="P75" s="183"/>
       <c r="Q75" s="183"/>
       <c r="R75" s="183"/>
-      <c r="S75" s="275"/>
+      <c r="S75" s="280"/>
       <c r="T75" s="183"/>
       <c r="U75" s="183"/>
       <c r="V75" s="183"/>
@@ -21477,13 +21499,13 @@
     </row>
     <row r="77" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="6"/>
-      <c r="B77" s="283" t="s">
+      <c r="B77" s="296" t="s">
         <v>424</v>
       </c>
-      <c r="C77" s="281">
+      <c r="C77" s="289">
         <v>1047</v>
       </c>
-      <c r="D77" s="287" t="str">
+      <c r="D77" s="294" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("4.01",'Input Data'!C:C,0)),"—")</f>
         <v>Fitness First Australia Pty Limited</v>
       </c>
@@ -21588,7 +21610,7 @@
       <c r="A80" s="6"/>
       <c r="B80" s="186"/>
       <c r="C80" s="186"/>
-      <c r="D80" s="284" t="str">
+      <c r="D80" s="286" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("4.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("4.01",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $856 | Net $906,078 pa</v>
       </c>
@@ -21623,7 +21645,7 @@
       <c r="A81" s="6"/>
       <c r="B81" s="186"/>
       <c r="C81" s="186"/>
-      <c r="D81" s="284" t="str">
+      <c r="D81" s="286" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("4.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("4.01",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $0 | Rev: FIXED 4%</v>
       </c>
@@ -21660,7 +21682,7 @@
       <c r="C82" s="186"/>
       <c r="D82" s="274" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("4.01",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("4.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Jun-31 (5.0 yrs)</v>
+        <v>Exp: Jun-31 (4.9 yrs)</v>
       </c>
       <c r="E82" s="183"/>
       <c r="F82" s="183"/>
@@ -21695,7 +21717,7 @@
       <c r="C83" s="186"/>
       <c r="D83" s="274" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("4.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>5.0 yrs remaining</v>
+        <v>4.9 yrs remaining</v>
       </c>
       <c r="E83" s="183"/>
       <c r="F83" s="183"/>
@@ -21790,13 +21812,13 @@
     </row>
     <row r="86" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="6"/>
-      <c r="B86" s="283" t="s">
+      <c r="B86" s="296" t="s">
         <v>425</v>
       </c>
-      <c r="C86" s="281">
+      <c r="C86" s="289">
         <v>903.2</v>
       </c>
-      <c r="D86" s="300" t="str">
+      <c r="D86" s="282" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("3.01",'Input Data'!C:C,0)),"—")</f>
         <v>Sydney Smiletree Pty Ltd</v>
       </c>
@@ -21804,7 +21826,7 @@
       <c r="F86" s="183"/>
       <c r="G86" s="183"/>
       <c r="H86" s="183"/>
-      <c r="I86" s="287" t="str">
+      <c r="I86" s="294" t="str">
         <f>IFERROR(INDEX('Input Data'!D:D,MATCH("3.02",'Input Data'!C:C,0)),"—")</f>
         <v>Fitness First Australia Pty Limited</v>
       </c>
@@ -21834,7 +21856,7 @@
       <c r="A87" s="6"/>
       <c r="B87" s="186"/>
       <c r="C87" s="186"/>
-      <c r="D87" s="291" t="str">
+      <c r="D87" s="281" t="str">
         <f>IFERROR("3.01 — "&amp;INDEX('Input Data'!B:B,MATCH("3.01",'Input Data'!C:C,0)),"—")</f>
         <v>3.01 — L03</v>
       </c>
@@ -21872,7 +21894,7 @@
       <c r="A88" s="6"/>
       <c r="B88" s="186"/>
       <c r="C88" s="186"/>
-      <c r="D88" s="291" t="str">
+      <c r="D88" s="281" t="str">
         <f>IFERROR(TEXT(INDEX('Input Data'!F:F,MATCH("3.01",'Input Data'!C:C,0)),"#,##0.0")&amp;" sqm","—")</f>
         <v>107.7 sqm</v>
       </c>
@@ -21910,7 +21932,7 @@
       <c r="A89" s="6"/>
       <c r="B89" s="186"/>
       <c r="C89" s="186"/>
-      <c r="D89" s="282" t="str">
+      <c r="D89" s="276" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("3.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("3.01",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $1,342 | Net $163,519 pa</v>
       </c>
@@ -21918,7 +21940,7 @@
       <c r="F89" s="183"/>
       <c r="G89" s="183"/>
       <c r="H89" s="183"/>
-      <c r="I89" s="284" t="str">
+      <c r="I89" s="286" t="str">
         <f>IFERROR("Face $"&amp;TEXT(INDEX('Input Data'!J:J,MATCH("3.02",'Input Data'!C:C,0)),"#,##0")&amp;" | Net $"&amp;TEXT(INDEX('Input Data'!Q:Q,MATCH("3.02",'Input Data'!C:C,0)),"#,##0 pa"),"—")</f>
         <v>Face $856 | Net $680,709 pa</v>
       </c>
@@ -21948,7 +21970,7 @@
       <c r="A90" s="6"/>
       <c r="B90" s="186"/>
       <c r="C90" s="186"/>
-      <c r="D90" s="282" t="str">
+      <c r="D90" s="276" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("3.01",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("3.01",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $7,244 | Rev: FIXED 4%</v>
       </c>
@@ -21956,7 +21978,7 @@
       <c r="F90" s="183"/>
       <c r="G90" s="183"/>
       <c r="H90" s="183"/>
-      <c r="I90" s="284" t="str">
+      <c r="I90" s="286" t="str">
         <f>IFERROR("Outg $"&amp;TEXT(INDEX('Input Data'!M:M,MATCH("3.02",'Input Data'!C:C,0)),"#,##0")&amp;" | Rev: "&amp;INDEX('Input Data'!S:S,MATCH("3.02",'Input Data'!C:C,0)),"—")</f>
         <v>Outg $0 | Rev: FIXED 4%</v>
       </c>
@@ -21986,9 +22008,9 @@
       <c r="A91" s="6"/>
       <c r="B91" s="186"/>
       <c r="C91" s="186"/>
-      <c r="D91" s="291" t="str">
+      <c r="D91" s="281" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("3.01",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("3.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Dec-28 (2.5 yrs)</v>
+        <v>Exp: Dec-28 (2.4 yrs)</v>
       </c>
       <c r="E91" s="183"/>
       <c r="F91" s="183"/>
@@ -21996,7 +22018,7 @@
       <c r="H91" s="183"/>
       <c r="I91" s="274" t="str">
         <f ca="1">IFERROR("Exp: "&amp;TEXT(INDEX('Input Data'!H:H,MATCH("3.02",'Input Data'!C:C,0)),"MMM-YY")&amp;" ("&amp;TEXT(INDEX('Input Data'!V:V,MATCH("3.02",'Input Data'!C:C,0)),"0.0")&amp;" yrs)","—")</f>
-        <v>Exp: Jun-31 (5.0 yrs)</v>
+        <v>Exp: Jun-31 (4.9 yrs)</v>
       </c>
       <c r="J91" s="183"/>
       <c r="K91" s="183"/>
@@ -22024,9 +22046,9 @@
       <c r="A92" s="6"/>
       <c r="B92" s="186"/>
       <c r="C92" s="186"/>
-      <c r="D92" s="291" t="str">
+      <c r="D92" s="281" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("3.01",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>2.5 yrs remaining</v>
+        <v>2.4 yrs remaining</v>
       </c>
       <c r="E92" s="183"/>
       <c r="F92" s="183"/>
@@ -22034,7 +22056,7 @@
       <c r="H92" s="183"/>
       <c r="I92" s="274" t="str">
         <f ca="1">IFERROR(TEXT(INDEX('Input Data'!V:V,MATCH("3.02",'Input Data'!C:C,0)),"0.0")&amp;" yrs remaining","—")</f>
-        <v>5.0 yrs remaining</v>
+        <v>4.9 yrs remaining</v>
       </c>
       <c r="J92" s="183"/>
       <c r="K92" s="183"/>
@@ -22062,7 +22084,7 @@
       <c r="A93" s="6"/>
       <c r="B93" s="186"/>
       <c r="C93" s="186"/>
-      <c r="D93" s="291"/>
+      <c r="D93" s="281"/>
       <c r="E93" s="183"/>
       <c r="F93" s="183"/>
       <c r="G93" s="183"/>
@@ -22124,13 +22146,13 @@
     </row>
     <row r="95" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="6"/>
-      <c r="B95" s="283" t="s">
+      <c r="B95" s="296" t="s">
         <v>426</v>
       </c>
-      <c r="C95" s="297" t="s">
+      <c r="C95" s="298" t="s">
         <v>178</v>
       </c>
-      <c r="D95" s="301" t="s">
+      <c r="D95" s="288" t="s">
         <v>427</v>
       </c>
       <c r="E95" s="183"/>
@@ -22164,7 +22186,7 @@
       <c r="A96" s="6"/>
       <c r="B96" s="186"/>
       <c r="C96" s="186"/>
-      <c r="D96" s="280" t="s">
+      <c r="D96" s="278" t="s">
         <v>428</v>
       </c>
       <c r="E96" s="183"/>
@@ -22198,7 +22220,7 @@
       <c r="A97" s="6"/>
       <c r="B97" s="186"/>
       <c r="C97" s="186"/>
-      <c r="D97" s="280" t="s">
+      <c r="D97" s="278" t="s">
         <v>178</v>
       </c>
       <c r="E97" s="183"/>
@@ -22232,7 +22254,7 @@
       <c r="A98" s="6"/>
       <c r="B98" s="186"/>
       <c r="C98" s="186"/>
-      <c r="D98" s="278" t="s">
+      <c r="D98" s="290" t="s">
         <v>429</v>
       </c>
       <c r="E98" s="183"/>
@@ -22266,7 +22288,7 @@
       <c r="A99" s="6"/>
       <c r="B99" s="186"/>
       <c r="C99" s="186"/>
-      <c r="D99" s="278" t="s">
+      <c r="D99" s="290" t="s">
         <v>430</v>
       </c>
       <c r="E99" s="183"/>
@@ -22300,7 +22322,7 @@
       <c r="A100" s="6"/>
       <c r="B100" s="186"/>
       <c r="C100" s="186"/>
-      <c r="D100" s="280" t="s">
+      <c r="D100" s="278" t="s">
         <v>431</v>
       </c>
       <c r="E100" s="183"/>
@@ -22334,7 +22356,7 @@
       <c r="A101" s="6"/>
       <c r="B101" s="186"/>
       <c r="C101" s="186"/>
-      <c r="D101" s="280" t="s">
+      <c r="D101" s="278" t="s">
         <v>432</v>
       </c>
       <c r="E101" s="183"/>
@@ -22368,7 +22390,7 @@
       <c r="A102" s="6"/>
       <c r="B102" s="186"/>
       <c r="C102" s="186"/>
-      <c r="D102" s="280"/>
+      <c r="D102" s="278"/>
       <c r="E102" s="183"/>
       <c r="F102" s="183"/>
       <c r="G102" s="183"/>
@@ -22432,7 +22454,7 @@
       <c r="A104" s="6"/>
       <c r="B104" s="68"/>
       <c r="C104" s="68"/>
-      <c r="D104" s="279"/>
+      <c r="D104" s="292"/>
       <c r="E104" s="186"/>
       <c r="F104" s="186"/>
       <c r="G104" s="186"/>
@@ -22494,7 +22516,7 @@
     </row>
     <row r="106" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="6"/>
-      <c r="B106" s="199" t="s">
+      <c r="B106" s="189" t="s">
         <v>433</v>
       </c>
       <c r="C106" s="183"/>
@@ -22530,43 +22552,43 @@
       <c r="A107" s="6"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
-      <c r="D107" s="242" t="s">
+      <c r="D107" s="236" t="s">
         <v>434</v>
       </c>
       <c r="E107" s="183"/>
       <c r="F107" s="183"/>
       <c r="G107" s="6"/>
-      <c r="H107" s="223" t="s">
+      <c r="H107" s="250" t="s">
         <v>261</v>
       </c>
       <c r="I107" s="183"/>
       <c r="J107" s="183"/>
       <c r="K107" s="6"/>
-      <c r="L107" s="227" t="s">
+      <c r="L107" s="226" t="s">
         <v>262</v>
       </c>
       <c r="M107" s="183"/>
       <c r="N107" s="183"/>
       <c r="O107" s="6"/>
-      <c r="P107" s="252" t="s">
+      <c r="P107" s="225" t="s">
         <v>263</v>
       </c>
       <c r="Q107" s="183"/>
       <c r="R107" s="183"/>
       <c r="S107" s="6"/>
-      <c r="T107" s="298" t="s">
+      <c r="T107" s="291" t="s">
         <v>264</v>
       </c>
       <c r="U107" s="183"/>
       <c r="V107" s="183"/>
       <c r="W107" s="6"/>
-      <c r="X107" s="299" t="s">
+      <c r="X107" s="293" t="s">
         <v>265</v>
       </c>
       <c r="Y107" s="183"/>
       <c r="Z107" s="183"/>
       <c r="AA107" s="6"/>
-      <c r="AB107" s="296" t="s">
+      <c r="AB107" s="301" t="s">
         <v>435</v>
       </c>
       <c r="AC107" s="183"/>
@@ -22606,7 +22628,7 @@
     </row>
     <row r="109" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="6"/>
-      <c r="B109" s="260" t="s">
+      <c r="B109" s="268" t="s">
         <v>436</v>
       </c>
       <c r="C109" s="183"/>
@@ -22640,18 +22662,177 @@
     </row>
   </sheetData>
   <mergeCells count="219">
-    <mergeCell ref="L107:N107"/>
-    <mergeCell ref="D64:H64"/>
-    <mergeCell ref="B109:AB109"/>
-    <mergeCell ref="D24:Q24"/>
-    <mergeCell ref="D75:M75"/>
-    <mergeCell ref="D89:H89"/>
-    <mergeCell ref="D14:K14"/>
-    <mergeCell ref="D33:Q33"/>
-    <mergeCell ref="L6:AB6"/>
-    <mergeCell ref="D51:Q51"/>
-    <mergeCell ref="D97:AB97"/>
-    <mergeCell ref="D88:H88"/>
+    <mergeCell ref="D4:AB4"/>
+    <mergeCell ref="R60:V60"/>
+    <mergeCell ref="C86:C93"/>
+    <mergeCell ref="D90:H90"/>
+    <mergeCell ref="I66:Q66"/>
+    <mergeCell ref="W66:AB66"/>
+    <mergeCell ref="C68:C75"/>
+    <mergeCell ref="R63:V63"/>
+    <mergeCell ref="L15:AB15"/>
+    <mergeCell ref="L18:AB18"/>
+    <mergeCell ref="D17:K17"/>
+    <mergeCell ref="L8:AB8"/>
+    <mergeCell ref="L10:AB10"/>
+    <mergeCell ref="D77:AB77"/>
+    <mergeCell ref="D39:Q39"/>
+    <mergeCell ref="R56:AB56"/>
+    <mergeCell ref="X44:AB44"/>
+    <mergeCell ref="I61:Q61"/>
+    <mergeCell ref="R62:V62"/>
+    <mergeCell ref="N69:R69"/>
+    <mergeCell ref="D92:H92"/>
+    <mergeCell ref="D78:AB78"/>
+    <mergeCell ref="R52:AB52"/>
+    <mergeCell ref="D26:Q26"/>
+    <mergeCell ref="X48:AB48"/>
+    <mergeCell ref="D35:Q35"/>
+    <mergeCell ref="X43:AB43"/>
+    <mergeCell ref="B95:B102"/>
+    <mergeCell ref="R64:V64"/>
+    <mergeCell ref="D44:W44"/>
+    <mergeCell ref="D107:F107"/>
+    <mergeCell ref="D63:H63"/>
+    <mergeCell ref="D74:M74"/>
+    <mergeCell ref="C77:C84"/>
+    <mergeCell ref="D68:M68"/>
+    <mergeCell ref="I86:AB86"/>
+    <mergeCell ref="I89:AB89"/>
+    <mergeCell ref="D65:H65"/>
+    <mergeCell ref="AB107:AD107"/>
+    <mergeCell ref="D98:AB98"/>
+    <mergeCell ref="D52:Q52"/>
+    <mergeCell ref="D57:Q57"/>
+    <mergeCell ref="N71:R71"/>
+    <mergeCell ref="D69:M69"/>
+    <mergeCell ref="W65:AB65"/>
+    <mergeCell ref="S69:AB69"/>
+    <mergeCell ref="X46:AB46"/>
+    <mergeCell ref="B41:B48"/>
+    <mergeCell ref="I90:AB90"/>
+    <mergeCell ref="P107:R107"/>
+    <mergeCell ref="B50:B57"/>
+    <mergeCell ref="D7:K7"/>
+    <mergeCell ref="D81:AB81"/>
+    <mergeCell ref="D48:W48"/>
+    <mergeCell ref="D16:K16"/>
+    <mergeCell ref="I59:Q59"/>
+    <mergeCell ref="L7:AB7"/>
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="D20:K20"/>
+    <mergeCell ref="N70:R70"/>
+    <mergeCell ref="B32:B39"/>
+    <mergeCell ref="L12:AB12"/>
+    <mergeCell ref="R25:AB25"/>
+    <mergeCell ref="C5:C12"/>
+    <mergeCell ref="D29:Q29"/>
+    <mergeCell ref="D5:K5"/>
+    <mergeCell ref="D42:W42"/>
+    <mergeCell ref="D23:Q23"/>
+    <mergeCell ref="D38:Q38"/>
+    <mergeCell ref="R33:AB33"/>
+    <mergeCell ref="D6:K6"/>
+    <mergeCell ref="L5:AB5"/>
+    <mergeCell ref="R28:AB28"/>
+    <mergeCell ref="W62:AB62"/>
+    <mergeCell ref="R59:V59"/>
+    <mergeCell ref="D18:K18"/>
+    <mergeCell ref="D8:K8"/>
+    <mergeCell ref="D25:Q25"/>
+    <mergeCell ref="N72:R72"/>
+    <mergeCell ref="D11:K11"/>
+    <mergeCell ref="R34:AB34"/>
+    <mergeCell ref="D10:K10"/>
+    <mergeCell ref="D79:AB79"/>
+    <mergeCell ref="D27:Q27"/>
+    <mergeCell ref="R65:V65"/>
+    <mergeCell ref="L14:AB14"/>
+    <mergeCell ref="S71:AB71"/>
+    <mergeCell ref="N73:R73"/>
+    <mergeCell ref="W59:AB59"/>
+    <mergeCell ref="D45:W45"/>
+    <mergeCell ref="R30:AB30"/>
+    <mergeCell ref="W61:AB61"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="R55:AB55"/>
+    <mergeCell ref="D53:Q53"/>
+    <mergeCell ref="R51:AB51"/>
+    <mergeCell ref="R54:AB54"/>
+    <mergeCell ref="R32:AB32"/>
+    <mergeCell ref="D37:Q37"/>
+    <mergeCell ref="C95:C102"/>
+    <mergeCell ref="B106:AB106"/>
+    <mergeCell ref="D55:Q55"/>
+    <mergeCell ref="D30:Q30"/>
+    <mergeCell ref="B68:B75"/>
+    <mergeCell ref="C32:C39"/>
+    <mergeCell ref="C23:C30"/>
+    <mergeCell ref="B5:B12"/>
+    <mergeCell ref="W64:AB64"/>
+    <mergeCell ref="D54:Q54"/>
+    <mergeCell ref="R23:AB23"/>
+    <mergeCell ref="D60:H60"/>
+    <mergeCell ref="R61:V61"/>
+    <mergeCell ref="S68:AB68"/>
+    <mergeCell ref="D71:M71"/>
+    <mergeCell ref="D19:K19"/>
+    <mergeCell ref="L17:AB17"/>
+    <mergeCell ref="W63:AB63"/>
+    <mergeCell ref="D102:AB102"/>
+    <mergeCell ref="D73:M73"/>
+    <mergeCell ref="D83:AB83"/>
+    <mergeCell ref="R57:AB57"/>
+    <mergeCell ref="L19:AB19"/>
+    <mergeCell ref="I62:Q62"/>
+    <mergeCell ref="B86:B93"/>
+    <mergeCell ref="C41:C48"/>
+    <mergeCell ref="X47:AB47"/>
+    <mergeCell ref="I64:Q64"/>
+    <mergeCell ref="S72:AB72"/>
+    <mergeCell ref="D32:Q32"/>
+    <mergeCell ref="C50:C57"/>
+    <mergeCell ref="B14:B21"/>
+    <mergeCell ref="R27:AB27"/>
+    <mergeCell ref="B23:B30"/>
+    <mergeCell ref="R36:AB36"/>
+    <mergeCell ref="D15:K15"/>
+    <mergeCell ref="R38:AB38"/>
+    <mergeCell ref="L16:AB16"/>
+    <mergeCell ref="B59:B66"/>
+    <mergeCell ref="I91:AB91"/>
+    <mergeCell ref="B77:B84"/>
+    <mergeCell ref="C59:C66"/>
+    <mergeCell ref="I60:Q60"/>
+    <mergeCell ref="D93:H93"/>
+    <mergeCell ref="S73:AB73"/>
+    <mergeCell ref="X41:AB41"/>
+    <mergeCell ref="D28:Q28"/>
+    <mergeCell ref="R66:V66"/>
+    <mergeCell ref="L20:AB20"/>
+    <mergeCell ref="S70:AB70"/>
+    <mergeCell ref="T107:V107"/>
+    <mergeCell ref="D80:AB80"/>
+    <mergeCell ref="D47:W47"/>
+    <mergeCell ref="I65:Q65"/>
+    <mergeCell ref="D96:AB96"/>
+    <mergeCell ref="D104:AB104"/>
+    <mergeCell ref="R53:AB53"/>
+    <mergeCell ref="X107:Z107"/>
+    <mergeCell ref="D70:M70"/>
+    <mergeCell ref="I88:AB88"/>
+    <mergeCell ref="N74:R74"/>
+    <mergeCell ref="D72:M72"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="D50:Q50"/>
+    <mergeCell ref="R39:AB39"/>
+    <mergeCell ref="S74:AB74"/>
+    <mergeCell ref="D34:Q34"/>
+    <mergeCell ref="R29:AB29"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="D99:AB99"/>
+    <mergeCell ref="X45:AB45"/>
+    <mergeCell ref="D101:AB101"/>
     <mergeCell ref="A2:AD2"/>
     <mergeCell ref="R24:AB24"/>
     <mergeCell ref="R37:AB37"/>
@@ -22676,6 +22857,18 @@
     <mergeCell ref="D95:AB95"/>
     <mergeCell ref="D3:AB3"/>
     <mergeCell ref="C14:C21"/>
+    <mergeCell ref="L107:N107"/>
+    <mergeCell ref="D64:H64"/>
+    <mergeCell ref="B109:AB109"/>
+    <mergeCell ref="D24:Q24"/>
+    <mergeCell ref="D75:M75"/>
+    <mergeCell ref="D89:H89"/>
+    <mergeCell ref="D14:K14"/>
+    <mergeCell ref="D33:Q33"/>
+    <mergeCell ref="L6:AB6"/>
+    <mergeCell ref="D51:Q51"/>
+    <mergeCell ref="D97:AB97"/>
+    <mergeCell ref="D88:H88"/>
     <mergeCell ref="D46:W46"/>
     <mergeCell ref="N75:R75"/>
     <mergeCell ref="D36:Q36"/>
@@ -22688,177 +22881,6 @@
     <mergeCell ref="D87:H87"/>
     <mergeCell ref="I63:Q63"/>
     <mergeCell ref="I87:AB87"/>
-    <mergeCell ref="L20:AB20"/>
-    <mergeCell ref="S70:AB70"/>
-    <mergeCell ref="T107:V107"/>
-    <mergeCell ref="D80:AB80"/>
-    <mergeCell ref="D47:W47"/>
-    <mergeCell ref="I65:Q65"/>
-    <mergeCell ref="D96:AB96"/>
-    <mergeCell ref="D104:AB104"/>
-    <mergeCell ref="R53:AB53"/>
-    <mergeCell ref="X107:Z107"/>
-    <mergeCell ref="D70:M70"/>
-    <mergeCell ref="I88:AB88"/>
-    <mergeCell ref="N74:R74"/>
-    <mergeCell ref="D72:M72"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="D50:Q50"/>
-    <mergeCell ref="R39:AB39"/>
-    <mergeCell ref="S74:AB74"/>
-    <mergeCell ref="D34:Q34"/>
-    <mergeCell ref="R29:AB29"/>
-    <mergeCell ref="B86:B93"/>
-    <mergeCell ref="C41:C48"/>
-    <mergeCell ref="X47:AB47"/>
-    <mergeCell ref="I64:Q64"/>
-    <mergeCell ref="S72:AB72"/>
-    <mergeCell ref="D32:Q32"/>
-    <mergeCell ref="C50:C57"/>
-    <mergeCell ref="B14:B21"/>
-    <mergeCell ref="R27:AB27"/>
-    <mergeCell ref="B23:B30"/>
-    <mergeCell ref="R36:AB36"/>
-    <mergeCell ref="D15:K15"/>
-    <mergeCell ref="R38:AB38"/>
-    <mergeCell ref="L16:AB16"/>
-    <mergeCell ref="B59:B66"/>
-    <mergeCell ref="I91:AB91"/>
-    <mergeCell ref="B77:B84"/>
-    <mergeCell ref="C95:C102"/>
-    <mergeCell ref="B106:AB106"/>
-    <mergeCell ref="D55:Q55"/>
-    <mergeCell ref="D30:Q30"/>
-    <mergeCell ref="B68:B75"/>
-    <mergeCell ref="C32:C39"/>
-    <mergeCell ref="C23:C30"/>
-    <mergeCell ref="B5:B12"/>
-    <mergeCell ref="W64:AB64"/>
-    <mergeCell ref="D54:Q54"/>
-    <mergeCell ref="R23:AB23"/>
-    <mergeCell ref="D60:H60"/>
-    <mergeCell ref="R61:V61"/>
-    <mergeCell ref="S68:AB68"/>
-    <mergeCell ref="D71:M71"/>
-    <mergeCell ref="D19:K19"/>
-    <mergeCell ref="L17:AB17"/>
-    <mergeCell ref="W63:AB63"/>
-    <mergeCell ref="D102:AB102"/>
-    <mergeCell ref="D73:M73"/>
-    <mergeCell ref="D83:AB83"/>
-    <mergeCell ref="R57:AB57"/>
-    <mergeCell ref="L19:AB19"/>
-    <mergeCell ref="I62:Q62"/>
-    <mergeCell ref="C59:C66"/>
-    <mergeCell ref="I60:Q60"/>
-    <mergeCell ref="D93:H93"/>
-    <mergeCell ref="S73:AB73"/>
-    <mergeCell ref="X41:AB41"/>
-    <mergeCell ref="D28:Q28"/>
-    <mergeCell ref="R66:V66"/>
-    <mergeCell ref="D18:K18"/>
-    <mergeCell ref="D8:K8"/>
-    <mergeCell ref="D25:Q25"/>
-    <mergeCell ref="N72:R72"/>
-    <mergeCell ref="D11:K11"/>
-    <mergeCell ref="R34:AB34"/>
-    <mergeCell ref="D10:K10"/>
-    <mergeCell ref="D79:AB79"/>
-    <mergeCell ref="D27:Q27"/>
-    <mergeCell ref="R65:V65"/>
-    <mergeCell ref="L14:AB14"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="S71:AB71"/>
-    <mergeCell ref="N73:R73"/>
-    <mergeCell ref="D7:K7"/>
-    <mergeCell ref="D81:AB81"/>
-    <mergeCell ref="D48:W48"/>
-    <mergeCell ref="D16:K16"/>
-    <mergeCell ref="I59:Q59"/>
-    <mergeCell ref="L7:AB7"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="D20:K20"/>
-    <mergeCell ref="N70:R70"/>
-    <mergeCell ref="B95:B102"/>
-    <mergeCell ref="R64:V64"/>
-    <mergeCell ref="D44:W44"/>
-    <mergeCell ref="D107:F107"/>
-    <mergeCell ref="D63:H63"/>
-    <mergeCell ref="D74:M74"/>
-    <mergeCell ref="C77:C84"/>
-    <mergeCell ref="D68:M68"/>
-    <mergeCell ref="I86:AB86"/>
-    <mergeCell ref="B32:B39"/>
-    <mergeCell ref="I89:AB89"/>
-    <mergeCell ref="D65:H65"/>
-    <mergeCell ref="AB107:AD107"/>
-    <mergeCell ref="L12:AB12"/>
-    <mergeCell ref="D98:AB98"/>
-    <mergeCell ref="R25:AB25"/>
-    <mergeCell ref="D52:Q52"/>
-    <mergeCell ref="D57:Q57"/>
-    <mergeCell ref="N71:R71"/>
-    <mergeCell ref="C5:C12"/>
-    <mergeCell ref="D69:M69"/>
-    <mergeCell ref="W65:AB65"/>
-    <mergeCell ref="D29:Q29"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="S69:AB69"/>
-    <mergeCell ref="D42:W42"/>
-    <mergeCell ref="X46:AB46"/>
-    <mergeCell ref="D23:Q23"/>
-    <mergeCell ref="D38:Q38"/>
-    <mergeCell ref="R33:AB33"/>
-    <mergeCell ref="D6:K6"/>
-    <mergeCell ref="L5:AB5"/>
-    <mergeCell ref="B41:B48"/>
-    <mergeCell ref="I90:AB90"/>
-    <mergeCell ref="P107:R107"/>
-    <mergeCell ref="R28:AB28"/>
-    <mergeCell ref="B50:B57"/>
-    <mergeCell ref="W62:AB62"/>
-    <mergeCell ref="R59:V59"/>
-    <mergeCell ref="W59:AB59"/>
-    <mergeCell ref="D45:W45"/>
-    <mergeCell ref="R30:AB30"/>
-    <mergeCell ref="W61:AB61"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="R55:AB55"/>
-    <mergeCell ref="D53:Q53"/>
-    <mergeCell ref="D99:AB99"/>
-    <mergeCell ref="R51:AB51"/>
-    <mergeCell ref="R54:AB54"/>
-    <mergeCell ref="R32:AB32"/>
-    <mergeCell ref="D37:Q37"/>
-    <mergeCell ref="X45:AB45"/>
-    <mergeCell ref="D101:AB101"/>
-    <mergeCell ref="R62:V62"/>
-    <mergeCell ref="N69:R69"/>
-    <mergeCell ref="D92:H92"/>
-    <mergeCell ref="D78:AB78"/>
-    <mergeCell ref="R52:AB52"/>
-    <mergeCell ref="D26:Q26"/>
-    <mergeCell ref="X48:AB48"/>
-    <mergeCell ref="D35:Q35"/>
-    <mergeCell ref="X43:AB43"/>
-    <mergeCell ref="D4:AB4"/>
-    <mergeCell ref="R60:V60"/>
-    <mergeCell ref="C86:C93"/>
-    <mergeCell ref="D90:H90"/>
-    <mergeCell ref="I66:Q66"/>
-    <mergeCell ref="W66:AB66"/>
-    <mergeCell ref="C68:C75"/>
-    <mergeCell ref="R63:V63"/>
-    <mergeCell ref="L15:AB15"/>
-    <mergeCell ref="L18:AB18"/>
-    <mergeCell ref="D17:K17"/>
-    <mergeCell ref="L8:AB8"/>
-    <mergeCell ref="L10:AB10"/>
-    <mergeCell ref="D77:AB77"/>
-    <mergeCell ref="D39:Q39"/>
-    <mergeCell ref="R56:AB56"/>
-    <mergeCell ref="X44:AB44"/>
-    <mergeCell ref="I61:Q61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
